--- a/data_skipgram_testing.xlsx
+++ b/data_skipgram_testing.xlsx
@@ -687,309 +687,309 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.001776007768600901</v>
+        <v>-0.4376794099807739</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001351836456432216</v>
+        <v>-0.6669853329658508</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.000131290500168495</v>
+        <v>0.1108608171343803</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0005541077819419674</v>
+        <v>-0.3955333232879639</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0009074081143614073</v>
+        <v>0.1039045676589012</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.00159874172880794</v>
+        <v>-0.466624915599823</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.001483386679343003</v>
+        <v>-0.222147136926651</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.000787498084366912</v>
+        <v>-0.05549504607915878</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.00193334200136346</v>
+        <v>-0.449854850769043</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.0008697818454661179</v>
+        <v>-0.002385182306170464</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0005907569833598639</v>
+        <v>-0.07232334464788437</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.0008240775698844103</v>
+        <v>-0.09250067174434662</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001071975217309669</v>
+        <v>-0.1506260335445404</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0003060459570095105</v>
+        <v>0.2318619042634964</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0004373649396203717</v>
+        <v>0.2807722985744476</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001177041061286063</v>
+        <v>0.0110613601282239</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.0005414198894425215</v>
+        <v>0.1575726866722107</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0003666476983804403</v>
+        <v>-0.6026690602302551</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001359927772568546</v>
+        <v>-0.05801428854465485</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0005411350293310627</v>
+        <v>0.2033176422119141</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.002512370087288066</v>
+        <v>0.1117400303483009</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008195660482895426</v>
+        <v>-0.4343593418598175</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001031538321207329</v>
+        <v>-0.3467110991477966</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.0006016790884575142</v>
+        <v>0.1216372922062874</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.0006386232293594293</v>
+        <v>0.5013274550437927</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.001572137807103435</v>
+        <v>-0.04606025665998459</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.00258428050502912</v>
+        <v>0.08906050026416779</v>
       </c>
       <c r="AB2" t="n">
-        <v>-2.80111438832318e-05</v>
+        <v>-0.02949569188058376</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.559177589755148e-05</v>
+        <v>0.06323827058076859</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.0002075851114519159</v>
+        <v>-0.2241843789815903</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.0008398585603191481</v>
+        <v>-0.01160466391593218</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.000933510911530143</v>
+        <v>-0.2242250293493271</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.001116861844020318</v>
+        <v>-0.3543377220630646</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.001401283978098059</v>
+        <v>-0.2639521956443787</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.001376086467621899</v>
+        <v>-0.1781814992427826</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.000262747049726381</v>
+        <v>0.1208892688155174</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.001449553496551577</v>
+        <v>0.08101175725460052</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.0008761180845708276</v>
+        <v>-0.7230228185653687</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.0001014097816905807</v>
+        <v>-0.1471943706274033</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.001586035453674716</v>
+        <v>0.09038117527961731</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.002238366875761953</v>
+        <v>0.08718881756067276</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.91915682374601e-05</v>
+        <v>0.04761424288153648</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.0009135603770582686</v>
+        <v>0.1249570921063423</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.0007878730606485105</v>
+        <v>-0.02517778985202312</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.0004700291233228193</v>
+        <v>0.1746312826871872</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0.0008791881318297285</v>
+        <v>0.2051965594291687</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.002369861640372062</v>
+        <v>-0.2465875148773193</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.0009787018860587609</v>
+        <v>0.5172117948532104</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.000964837746529401</v>
+        <v>0.2058839797973633</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.001228375107076025</v>
+        <v>-0.28225177526474</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.001154034556778185</v>
+        <v>-0.2607400715351105</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002184713723566374</v>
+        <v>-0.7429633736610413</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0008995686316353448</v>
+        <v>0.08398856222629547</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00138038453865214</v>
+        <v>-0.4700574576854706</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005467563524149724</v>
+        <v>0.159291073679924</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.002529185792432729</v>
+        <v>-0.4384904205799103</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0015245129863152</v>
+        <v>-0.1659969091415405</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0001931917320815278</v>
+        <v>-0.1062516197562218</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.001591940672468959</v>
+        <v>-0.4282546639442444</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005249285454666565</v>
+        <v>0.008421625010669231</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.001687106943850151</v>
+        <v>0.1119534894824028</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001624475624800064</v>
+        <v>-0.1557355225086212</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0004353637850609984</v>
+        <v>-0.3227013945579529</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.000291350923435183</v>
+        <v>0.2293752282857895</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001564956194964098</v>
+        <v>0.291478157043457</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.001833642117515285</v>
+        <v>-0.07834389805793762</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.0003016392669564345</v>
+        <v>0.2801605463027954</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0002734618054103094</v>
+        <v>-0.61661696434021</v>
       </c>
       <c r="S3" t="n">
-        <v>0.002928623686219788</v>
+        <v>-0.02374829910695553</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0008862710763067817</v>
+        <v>0.1936531215906143</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.001964854409876466</v>
+        <v>0.2525511682033539</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0004298094735511692</v>
+        <v>-0.4789888560771942</v>
       </c>
       <c r="W3" t="n">
-        <v>0.001463364620747612</v>
+        <v>-0.3248719871044159</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.0001787038731046094</v>
+        <v>0.06840001046657562</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.0004121402949196259</v>
+        <v>0.4876037538051605</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.001136602802429685</v>
+        <v>-0.01297631114721298</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.532671269613597e-05</v>
+        <v>0.2096331119537354</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.002693789754008792</v>
+        <v>-0.1148270443081856</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.001372802874372881</v>
+        <v>0.1247165501117706</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.0002092529688246049</v>
+        <v>-0.2254936099052429</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.001538676101000421</v>
+        <v>-0.005714231170713902</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.0004115271836853295</v>
+        <v>-0.4114654064178467</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.001623592658261469</v>
+        <v>-0.3965286612510681</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.002341829315123803</v>
+        <v>-0.3331825733184814</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.0001787193250644583</v>
+        <v>-0.1034622862935066</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.001269127675364188</v>
+        <v>0.1764350682497025</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.0003210343515175822</v>
+        <v>0.01439967378973961</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.0001030735798999052</v>
+        <v>-0.779029905796051</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.0004487779541344749</v>
+        <v>-0.2222966551780701</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.0001467379750849488</v>
+        <v>0.05198205262422562</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.0007601277438801213</v>
+        <v>0.212236762046814</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.001727505988162883</v>
+        <v>-0.1172317489981651</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.001824553565275697</v>
+        <v>0.04287764057517052</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.0001055597681462047</v>
+        <v>0.05011151731014252</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0008843950016454049</v>
+        <v>0.06993597745895386</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.001364899219511808</v>
+        <v>0.2501054704189301</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.0003568881114932487</v>
+        <v>-0.3071699738502502</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.000618176396692584</v>
+        <v>0.4634707570075989</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.001024756949134486</v>
+        <v>0.2385922223329544</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.001565640345260599</v>
+        <v>-0.1275933086872101</v>
       </c>
       <c r="AY3" t="n">
         <v>1</v>
@@ -997,154 +997,154 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0.001572186324431318</v>
+        <v>-0.2851965725421906</v>
       </c>
       <c r="B4" t="n">
-        <v>0.001280424200435985</v>
+        <v>-0.4455805718898773</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.001091991502971667</v>
+        <v>0.1659360080957413</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.000880288989177977</v>
+        <v>-0.2772097587585449</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0005628949415703248</v>
+        <v>0.07135864347219467</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.004275379440693844</v>
+        <v>-0.3258165717124939</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.001526135577154251</v>
+        <v>-0.1150088757276535</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.000582119329646938</v>
+        <v>-0.005745626054704189</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.003401311130866765</v>
+        <v>-0.4663284420967102</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.002500729093896077</v>
+        <v>-0.006704442203044891</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001565453843933809</v>
+        <v>-0.0464642271399498</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0006879131859742013</v>
+        <v>-0.1194339469075203</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0001115646637113325</v>
+        <v>-0.04811515286564827</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0003579531038080494</v>
+        <v>0.4212293326854706</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0007268668065234018</v>
+        <v>0.1788919121026993</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0005831851444465252</v>
+        <v>0.1585516780614853</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0002584277942900769</v>
+        <v>0.1777128577232361</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001331549931563433</v>
+        <v>-0.6044647097587585</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003564373536658048</v>
+        <v>-0.1026172116398811</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0006604421904614537</v>
+        <v>0.1040594279766083</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0001404625007719473</v>
+        <v>0.1300135999917984</v>
       </c>
       <c r="V4" t="n">
-        <v>0.003570197012444985</v>
+        <v>-0.3519763648509979</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0001797079866795386</v>
+        <v>-0.3034533262252808</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.000393052770497574</v>
+        <v>0.1689444780349731</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.0003566374161630142</v>
+        <v>0.4930707216262817</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.001219392707565635</v>
+        <v>0.06547561287879944</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0001752746114099165</v>
+        <v>0.01590987667441368</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.001598365879967404</v>
+        <v>0.002910256385803223</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.002425668757995615</v>
+        <v>0.02752806805074215</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0003952921354732957</v>
+        <v>-0.07336685061454773</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0004545980247405221</v>
+        <v>0.02232668735086918</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0006504259781751372</v>
+        <v>-0.1536982506513596</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.002310812705796189</v>
+        <v>-0.2584252655506134</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.001414427981016997</v>
+        <v>-0.2183492183685303</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.0003505272506450288</v>
+        <v>-0.1630683690309525</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.001753439772344204</v>
+        <v>0.1362833827733994</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.000596428181228933</v>
+        <v>0.04840843006968498</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.0007522698030539566</v>
+        <v>-0.5696082711219788</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0008422010913212507</v>
+        <v>-0.1028088703751564</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.0005902817074060094</v>
+        <v>0.06724578887224197</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.0002485006896336426</v>
+        <v>0.01702936366200447</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.002668286533525664</v>
+        <v>0.04875670745968819</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.0007919115006742947</v>
+        <v>-0.002947199624031782</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.0003925164289066061</v>
+        <v>-0.1365523487329483</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.001040861163188982</v>
+        <v>0.2331007868051529</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.0006664467352631929</v>
+        <v>0.2929077744483948</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.002829287648199453</v>
+        <v>-0.317444771528244</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.001448271424573527</v>
+        <v>0.3243308067321777</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.001067534925192315</v>
+        <v>0.2391465455293655</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.001754554264235432</v>
+        <v>-0.2554647326469421</v>
       </c>
       <c r="AY4" t="n">
         <v>1</v>
@@ -1152,154 +1152,154 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0.0007028393312140633</v>
+        <v>-0.3807328641414642</v>
       </c>
       <c r="B5" t="n">
-        <v>0.001843154177421579</v>
+        <v>-0.757359504699707</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.00218183791131333</v>
+        <v>0.2017263472080231</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0007390256358001177</v>
+        <v>-0.3856419920921326</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001091857634614118</v>
+        <v>0.14090895652771</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.002567259022785456</v>
+        <v>-0.5020096898078918</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0009694771361549896</v>
+        <v>-0.1039757952094078</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.002979817296767686</v>
+        <v>-0.07267353683710098</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.002421118476171615</v>
+        <v>-0.4583375751972198</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.001656523936117899</v>
+        <v>0.003629842074587941</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0004163047653111358</v>
+        <v>0.1071151569485664</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005341537846586577</v>
+        <v>-0.08667617291212082</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001595180732668601</v>
+        <v>-0.2852366268634796</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0005041087651472951</v>
+        <v>0.1494068652391434</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0002769695920356007</v>
+        <v>0.3978273570537567</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.002296824895760445</v>
+        <v>-0.03235464170575142</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.000503807243329283</v>
+        <v>0.2130731493234634</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.001167022764537978</v>
+        <v>-0.6768657565116882</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004193264590233396</v>
+        <v>-0.009998905472457409</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0006566169813005071</v>
+        <v>0.1998831331729889</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.002357049803521067</v>
+        <v>0.2080437839031219</v>
       </c>
       <c r="V5" t="n">
-        <v>0.001250565777319051</v>
+        <v>-0.4949993491172791</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0005015655030045201</v>
+        <v>-0.3142072558403015</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0001878692411821026</v>
+        <v>0.1418488472700119</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0006061500168848781</v>
+        <v>0.4709171652793884</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.002288126467045319</v>
+        <v>-0.1468804478645325</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.000423018788305258</v>
+        <v>0.173706904053688</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.001047164827229387</v>
+        <v>-0.239596962928772</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.02903078625774e-05</v>
+        <v>0.2295169979333878</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.001662509289571568</v>
+        <v>-0.2274740487337112</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.001861369525121744</v>
+        <v>-0.08322078734636307</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.001563401530911579</v>
+        <v>-0.4131959676742554</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.001395810953043788</v>
+        <v>-0.4512740671634674</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.002159120520307188</v>
+        <v>-0.3545535504817963</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.001994840310073686</v>
+        <v>-0.1613670587539673</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.002083562064566599</v>
+        <v>0.1846732348203659</v>
       </c>
       <c r="AK5" t="n">
-        <v>6.215446634517275e-05</v>
+        <v>0.08171994239091873</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.000399992121289709</v>
+        <v>-0.7607449889183044</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.001249993138943469</v>
+        <v>-0.1413888782262802</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.0006803338341067625</v>
+        <v>-0.03774240240454674</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0009854750176742659</v>
+        <v>0.1953532993793488</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.000293510922307589</v>
+        <v>0.01735339500010014</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.000258085286949505</v>
+        <v>0.08965089172124863</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.001157902003644586</v>
+        <v>0.08412124216556549</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.001286330116098017</v>
+        <v>0.09021931886672974</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.0009527824407763459</v>
+        <v>0.2331555783748627</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.001799631645492463</v>
+        <v>-0.2194082289934158</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.002784668945252816</v>
+        <v>0.5701063871383667</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.001599616716743272</v>
+        <v>0.09345061331987381</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.002079500142684373</v>
+        <v>-0.1431385278701782</v>
       </c>
       <c r="AY5" t="n">
         <v>1</v>
@@ -1307,309 +1307,309 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0.001661862119139785</v>
+        <v>-0.493979811668396</v>
       </c>
       <c r="B6" t="n">
-        <v>0.002744975273767957</v>
+        <v>-0.906187117099762</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0009707240462092559</v>
+        <v>0.3394304215908051</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001233576808398809</v>
+        <v>-0.3037749230861664</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001296814064163035</v>
+        <v>0.1430048495531082</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0003232316072152333</v>
+        <v>-0.4796672463417053</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.003093083839775376</v>
+        <v>-0.1097825467586517</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0008901867768356199</v>
+        <v>-0.1977571547031403</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.001787330335900951</v>
+        <v>-0.4297157824039459</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.001086021254657368</v>
+        <v>0.05806911364197731</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.001058384394050785</v>
+        <v>0.2233830243349075</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0004667401125856574</v>
+        <v>-0.1105020195245743</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0009526922407311919</v>
+        <v>-0.3041168451309204</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002527978576363725</v>
+        <v>0.1535240113735199</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0003300524371225578</v>
+        <v>0.458317369222641</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.001086524379956503</v>
+        <v>0.02417317591607571</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001134486842987534</v>
+        <v>0.1195904016494751</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0007960055698685451</v>
+        <v>-0.7738772034645081</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002061757440464483</v>
+        <v>0.07271300256252289</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0004866230415734095</v>
+        <v>0.2183335870504379</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0004886563884200188</v>
+        <v>0.2571606636047363</v>
       </c>
       <c r="V6" t="n">
-        <v>0.001128817287519807</v>
+        <v>-0.5687812566757202</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0006353124579421614</v>
+        <v>-0.4194035232067108</v>
       </c>
       <c r="X6" t="n">
-        <v>-7.716965908790472e-05</v>
+        <v>0.1578142046928406</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0005821842645597977</v>
+        <v>0.4956386089324951</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.002286285851552333</v>
+        <v>-0.2064811885356903</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0006914532198730234</v>
+        <v>0.1471113413572311</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0002545682433926898</v>
+        <v>-0.3282759487628937</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.001218312306930837</v>
+        <v>0.4147102534770966</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.0001864255476282224</v>
+        <v>-0.2258486598730087</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.0005054288315935322</v>
+        <v>-0.1477210521697998</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.001159559084896634</v>
+        <v>-0.4099305272102356</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.002273305691357231</v>
+        <v>-0.4887963533401489</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.002017668418375829</v>
+        <v>-0.3592402338981628</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.000477290099930611</v>
+        <v>-0.180294468998909</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0008894114659035305</v>
+        <v>0.2127759456634521</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.0004392852815764338</v>
+        <v>0.07176738977432251</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.001691978909717429</v>
+        <v>-0.7720219492912292</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.0004676631047778255</v>
+        <v>-0.1890179812908173</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.0004134470151751604</v>
+        <v>-0.1989350765943527</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.002296577127829125</v>
+        <v>0.2573147416114807</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.001195609045841051</v>
+        <v>0.04032082483172417</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.001570895554245056</v>
+        <v>0.09117253124713898</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.0007903175525260812</v>
+        <v>0.06963425129652023</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.001044778544272095</v>
+        <v>0.1611543595790863</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.0008431307604697146</v>
+        <v>0.2294671535491943</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.001766986391724206</v>
+        <v>-0.3351448774337769</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.001005702660909848</v>
+        <v>0.3520559966564178</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.0007193428806561669</v>
+        <v>-0.02334628067910671</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.00232299402446007</v>
+        <v>-0.1124632135033607</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0.001901594941410894</v>
+        <v>-0.4416503608226776</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0006439446488892742</v>
+        <v>-0.816383421421051</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0006196805192187247</v>
+        <v>0.2310643345117569</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0005057878591590344</v>
+        <v>-0.3123792707920074</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0003127623316235839</v>
+        <v>0.1464854180812836</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002838567137831143</v>
+        <v>-0.4033383131027222</v>
       </c>
       <c r="G7" t="n">
-        <v>2.722550554686077e-05</v>
+        <v>-0.1376257091760635</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0008449153259185715</v>
+        <v>-0.05800968408584595</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.003624725518368085</v>
+        <v>-0.4083372354507446</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.001942175740186991</v>
+        <v>-0.005698347929865122</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0006845852943539703</v>
+        <v>0.08976057916879654</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.001490228039709095</v>
+        <v>-0.06452414393424988</v>
       </c>
       <c r="M7" t="n">
-        <v>0.003241041790291547</v>
+        <v>-0.2631322145462036</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0002939643522989413</v>
+        <v>0.2106028199195862</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0001205320066462729</v>
+        <v>0.3489574790000916</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.0007867562227662007</v>
+        <v>-0.01047379989176989</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.925139909511904e-05</v>
+        <v>0.1628014147281647</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002024307798027461</v>
+        <v>-0.660418689250946</v>
       </c>
       <c r="S7" t="n">
-        <v>0.004757051630997666</v>
+        <v>-0.03211230784654617</v>
       </c>
       <c r="T7" t="n">
-        <v>0.002528844316442572</v>
+        <v>0.2040765285491943</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.002030030733276126</v>
+        <v>0.108354426920414</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.0004151790536262918</v>
+        <v>-0.4649358093738556</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0006587284440518488</v>
+        <v>-0.3259482979774475</v>
       </c>
       <c r="X7" t="n">
-        <v>0.002883950321917637</v>
+        <v>0.1274779886007309</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001694607850685012</v>
+        <v>0.4749771654605865</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0006261418333569873</v>
+        <v>-0.1405873596668243</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.001665631768442386</v>
+        <v>0.1486401706933975</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0003179715585918718</v>
+        <v>-0.3258440792560577</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.003886273216014246</v>
+        <v>0.3036745190620422</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.000882378428575923</v>
+        <v>-0.1996991634368896</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.0006241977496335066</v>
+        <v>-0.06954924017190933</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.002179672158778819</v>
+        <v>-0.3573387563228607</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.003154005705626604</v>
+        <v>-0.4707641899585724</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.003579714732094426</v>
+        <v>-0.3323400616645813</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0003438780546830615</v>
+        <v>-0.1337276995182037</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0001246251439229529</v>
+        <v>0.13520647585392</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.001457795342291863</v>
+        <v>0.07974254339933395</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.001965457712526424</v>
+        <v>-0.6464630961418152</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0005949626567763743</v>
+        <v>-0.172204002737999</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.002517746559487073</v>
+        <v>-0.1412772685289383</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.001842853590846389</v>
+        <v>0.2178712487220764</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.001845343391754397</v>
+        <v>0.03375809267163277</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.000117548438343696</v>
+        <v>0.1038702949881554</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.001801251628201043</v>
+        <v>0.004164182581007481</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.003441951120793247</v>
+        <v>0.09724362939596176</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.003100686221297503</v>
+        <v>0.172182485461235</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.001022547893886696</v>
+        <v>-0.2119139581918716</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.0006473140676593388</v>
+        <v>0.4257508516311646</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.0006843239247763585</v>
+        <v>0.1635100096464157</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.003542400572013372</v>
+        <v>-0.1113829463720322</v>
       </c>
       <c r="AY7" t="n">
         <v>1</v>
@@ -1617,309 +1617,309 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0003333936059228353</v>
+        <v>-0.3225782811641693</v>
       </c>
       <c r="B8" t="n">
-        <v>0.002707428531335325</v>
+        <v>-0.5031809210777283</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.001944645863794137</v>
+        <v>0.1526766717433929</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0002186430851063921</v>
+        <v>-0.2753248810768127</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0005805016984481982</v>
+        <v>0.07582160085439682</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0009519014783858995</v>
+        <v>-0.2768823206424713</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.001610064955692541</v>
+        <v>-0.1497514098882675</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.001348331271555919</v>
+        <v>0.0004157331422902644</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.001478619461388677</v>
+        <v>-0.4734157919883728</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0003456199408109903</v>
+        <v>-0.03046010062098503</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0001852383061712484</v>
+        <v>-0.08337230980396271</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0005412486444064418</v>
+        <v>-0.1475317031145096</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0003706537080348634</v>
+        <v>-0.1623921245336533</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0001663396735387924</v>
+        <v>0.3317847847938538</v>
       </c>
       <c r="O8" t="n">
-        <v>0.001489106127506446</v>
+        <v>0.1536774039268494</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.001000596362340255</v>
+        <v>0.1236855313181877</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0008265540125141501</v>
+        <v>0.1787065863609314</v>
       </c>
       <c r="R8" t="n">
-        <v>-7.792420472569767e-05</v>
+        <v>-0.4986359477043152</v>
       </c>
       <c r="S8" t="n">
-        <v>0.000121070390603289</v>
+        <v>-0.1373085975646973</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.001271846577991298</v>
+        <v>0.08016081899404526</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0002916883967453095</v>
+        <v>0.09049596637487411</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0001894305369615638</v>
+        <v>-0.3490438461303711</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.00109963914071041</v>
+        <v>-0.2921131551265717</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001448581979859657</v>
+        <v>0.1421898603439331</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0007480026870271932</v>
+        <v>0.438051700592041</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.001959911703306726</v>
+        <v>0.02677181549370289</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0005995276313095821</v>
+        <v>-0.01423707231879234</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.001406972064946692</v>
+        <v>-0.007325825747102499</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.001625642326762117</v>
+        <v>-0.00304233212955296</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.00107515944638598</v>
+        <v>-0.09209765493869781</v>
       </c>
       <c r="AE8" t="n">
-        <v>7.59514073711894e-06</v>
+        <v>0.02224242873489857</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.00150529323832696</v>
+        <v>-0.1039642542600632</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.001708230588536428</v>
+        <v>-0.3016222715377808</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.0004867919635416422</v>
+        <v>-0.1662070006132126</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0001728873373435767</v>
+        <v>-0.1316977292299271</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.001763797750013654</v>
+        <v>0.09289585798978806</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.001811241642899675</v>
+        <v>0.01766087859869003</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0009644077937926034</v>
+        <v>-0.583210825920105</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0.0007379426613362396</v>
+        <v>-0.1449975818395615</v>
       </c>
       <c r="AN8" t="n">
-        <v>-5.357799049341058e-06</v>
+        <v>0.1043941080570221</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.001307990451511598</v>
+        <v>-0.02221334539353848</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.001039459029388527</v>
+        <v>0.1085151061415672</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.002164465992846691</v>
+        <v>0.09489854425191879</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.001607425987773698</v>
+        <v>-0.1409794688224792</v>
       </c>
       <c r="AS8" t="n">
-        <v>-0.001275303448913712</v>
+        <v>0.2621213495731354</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.555792517275645e-05</v>
+        <v>0.2030261754989624</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.0006401703615319381</v>
+        <v>-0.3110019862651825</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.001504883143689683</v>
+        <v>0.3297373056411743</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0004790393566164002</v>
+        <v>0.180753618478775</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.001884396287383608</v>
+        <v>-0.2521210908889771</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0.002205109181120947</v>
+        <v>-0.4139147996902466</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0006947425286588425</v>
+        <v>-0.7954563498497009</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.001892657672615407</v>
+        <v>0.2061206698417664</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0003301972100116358</v>
+        <v>-0.3564907014369965</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001009584220930577</v>
+        <v>0.03119701147079468</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.002278443265394866</v>
+        <v>-0.5226585268974304</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.002325018963552976</v>
+        <v>-0.1192100197076797</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.001918406782398452</v>
+        <v>-0.1102196723222733</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.002716642885384449</v>
+        <v>-0.456668496131897</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.001617579636650091</v>
+        <v>0.005593256093561649</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0003035234588523254</v>
+        <v>0.07819119840860367</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0002694934188529507</v>
+        <v>-0.06085779145359993</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.000736715951074629</v>
+        <v>-0.2880086600780487</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0003347088434683169</v>
+        <v>0.1984082758426666</v>
       </c>
       <c r="O9" t="n">
-        <v>0.000427364253842066</v>
+        <v>0.3766690790653229</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.00279503009986202</v>
+        <v>-0.07757074385881424</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.002403715736414202</v>
+        <v>0.1740548759698868</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.0005031203738473274</v>
+        <v>-0.7191902995109558</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002731452589778841</v>
+        <v>0.02665557526051998</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0008075199557640938</v>
+        <v>0.2353903651237488</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0001452608397425948</v>
+        <v>0.1718743890523911</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001654759246641824</v>
+        <v>-0.5095469951629639</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.001313503316806362</v>
+        <v>-0.3141758143901825</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.0003794624792675225</v>
+        <v>0.1589548140764236</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.136071220165909e-05</v>
+        <v>0.524151086807251</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.002870781866625202</v>
+        <v>-0.1334067732095718</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0002236512057877481</v>
+        <v>0.2399897873401642</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.001145850478261084</v>
+        <v>-0.1904216110706329</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.001678570587060542</v>
+        <v>0.1987936645746231</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0007780522677950386</v>
+        <v>-0.2539132237434387</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.001823632191951043</v>
+        <v>-0.06550928950309753</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.0002495719272860407</v>
+        <v>-0.3618475198745728</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.001810873415369494</v>
+        <v>-0.4505641758441925</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.002536508397114782</v>
+        <v>-0.3626830875873566</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.001555059719039802</v>
+        <v>-0.1731360703706741</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.003117792657810985</v>
+        <v>0.1968348920345306</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.001056009203270292</v>
+        <v>0.1072264611721039</v>
       </c>
       <c r="AL9" t="n">
-        <v>8.661636631335398e-05</v>
+        <v>-0.7659903764724731</v>
       </c>
       <c r="AM9" t="n">
-        <v>4.483332130392666e-05</v>
+        <v>-0.1342098116874695</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.0002764418036577678</v>
+        <v>-0.03292392939329147</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.0003189731263841963</v>
+        <v>0.1879492998123169</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0006350315601772542</v>
+        <v>-0.03861472010612488</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.0001071679754196584</v>
+        <v>0.04123151674866676</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.001795603818106068</v>
+        <v>0.001804073457606137</v>
       </c>
       <c r="AS9" t="n">
-        <v>-0.0009211008261872876</v>
+        <v>0.1272266060113907</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.0002161703754091004</v>
+        <v>0.2589588463306427</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.0009441407197598716</v>
+        <v>-0.2364661991596222</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.001182550015947551</v>
+        <v>0.5444678068161011</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.000301696794178231</v>
+        <v>0.07831430435180664</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.0008307778571214402</v>
+        <v>-0.1609886139631271</v>
       </c>
       <c r="AY9" t="n">
         <v>1</v>
@@ -1927,154 +1927,154 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0.002145123297356893</v>
+        <v>-0.4474331736564636</v>
       </c>
       <c r="B10" t="n">
-        <v>0.001545919744648323</v>
+        <v>-0.65813148021698</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.00160148125913464</v>
+        <v>0.2220528423786163</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0003446679414288325</v>
+        <v>-0.2422275245189667</v>
       </c>
       <c r="E10" t="n">
-        <v>7.36461625663546e-05</v>
+        <v>0.1672690361738205</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.002474766043995459</v>
+        <v>-0.4392707347869873</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.002269175783346132</v>
+        <v>-0.1399498134851456</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0009870044507513059</v>
+        <v>-0.1286080479621887</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.002936187381557473</v>
+        <v>-0.4197312891483307</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.001706686490284031</v>
+        <v>0.05497275665402412</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001814437329782909</v>
+        <v>0.1239662021398544</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0002081601972331184</v>
+        <v>-0.08470830321311951</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0003172225946626409</v>
+        <v>-0.2831909358501434</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0007110114784982755</v>
+        <v>0.3082621693611145</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.751178058610885e-05</v>
+        <v>0.3374238610267639</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.001724754256182999</v>
+        <v>0.07007688283920288</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0004623503964760404</v>
+        <v>0.0265588816255331</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.000314033075650733</v>
+        <v>-0.6087594032287598</v>
       </c>
       <c r="S10" t="n">
-        <v>0.002384700011917569</v>
+        <v>0.04668018966913223</v>
       </c>
       <c r="T10" t="n">
-        <v>0.001822982006045782</v>
+        <v>0.2185011655092239</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.001994018581190631</v>
+        <v>0.1813826262950897</v>
       </c>
       <c r="V10" t="n">
-        <v>0.002403060256086923</v>
+        <v>-0.4481462836265564</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0002641568104228772</v>
+        <v>-0.3399818539619446</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.000268955890771179</v>
+        <v>0.2206493765115738</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.0003533249543698321</v>
+        <v>0.4475933909416199</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.003080219134272439</v>
+        <v>-0.1335562914609909</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0009106481670414494</v>
+        <v>0.1624075323343277</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.001540822336797091</v>
+        <v>-0.1332186460494995</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.0006882584845016392</v>
+        <v>0.1814530938863754</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0007034912550713476</v>
+        <v>-0.2046146541833878</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0008493054655978701</v>
+        <v>-0.05404436215758324</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.001276756610462686</v>
+        <v>-0.2987118065357208</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.002219242881441953</v>
+        <v>-0.4648769795894623</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.001596737429292611</v>
+        <v>-0.1857080310583115</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.002185236644521764</v>
+        <v>-0.2078747749328613</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.003841429920444856</v>
+        <v>0.1269083619117737</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.0009309037754533385</v>
+        <v>0.1643454730510712</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.0008764651581143714</v>
+        <v>-0.6727087497711182</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.001013610701829604</v>
+        <v>-0.1724907755851746</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.00195504760237896</v>
+        <v>0.01558991428464651</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.001376766704820319</v>
+        <v>0.04083799198269844</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.001390125298949727</v>
+        <v>0.00112455862108618</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.001209540436450194</v>
+        <v>0.1057601943612099</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.002343706740143361</v>
+        <v>-0.05077983066439629</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.000637413905253405</v>
+        <v>0.1558593660593033</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.0008714715422310147</v>
+        <v>0.2469978481531143</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.003285110724750258</v>
+        <v>-0.3335477113723755</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.000495702710567839</v>
+        <v>0.4485160708427429</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.0008986718233490833</v>
+        <v>0.04956324025988579</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.001708543388142902</v>
+        <v>-0.2139402776956558</v>
       </c>
       <c r="AY10" t="n">
         <v>1</v>
@@ -2082,309 +2082,309 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.0007198733510512164</v>
+        <v>-0.3375508189201355</v>
       </c>
       <c r="B11" t="n">
-        <v>0.003005258468890991</v>
+        <v>-0.9660824537277222</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0004030225156015496</v>
+        <v>0.4393262267112732</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0008929505409253316</v>
+        <v>-0.284423828125</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0003461335427449415</v>
+        <v>0.1739552468061447</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.001858715033109116</v>
+        <v>-0.5529510378837585</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0009284657116348545</v>
+        <v>0.04933826997876167</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0008718736201552473</v>
+        <v>-0.05486749857664108</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.002041526587507776</v>
+        <v>-0.4792252779006958</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.001426921927964711</v>
+        <v>-0.004477648064494133</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0003561304660602724</v>
+        <v>0.1878903657197952</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0007432416587262507</v>
+        <v>0.004350845701992512</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0008888633148649553</v>
+        <v>-0.4491163790225983</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0001985598581770124</v>
+        <v>0.1775009781122208</v>
       </c>
       <c r="O11" t="n">
-        <v>0.001619648703322156</v>
+        <v>0.4607645869255066</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.0001279141314325981</v>
+        <v>-0.06019533798098564</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0008355083361523453</v>
+        <v>0.1383921355009079</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.0005397583422540327</v>
+        <v>-0.7992656826972961</v>
       </c>
       <c r="S11" t="n">
-        <v>0.001297766768487689</v>
+        <v>0.02028290554881096</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0004660437494398541</v>
+        <v>0.1847085505723953</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.001048105792361051</v>
+        <v>0.2871144413948059</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.0002041441957569048</v>
+        <v>-0.7274510860443115</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.001356239649985723</v>
+        <v>-0.4619045555591583</v>
       </c>
       <c r="X11" t="n">
-        <v>0.000517503736133052</v>
+        <v>0.1527691334486008</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0003870167792893627</v>
+        <v>0.4879476130008698</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.001981971615818145</v>
+        <v>-0.2279496788978577</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0006037314277506777</v>
+        <v>0.2720246016979218</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.000823818915644847</v>
+        <v>-0.3573585748672485</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.001015782247435248</v>
+        <v>0.4697335660457611</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0005700418923140261</v>
+        <v>-0.2255748957395554</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.000852336220796698</v>
+        <v>-0.1878692060709</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.002490622066245356</v>
+        <v>-0.5594081878662109</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.001294584306568587</v>
+        <v>-0.6427844166755676</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0.0003498821136732633</v>
+        <v>-0.4525806307792664</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.0009065687333221538</v>
+        <v>-0.1253995150327682</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.001173723653933103</v>
+        <v>0.2920138537883759</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.000412433555547069</v>
+        <v>0.0007775829290039837</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.0003152111873578887</v>
+        <v>-0.8351773023605347</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0003237257281392019</v>
+        <v>-0.1597317159175873</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.0007336947345092465</v>
+        <v>-0.3155811131000519</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.0001319162583470135</v>
+        <v>0.4004271030426025</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.0002629853421249213</v>
+        <v>-0.02200699225068092</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.000664485491176839</v>
+        <v>0.05750659480690956</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.93072990217617e-05</v>
+        <v>-0.01011199876666069</v>
       </c>
       <c r="AS11" t="n">
-        <v>-0.0005086896351131705</v>
+        <v>0.1128322705626488</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0.0009147209493377287</v>
+        <v>0.2167607098817825</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.035647969049271e-05</v>
+        <v>-0.2600299119949341</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.002735424725186884</v>
+        <v>0.364639550447464</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.0003616190467024375</v>
+        <v>0.03310070186853409</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.0004366662094648364</v>
+        <v>-0.0586516298353672</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-0.002824219193897264</v>
+        <v>-0.2730807065963745</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0007294023788288991</v>
+        <v>-0.7005878090858459</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.002532697892053426</v>
+        <v>0.3422141969203949</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.002921395755815886</v>
+        <v>0.0006083181360736489</v>
       </c>
       <c r="E12" t="n">
-        <v>0.001549547467515473</v>
+        <v>0.3125644326210022</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.003624886876320767</v>
+        <v>-0.1933600455522537</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0007002813039243549</v>
+        <v>-0.1234471425414085</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0001369550954300249</v>
+        <v>-0.1356116384267807</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.009073148711133275</v>
+        <v>-0.7128939628601074</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0006146617628874546</v>
+        <v>0.01038550399243832</v>
       </c>
       <c r="K12" t="n">
-        <v>0.002557016065553597</v>
+        <v>0.3221528232097626</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0005812329828545253</v>
+        <v>-0.1619267910718918</v>
       </c>
       <c r="M12" t="n">
-        <v>0.002615619556683021</v>
+        <v>-0.2514184713363647</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.003044750046229895</v>
+        <v>0.5086818337440491</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0012796660818135</v>
+        <v>0.4223620891571045</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.003179568770498436</v>
+        <v>0.1439007073640823</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.002664235675421028</v>
+        <v>0.01473435573279858</v>
       </c>
       <c r="R12" t="n">
-        <v>0.001134888644021308</v>
+        <v>-0.4910756945610046</v>
       </c>
       <c r="S12" t="n">
-        <v>0.009444227267954899</v>
+        <v>-0.1294562369585037</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0001016875263525996</v>
+        <v>0.4775163531303406</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.001474562619870438</v>
+        <v>0.198214203119278</v>
       </c>
       <c r="V12" t="n">
-        <v>0.002271289651497402</v>
+        <v>-0.3368191123008728</v>
       </c>
       <c r="W12" t="n">
-        <v>0.003883642245656599</v>
+        <v>-0.3160361051559448</v>
       </c>
       <c r="X12" t="n">
-        <v>8.974313440436645e-06</v>
+        <v>0.3950160145759583</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0002078049214396303</v>
+        <v>0.613580048084259</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0004332290697218687</v>
+        <v>0.01350946631282568</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.00216191781885442</v>
+        <v>0.1444632112979889</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.001608463763379169</v>
+        <v>-0.2933333218097687</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.002486572030396581</v>
+        <v>-0.04942192509770393</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0001169423631145605</v>
+        <v>-0.09333343803882599</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.0003646149655440639</v>
+        <v>-0.1255511045455933</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.00151621127435527</v>
+        <v>-0.2768644094467163</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.003403904329916997</v>
+        <v>-0.3785906434059143</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.00581669070851864</v>
+        <v>-0.1631979197263718</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.0006155026428072376</v>
+        <v>-0.1573414355516434</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.001138680400896489</v>
+        <v>0.1452436745166779</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.002756803167872371</v>
+        <v>0.02660147473216057</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.001061394715505885</v>
+        <v>-0.6000322699546814</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.002344904031917331</v>
+        <v>-0.05802979692816734</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.0005808877734257659</v>
+        <v>-0.1166555732488632</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.004322337638147213</v>
+        <v>0.1710294932126999</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.004203135285750446</v>
+        <v>0.01509209908545017</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.003458239666196125</v>
+        <v>0.1004811748862267</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.001621798032983744</v>
+        <v>0.02525816857814789</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.001507371443367499</v>
+        <v>0.2894142270088196</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.00262873819264737</v>
+        <v>0.207002729177475</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.004522733958040436</v>
+        <v>-0.3282931745052338</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.0002032429146797541</v>
+        <v>0.3926712572574615</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.002376873233506102</v>
+        <v>0.2754518389701843</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.006400167096671921</v>
+        <v>-0.3187676966190338</v>
       </c>
       <c r="AY12" t="n">
         <v>1</v>
@@ -2392,154 +2392,154 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-0.0002372739770418826</v>
+        <v>-0.2613119184970856</v>
       </c>
       <c r="B13" t="n">
-        <v>0.003217680992619927</v>
+        <v>-0.5231353640556335</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.001171069081374112</v>
+        <v>0.1445508003234863</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0009474913330175869</v>
+        <v>-0.2549810409545898</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.001690574389939177</v>
+        <v>0.07698151469230652</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.002420158892456855</v>
+        <v>-0.2328624427318573</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0009331769693331252</v>
+        <v>-0.2497898936271667</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.00132778715235225</v>
+        <v>-0.0626460462808609</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.00342933011724635</v>
+        <v>-0.4992201626300812</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0004451216341337242</v>
+        <v>0.01503492891788483</v>
       </c>
       <c r="K13" t="n">
-        <v>0.001439881610273121</v>
+        <v>-0.005216008983552456</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.0002303291195010033</v>
+        <v>-0.08261369168758392</v>
       </c>
       <c r="M13" t="n">
-        <v>8.822995072369976e-07</v>
+        <v>-0.1879062801599503</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.212957563635538e-05</v>
+        <v>0.3504605889320374</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0004387500817797904</v>
+        <v>0.1752933263778687</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.002224294397235361</v>
+        <v>0.118165947496891</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0005756898393108879</v>
+        <v>0.1053741574287415</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.001106134262134852</v>
+        <v>-0.5106444358825684</v>
       </c>
       <c r="S13" t="n">
-        <v>0.001534810521717524</v>
+        <v>-0.1168060526251793</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0005553671468347019</v>
+        <v>0.1465958952903748</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.002415409361897847</v>
+        <v>0.08906036615371704</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.00023354422732175</v>
+        <v>-0.3657196462154388</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.001446973919629539</v>
+        <v>-0.2308162003755569</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0003936731658178824</v>
+        <v>0.2027848213911057</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.0002172891501119681</v>
+        <v>0.4851996004581451</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.002367041867194677</v>
+        <v>0.04705247282981873</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0004227787923816</v>
+        <v>-0.04771599173545837</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.004251518262930956</v>
+        <v>-0.103361688554287</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.0008077496221407927</v>
+        <v>0.06139229610562325</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.001293040094605173</v>
+        <v>-0.1448692381381989</v>
       </c>
       <c r="AE13" t="n">
-        <v>4.712586043733077e-05</v>
+        <v>0.01643037796020508</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.0005454647432944952</v>
+        <v>-0.1230861693620682</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.003156322266796833</v>
+        <v>-0.3050646185874939</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0.001388530618178911</v>
+        <v>-0.184575691819191</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.001195332245149279</v>
+        <v>-0.1562591791152954</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.00379319831353969</v>
+        <v>0.1294735968112946</v>
       </c>
       <c r="AK13" t="n">
-        <v>6.610775813817578e-07</v>
+        <v>-0.01021974720060825</v>
       </c>
       <c r="AL13" t="n">
-        <v>-9.579423949741274e-05</v>
+        <v>-0.6486862301826477</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0.0004040328704711914</v>
+        <v>-0.207745686173439</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.001764225186948345</v>
+        <v>0.1018159464001656</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.001698207958123533</v>
+        <v>0.08697208017110825</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.001048575364464779</v>
+        <v>0.01158058177679777</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.000689876112876973</v>
+        <v>0.04092271998524666</v>
       </c>
       <c r="AR13" t="n">
-        <v>-0.001429059946800529</v>
+        <v>-0.08876791596412659</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0.0002932756266546463</v>
+        <v>0.224977120757103</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0.001863886192564318</v>
+        <v>0.261923760175705</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.0003902449279750724</v>
+        <v>-0.2514935731887817</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.001272512550362632</v>
+        <v>0.3620445132255554</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.001918806241072867</v>
+        <v>0.2843128442764282</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.001340248954190005</v>
+        <v>-0.2134806364774704</v>
       </c>
       <c r="AY13" t="n">
         <v>1</v>
@@ -2547,309 +2547,309 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-0.00111475403545142</v>
+        <v>-0.2547828853130341</v>
       </c>
       <c r="B14" t="n">
-        <v>0.001741446763783939</v>
+        <v>-0.6066038012504578</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.0008637092367218451</v>
+        <v>0.07182101160287857</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0008847456382630988</v>
+        <v>-0.2177480906248093</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0004534505514887451</v>
+        <v>0.05669759586453438</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0004137682075433675</v>
+        <v>-0.2057691663503647</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.003110330815863577</v>
+        <v>-0.1627142280340195</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.001322672156151854</v>
+        <v>-0.06816729158163071</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.001925297903277594</v>
+        <v>-0.5165308713912964</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0009394906555400648</v>
+        <v>-0.0134208295494318</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.002163662943534451</v>
+        <v>-0.1042021885514259</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001713417360743555</v>
+        <v>-0.1455634832382202</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0001417930714683101</v>
+        <v>-0.1961170136928558</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0004134047443417985</v>
+        <v>0.3651078343391418</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0006550774402692888</v>
+        <v>0.07209537923336029</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.001399158230574462</v>
+        <v>0.1323836743831635</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.0006690552355013375</v>
+        <v>0.04543334990739822</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0005999523126075221</v>
+        <v>-0.4247362315654755</v>
       </c>
       <c r="S14" t="n">
-        <v>0.00272744859167422</v>
+        <v>-0.1552666276693344</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.001143459712558209</v>
+        <v>0.170393317937851</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.001628218198632808</v>
+        <v>0.04831976071000099</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.0002071076213187235</v>
+        <v>-0.3902647495269775</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.001991727668393258</v>
+        <v>-0.2542801797389984</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.0001188494181211848</v>
+        <v>0.1195204257965088</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0001541334515511117</v>
+        <v>0.4191282093524933</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.001958890830784927</v>
+        <v>0.1939878761768341</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.000790079373692799</v>
+        <v>-0.09618275612592697</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.0008736974252295344</v>
+        <v>-0.09833892434835434</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.002703641169601503</v>
+        <v>0.06215251982212067</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0007304082608035245</v>
+        <v>-0.1262590885162354</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.0007372786516167876</v>
+        <v>0.03389152884483337</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0004361738620756376</v>
+        <v>-0.04714059084653854</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.004498614549331654</v>
+        <v>-0.2701911926269531</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.00127138050512559</v>
+        <v>-0.2043799608945847</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0009819301802467828</v>
+        <v>-0.1428331732749939</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.003131804835119269</v>
+        <v>0.09637120366096497</v>
       </c>
       <c r="AK14" t="n">
-        <v>-0.0004483784376079081</v>
+        <v>-0.06292053312063217</v>
       </c>
       <c r="AL14" t="n">
-        <v>7.226622667118486e-05</v>
+        <v>-0.7402031421661377</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0002981966655360587</v>
+        <v>-0.3222865164279938</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0006711314179601509</v>
+        <v>0.1799633204936981</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.002506528837752156</v>
+        <v>0.1333829760551453</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0.0001395577886049688</v>
+        <v>0.0003438584681134671</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0.000305764280393569</v>
+        <v>-0.01962794549763203</v>
       </c>
       <c r="AR14" t="n">
-        <v>-0.001040602795441199</v>
+        <v>-0.1266440004110336</v>
       </c>
       <c r="AS14" t="n">
-        <v>-4.375812225558344e-05</v>
+        <v>0.1808559596538544</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0.001632860288120004</v>
+        <v>0.2619926631450653</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.0006329326892681928</v>
+        <v>-0.1513707339763641</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.001685883302008789</v>
+        <v>0.3715340793132782</v>
       </c>
       <c r="AW14" t="n">
-        <v>-0.0003074947950867703</v>
+        <v>0.3724202513694763</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.0004395344015689081</v>
+        <v>-0.2288597375154495</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0.00118748141930036</v>
+        <v>-0.5321901440620422</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0007672456589633751</v>
+        <v>-0.7698443531990051</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.001755659758553549</v>
+        <v>0.3354141712188721</v>
       </c>
       <c r="D15" t="n">
-        <v>0.002105245476885931</v>
+        <v>-0.1908564567565918</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0006536961905457528</v>
+        <v>0.1618697792291641</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.001193657873338675</v>
+        <v>-0.4702095985412598</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.002063490840059514</v>
+        <v>-0.1638767868280411</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.001629466340343542</v>
+        <v>-0.1418881714344025</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.002047313621706112</v>
+        <v>-0.4460492432117462</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0005518146160550122</v>
+        <v>0.01078507862985134</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0002145526928819255</v>
+        <v>0.245273545384407</v>
       </c>
       <c r="L15" t="n">
-        <v>0.001079025287735095</v>
+        <v>-0.1271140575408936</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0001569581732218779</v>
+        <v>-0.2749888300895691</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0003001109465595083</v>
+        <v>0.2682514488697052</v>
       </c>
       <c r="O15" t="n">
-        <v>3.101138995717789e-05</v>
+        <v>0.4310911595821381</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0004025161768041764</v>
+        <v>0.02270253375172615</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.001172040528999882</v>
+        <v>0.02513799630105495</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.0005645221674412385</v>
+        <v>-0.6976146697998047</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0009342855364358524</v>
+        <v>0.03168747946619987</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0004102586018476258</v>
+        <v>0.3089123070240021</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.003890447008528131</v>
+        <v>0.2409220039844513</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.0004646591067883728</v>
+        <v>-0.5515319108963013</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.0001164582702280735</v>
+        <v>-0.3766395151615143</v>
       </c>
       <c r="X15" t="n">
-        <v>0.00203573163951808</v>
+        <v>0.273463636636734</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.001355894399354805</v>
+        <v>0.429436057806015</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.0008791145207795779</v>
+        <v>-0.1847981363534927</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.499536253768521e-05</v>
+        <v>0.1483597755432129</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.001424855482324231</v>
+        <v>-0.2548723816871643</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.001196232874811704</v>
+        <v>0.2936737239360809</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.0001490473643171507</v>
+        <v>-0.23673115670681</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.0006018476807983509</v>
+        <v>-0.1540604829788208</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.001374297903251992</v>
+        <v>-0.342015266418457</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.001504941775197386</v>
+        <v>-0.5286678075790405</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0.0004216168952516221</v>
+        <v>-0.2902235686779022</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.002334046515667433</v>
+        <v>-0.238229364156723</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.002578043615070221</v>
+        <v>0.1521879285573959</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0.0002839611600634843</v>
+        <v>0.2230032086372375</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.0001366811093187987</v>
+        <v>-0.6557019948959351</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0.000727800135434591</v>
+        <v>-0.1223338171839714</v>
       </c>
       <c r="AN15" t="n">
-        <v>-1.535954707345865e-05</v>
+        <v>-0.1513804793357849</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.0009761134945271623</v>
+        <v>0.0933128297328949</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.000217496009720195</v>
+        <v>0.05911421403288841</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.001025780331666921</v>
+        <v>0.159361869096756</v>
       </c>
       <c r="AR15" t="n">
-        <v>-0.001997206004420332</v>
+        <v>0.02691600471735001</v>
       </c>
       <c r="AS15" t="n">
-        <v>-0.002153936550181403</v>
+        <v>0.1754450798034668</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.0001689134215428923</v>
+        <v>0.2875502407550812</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.000449426663464436</v>
+        <v>-0.3418180644512177</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.002679469726953238</v>
+        <v>0.4779697060585022</v>
       </c>
       <c r="AW15" t="n">
-        <v>-5.490128001076465e-05</v>
+        <v>-0.06491195410490036</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.001196788229525688</v>
+        <v>-0.1439388394355774</v>
       </c>
       <c r="AY15" t="n">
         <v>1</v>
@@ -2857,464 +2857,464 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.001445015756898307</v>
+        <v>-0.4325193166732788</v>
       </c>
       <c r="B16" t="n">
-        <v>0.002143820189388974</v>
+        <v>-0.7314843535423279</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.001569324209622522</v>
+        <v>0.3994533121585846</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0002104852509859663</v>
+        <v>-0.0606086254119873</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0005784484062654584</v>
+        <v>0.245400458574295</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0009275552128616258</v>
+        <v>-0.4495263993740082</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.002228586211971624</v>
+        <v>-0.1302728801965714</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0008173959444015932</v>
+        <v>-0.02374671772122383</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0003968631224656931</v>
+        <v>-0.5171656608581543</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0003530219346034816</v>
+        <v>-0.01661830209195614</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.001146899139310461</v>
+        <v>0.2569244205951691</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0004510982053852622</v>
+        <v>-0.06467969715595245</v>
       </c>
       <c r="M16" t="n">
-        <v>0.001209798829493413</v>
+        <v>-0.4332745373249054</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.000233084901751809</v>
+        <v>0.3344403207302094</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0009746567606930832</v>
+        <v>0.4225142896175385</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.0008095925754534751</v>
+        <v>0.007324031554162502</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.002420135302813008</v>
+        <v>0.06433704495429993</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0006647284008561389</v>
+        <v>-0.6669290065765381</v>
       </c>
       <c r="S16" t="n">
-        <v>0.001289618563187585</v>
+        <v>-0.0104838190600276</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0001418246179289282</v>
+        <v>0.2599375545978546</v>
       </c>
       <c r="U16" t="n">
-        <v>9.499496639750254e-05</v>
+        <v>0.2527923882007599</v>
       </c>
       <c r="V16" t="n">
-        <v>0.003089468082090898</v>
+        <v>-0.6605742573738098</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.002534751970026781</v>
+        <v>-0.3336359560489655</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0008454305119409714</v>
+        <v>0.3664111196994781</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.000544986796865299</v>
+        <v>0.4886379241943359</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.003218147049307968</v>
+        <v>-0.2935959696769714</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.002638011859074401</v>
+        <v>0.2247807830572128</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.0003381309859823559</v>
+        <v>-0.4028478562831879</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.0008497489683194549</v>
+        <v>0.2882621884346008</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.001107287629151632</v>
+        <v>-0.2050565034151077</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.0003979093092533033</v>
+        <v>-0.2304985821247101</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.0002343338103623285</v>
+        <v>-0.3212055861949921</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.001385042464207605</v>
+        <v>-0.6568717360496521</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0.0006065624784620501</v>
+        <v>-0.2344813793897629</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.0003297867545700593</v>
+        <v>-0.3291937112808228</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.0008530180620555481</v>
+        <v>0.1201283410191536</v>
       </c>
       <c r="AK16" t="n">
-        <v>-0.0005867839735940602</v>
+        <v>0.1707227230072021</v>
       </c>
       <c r="AL16" t="n">
-        <v>-0.000745171050790329</v>
+        <v>-0.7110710740089417</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0.0002129162457776427</v>
+        <v>-0.08155689388513565</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.0002824198055708164</v>
+        <v>-0.1778042167425156</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.0005860955887018737</v>
+        <v>0.09874475747346878</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.001211152135840434</v>
+        <v>0.04058185592293739</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-0.001220863308664712</v>
+        <v>0.1401349902153015</v>
       </c>
       <c r="AR16" t="n">
-        <v>-0.0005710980328875314</v>
+        <v>0.02423268556594849</v>
       </c>
       <c r="AS16" t="n">
-        <v>-0.000932943443415393</v>
+        <v>0.2177857011556625</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0.0002735770433007872</v>
+        <v>0.2829199433326721</v>
       </c>
       <c r="AU16" t="n">
-        <v>-0.0002420204070241359</v>
+        <v>-0.2581605017185211</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.001786266540890087</v>
+        <v>0.556733250617981</v>
       </c>
       <c r="AW16" t="n">
-        <v>-0.002742869143992777</v>
+        <v>-0.04102391004562378</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.001370565854859314</v>
+        <v>-0.1394631713628769</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.000273541014074666</v>
+        <v>-0.2475138008594513</v>
       </c>
       <c r="B17" t="n">
-        <v>0.003592500157944921</v>
+        <v>-0.5033755898475647</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.001567439196006076</v>
+        <v>0.03592019900679588</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0002706395622531508</v>
+        <v>-0.3572044372558594</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0009066028520563147</v>
+        <v>0.1747307926416397</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0005387854769819033</v>
+        <v>-0.3871159553527832</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.001750270293172276</v>
+        <v>-0.2517033219337463</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.001797899478712319</v>
+        <v>-0.01464415993541479</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.00198021179641937</v>
+        <v>-0.534101128578186</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0009121504653646764</v>
+        <v>0.1172799468040466</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.000799499586178575</v>
+        <v>0.0512021966278553</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.00046575860360099</v>
+        <v>-0.0604536309838295</v>
       </c>
       <c r="M17" t="n">
-        <v>0.001750517639361693</v>
+        <v>-0.2775986790657043</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0004774594409200565</v>
+        <v>0.3193204700946808</v>
       </c>
       <c r="O17" t="n">
-        <v>0.002028073342637687</v>
+        <v>0.1872263103723526</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0006650507668127043</v>
+        <v>0.02199131064116955</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.001269329308562577</v>
+        <v>0.01393399853259325</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.0007689909628856714</v>
+        <v>-0.6138084530830383</v>
       </c>
       <c r="S17" t="n">
-        <v>0.002292485957115212</v>
+        <v>-0.0243950430303812</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0002766598938104959</v>
+        <v>0.1612604707479477</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.001518900307689326</v>
+        <v>0.2534134685993195</v>
       </c>
       <c r="V17" t="n">
-        <v>0.001663864795717043</v>
+        <v>-0.2882253229618073</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.001100344190592533</v>
+        <v>-0.2969545125961304</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.214541910682537e-05</v>
+        <v>0.1159782260656357</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.0004490417966728211</v>
+        <v>0.4903362691402435</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.002836251454855391</v>
+        <v>0.1097507178783417</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.001339685927294909</v>
+        <v>0.02825292199850082</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.0003659797233392811</v>
+        <v>-0.06645920872688293</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.0004899499421989362</v>
+        <v>0.1150650009512901</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.0002532238070988179</v>
+        <v>-0.2908926904201508</v>
       </c>
       <c r="AE17" t="n">
-        <v>-0.0005193447656959839</v>
+        <v>0.04005397111177444</v>
       </c>
       <c r="AF17" t="n">
-        <v>-7.962745725768666e-05</v>
+        <v>-0.09726455062627792</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.001018667396739833</v>
+        <v>-0.3435677587985992</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.0009531685937264211</v>
+        <v>-0.1909526437520981</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0.001033532535629754</v>
+        <v>-0.08186401426792145</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.00197431064312303</v>
+        <v>0.01443094108253717</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.0002652024704432334</v>
+        <v>-0.01627375744283199</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.001595028242321596</v>
+        <v>-0.7212452292442322</v>
       </c>
       <c r="AM17" t="n">
-        <v>-5.124727157934878e-05</v>
+        <v>-0.2610554993152618</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.11088502635575e-05</v>
+        <v>0.1884196698665619</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.0001386286571411513</v>
+        <v>0.1330987960100174</v>
       </c>
       <c r="AP17" t="n">
-        <v>-0.0006846089517185513</v>
+        <v>0.04411675781011581</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.001657175047384553</v>
+        <v>0.227220356464386</v>
       </c>
       <c r="AR17" t="n">
-        <v>-0.0005820154716753473</v>
+        <v>-0.003119871951639652</v>
       </c>
       <c r="AS17" t="n">
-        <v>-0.0006280131605287154</v>
+        <v>0.1487824469804764</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.001031386440173531</v>
+        <v>0.09950406849384308</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.0008035000339529593</v>
+        <v>-0.1259386986494064</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.001588049545742727</v>
+        <v>0.4077855348587036</v>
       </c>
       <c r="AW17" t="n">
-        <v>-0.0006461606974054499</v>
+        <v>0.2564958333969116</v>
       </c>
       <c r="AX17" t="n">
-        <v>-3.034547319448473e-05</v>
+        <v>-0.233748123049736</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-0.0009960520811906192</v>
+        <v>-0.4989888072013855</v>
       </c>
       <c r="B18" t="n">
-        <v>0.002893079824879001</v>
+        <v>-0.724574089050293</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.002119681904633025</v>
+        <v>0.3570743203163147</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0001482984064473743</v>
+        <v>-0.156210795044899</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0006698013041355318</v>
+        <v>0.1960915774106979</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0008590457091168799</v>
+        <v>-0.4394429624080658</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.002537200917703591</v>
+        <v>-0.1430689841508865</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.00178513862536539</v>
+        <v>-0.07446428388357162</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.001461537950100341</v>
+        <v>-0.4554681777954102</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0008554817264264761</v>
+        <v>-0.01614984124898911</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0007375867369412634</v>
+        <v>0.2066527903079987</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0004777147805439666</v>
+        <v>-0.1116250231862068</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.001069194625438245</v>
+        <v>-0.2904110252857208</v>
       </c>
       <c r="N18" t="n">
-        <v>0.000715191452768618</v>
+        <v>0.2731943130493164</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0005504223771464057</v>
+        <v>0.425447553396225</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.0004006798182424716</v>
+        <v>0.05703706666827202</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.0007669383421200074</v>
+        <v>0.02528475970029831</v>
       </c>
       <c r="R18" t="n">
-        <v>0.0001299759427467087</v>
+        <v>-0.6553663611412048</v>
       </c>
       <c r="S18" t="n">
-        <v>0.001714806774522498</v>
+        <v>0.03938329219818115</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0009095567219503857</v>
+        <v>0.2769514322280884</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.001640071191887694</v>
+        <v>0.186641052365303</v>
       </c>
       <c r="V18" t="n">
-        <v>0.0005297843137662745</v>
+        <v>-0.5935114026069641</v>
       </c>
       <c r="W18" t="n">
-        <v>0.0007635929905812897</v>
+        <v>-0.353251039981842</v>
       </c>
       <c r="X18" t="n">
-        <v>0.001342879126318105</v>
+        <v>0.3005176186561584</v>
       </c>
       <c r="Y18" t="n">
-        <v>-9.936097725035397e-05</v>
+        <v>0.4043606519699097</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0.001648210493956458</v>
+        <v>-0.2080257385969162</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.001666231459656555</v>
+        <v>0.2012081146240234</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.384663324944895e-05</v>
+        <v>-0.238764762878418</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.0007349646989063816</v>
+        <v>0.2636377513408661</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.0004586302982652995</v>
+        <v>-0.2339839935302734</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.0003686133373829087</v>
+        <v>-0.1681157648563385</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.0007864851720520202</v>
+        <v>-0.2992361485958099</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.002074151621566681</v>
+        <v>-0.56919264793396</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.002961596190759665</v>
+        <v>-0.2606218159198761</v>
       </c>
       <c r="AI18" t="n">
-        <v>-0.001680618851547066</v>
+        <v>-0.2256083488464355</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.001372817629040899</v>
+        <v>0.1086366176605225</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.0005001747917483257</v>
+        <v>0.2635564208030701</v>
       </c>
       <c r="AL18" t="n">
-        <v>-1.209705539684699e-05</v>
+        <v>-0.658062756061554</v>
       </c>
       <c r="AM18" t="n">
-        <v>-0.0002275062912067564</v>
+        <v>-0.1239065378904343</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.0002305503114723601</v>
+        <v>-0.1649033725261688</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.001608007581057672</v>
+        <v>0.09946919232606888</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.0009141201363223047</v>
+        <v>0.05482489988207817</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.001170821712494423</v>
+        <v>0.1280434429645538</v>
       </c>
       <c r="AR18" t="n">
-        <v>-0.001784527817111866</v>
+        <v>-0.002772798296064138</v>
       </c>
       <c r="AS18" t="n">
-        <v>-0.001144438812158477</v>
+        <v>0.1599367260932922</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.951195315892119e-05</v>
+        <v>0.2641191482543945</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.00140785271540377</v>
+        <v>-0.3572805225849152</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.002157126172046353</v>
+        <v>0.4899206161499023</v>
       </c>
       <c r="AW18" t="n">
-        <v>-0.001836951079306787</v>
+        <v>-0.05408130586147308</v>
       </c>
       <c r="AX18" t="n">
-        <v>-0.0005748930634064509</v>
+        <v>-0.1478240638971329</v>
       </c>
       <c r="AY18" t="n">
         <v>1</v>
@@ -3322,464 +3322,464 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.001300612544464345</v>
+        <v>-0.3867968320846558</v>
       </c>
       <c r="B19" t="n">
-        <v>0.001919089502459072</v>
+        <v>-0.7831184864044189</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0005704630852524854</v>
+        <v>0.106560193002224</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0002980146157323829</v>
+        <v>-0.3654052913188934</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0007990988198750378</v>
+        <v>0.2412389665842056</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0001457095228635596</v>
+        <v>-0.4532082378864288</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.000743498978452779</v>
+        <v>-0.2128506451845169</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0005950648489962414</v>
+        <v>-0.008726823143661022</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0007766531302089374</v>
+        <v>-0.436086505651474</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0002073235841064315</v>
+        <v>-0.07056265324354172</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0002846896198213999</v>
+        <v>0.1532637774944305</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0003161485444548464</v>
+        <v>-0.1872003674507141</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0009113040692971267</v>
+        <v>-0.2889281511306763</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.001675293642161689</v>
+        <v>0.1144340932369232</v>
       </c>
       <c r="O19" t="n">
-        <v>0.001486586693410277</v>
+        <v>0.3305055797100067</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.0004186000024524744</v>
+        <v>-0.0555441714823246</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.001139568844370916</v>
+        <v>0.09993012994527817</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.0006568866182442244</v>
+        <v>-0.5907788872718811</v>
       </c>
       <c r="S19" t="n">
-        <v>0.002653613810465966</v>
+        <v>-0.0455031655728817</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0001059641000011356</v>
+        <v>0.1144665405154228</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.001462785712476451</v>
+        <v>0.1316342949867249</v>
       </c>
       <c r="V19" t="n">
-        <v>-7.26130264893087e-05</v>
+        <v>-0.3676263391971588</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.0005406846914543943</v>
+        <v>-0.2986864745616913</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.001823352540216688</v>
+        <v>0.1100236028432846</v>
       </c>
       <c r="Y19" t="n">
-        <v>-7.940612356456024e-05</v>
+        <v>0.5132423639297485</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.001444795826624984</v>
+        <v>-0.07047697901725769</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.001842446717582983</v>
+        <v>0.1189303025603294</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.0003901425447724919</v>
+        <v>-0.1681385636329651</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.0006239356598231314</v>
+        <v>0.1490330100059509</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.0001011929655764433</v>
+        <v>-0.2184505313634872</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.00015665608616303</v>
+        <v>-0.05127254500985146</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.00127708347713114</v>
+        <v>-0.3463945984840393</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.002610768130747843</v>
+        <v>-0.4594290256500244</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0.001172933450809568</v>
+        <v>-0.3492178320884705</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.0005010083734478888</v>
+        <v>-0.1303483545780182</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-0.0007477794795316836</v>
+        <v>0.1398632675409317</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.0002071182522991507</v>
+        <v>0.02763272449374199</v>
       </c>
       <c r="AL19" t="n">
-        <v>-0.0005876267948204155</v>
+        <v>-0.8301291465759277</v>
       </c>
       <c r="AM19" t="n">
-        <v>-0.000152061193941934</v>
+        <v>-0.1847829073667526</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.000683427321540647</v>
+        <v>0.06651061028242111</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.0003385774408648939</v>
+        <v>0.2356545180082321</v>
       </c>
       <c r="AP19" t="n">
-        <v>6.003340258419385e-05</v>
+        <v>0.007068292237818241</v>
       </c>
       <c r="AQ19" t="n">
-        <v>-0.0002769497575195137</v>
+        <v>0.0682908296585083</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.0003016886934928718</v>
+        <v>0.1218282878398895</v>
       </c>
       <c r="AS19" t="n">
-        <v>-0.0002318078556012776</v>
+        <v>0.01061640866100788</v>
       </c>
       <c r="AT19" t="n">
-        <v>9.155510686329328e-06</v>
+        <v>0.1809522360563278</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.00053293426966985</v>
+        <v>-0.2047027349472046</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.0002050237548694922</v>
+        <v>0.6114102005958557</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.0004776809886179536</v>
+        <v>0.2050102800130844</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.00058291243210932</v>
+        <v>0.01385866571217775</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.001224748984452711</v>
+        <v>-0.4610674679279327</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0009847468190049369</v>
+        <v>-0.8961787819862366</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.001045775451789089</v>
+        <v>0.06583016365766525</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0007468241083087618</v>
+        <v>-0.4251188635826111</v>
       </c>
       <c r="E20" t="n">
-        <v>7.218321678958448e-05</v>
+        <v>0.2716987729072571</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.000552187241070664</v>
+        <v>-0.4837760031223297</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0006406534218422178</v>
+        <v>-0.1074667349457741</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.00116043863872255</v>
+        <v>0.09808400273323059</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.001162701904867254</v>
+        <v>-0.3225676715373993</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0002289794394379792</v>
+        <v>-0.09867651015520096</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.002210762917672948</v>
+        <v>0.1774968057870865</v>
       </c>
       <c r="L20" t="n">
-        <v>-8.722185340679114e-05</v>
+        <v>-0.2396932989358902</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0006157190483320188</v>
+        <v>-0.3964356184005737</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0003198874858156748</v>
+        <v>0.03677824512124062</v>
       </c>
       <c r="O20" t="n">
-        <v>-4.474711852674837e-05</v>
+        <v>0.2637102901935577</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.001370809339189112</v>
+        <v>-7.319152064155787e-05</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.001547197045928633</v>
+        <v>0.1994747668504715</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.0003899040213157328</v>
+        <v>-0.6857191324234009</v>
       </c>
       <c r="S20" t="n">
-        <v>0.001599698683100242</v>
+        <v>-0.10183235257864</v>
       </c>
       <c r="T20" t="n">
-        <v>9.411685338572051e-05</v>
+        <v>0.1111996993422508</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.001267612837685322</v>
+        <v>0.08214154094457626</v>
       </c>
       <c r="V20" t="n">
-        <v>0.002443121155528712</v>
+        <v>-0.3572133779525757</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.0003414434404177329</v>
+        <v>-0.2600347101688385</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0004166933323643465</v>
+        <v>0.09379356354475021</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.001514594999288458</v>
+        <v>0.5376084446907043</v>
       </c>
       <c r="Z20" t="n">
-        <v>-0.00188260631868212</v>
+        <v>-0.2137269079685211</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.001578896046772797</v>
+        <v>0.1599085330963135</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.001364528740336298</v>
+        <v>-0.1985936760902405</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.001199224179798309</v>
+        <v>0.09490148723125458</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.001557802657226872</v>
+        <v>-0.262633353471756</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.0001865527621948721</v>
+        <v>-0.05605500191450119</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.001723394272626348</v>
+        <v>-0.4743688702583313</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.000838156446934429</v>
+        <v>-0.4386777579784393</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.0002028041142156359</v>
+        <v>-0.3531547486782074</v>
       </c>
       <c r="AI20" t="n">
-        <v>-0.0003959656699492102</v>
+        <v>-0.08831705898046494</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.000499696058543308</v>
+        <v>0.2132066935300827</v>
       </c>
       <c r="AK20" t="n">
-        <v>-0.0006748255140616138</v>
+        <v>0.003600982716307044</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.0005986198541941087</v>
+        <v>-0.8477981686592102</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.0002632932718638229</v>
+        <v>-0.1601255536079407</v>
       </c>
       <c r="AN20" t="n">
-        <v>-0.0001666693807216127</v>
+        <v>0.02257637865841389</v>
       </c>
       <c r="AO20" t="n">
-        <v>-0.001599433268450467</v>
+        <v>0.2553922235965729</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.0003103489953109084</v>
+        <v>0.07587063312530518</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9.480286554032618e-05</v>
+        <v>0.2059106677770615</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.104559538408266e-05</v>
+        <v>0.0941949188709259</v>
       </c>
       <c r="AS20" t="n">
-        <v>-0.0004909993748160628</v>
+        <v>-0.04815738648176193</v>
       </c>
       <c r="AT20" t="n">
-        <v>-0.0004760396246155064</v>
+        <v>0.1539153903722763</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.001049577753695414</v>
+        <v>-0.2476865947246552</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.0001788891100260576</v>
+        <v>0.6698542833328247</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.0003699013705314864</v>
+        <v>0.1919935792684555</v>
       </c>
       <c r="AX20" t="n">
-        <v>-0.0007522586082253742</v>
+        <v>0.04470450058579445</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.0001982962962606158</v>
+        <v>-0.3612963855266571</v>
       </c>
       <c r="B21" t="n">
-        <v>0.002242876306055033</v>
+        <v>-0.9372209906578064</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.002470654899888163</v>
+        <v>0.1216894313693047</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0002295358977431363</v>
+        <v>-0.3922127783298492</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0004968029398337956</v>
+        <v>0.2607589960098267</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.001924316204086116</v>
+        <v>-0.5063797831535339</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0009966683209567827</v>
+        <v>-0.09696543961763382</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.001818328420169626</v>
+        <v>0.09300334751605988</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.002398125425576702</v>
+        <v>-0.3860394060611725</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.153031247437426e-05</v>
+        <v>-0.08172576129436493</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0004312776555051609</v>
+        <v>0.2504144608974457</v>
       </c>
       <c r="L21" t="n">
-        <v>0.001630168766768637</v>
+        <v>-0.2058982253074646</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.001576910935896255</v>
+        <v>-0.4544918537139893</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.001033718483294243</v>
+        <v>0.08224765211343765</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0001216460030095719</v>
+        <v>0.2738466560840607</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.00170101251475501</v>
+        <v>-0.06963430345058441</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.0007271673958782679</v>
+        <v>0.2132366001605988</v>
       </c>
       <c r="R21" t="n">
-        <v>0.0002912392912240352</v>
+        <v>-0.6511077880859375</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0004132379823705394</v>
+        <v>-0.1200313717126846</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0008230034670329804</v>
+        <v>0.1525163203477859</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.002016298462406508</v>
+        <v>0.1286522746086121</v>
       </c>
       <c r="V21" t="n">
-        <v>0.0007239215265155346</v>
+        <v>-0.4123506546020508</v>
       </c>
       <c r="W21" t="n">
-        <v>0.0007780715469405694</v>
+        <v>-0.2719243466854095</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.0008988561673820575</v>
+        <v>0.08914964646100998</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.001482526067853694</v>
+        <v>0.5314080119132996</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.001105372198315451</v>
+        <v>-0.2223209142684937</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.0006109362170490397</v>
+        <v>0.09750159084796906</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0.001953283945586767</v>
+        <v>-0.2958405315876007</v>
       </c>
       <c r="AC21" t="n">
-        <v>-0.0001396585734316607</v>
+        <v>0.165405735373497</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.0001844546549412737</v>
+        <v>-0.2234370559453964</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.0001154449171119268</v>
+        <v>-0.08685882389545441</v>
       </c>
       <c r="AF21" t="n">
-        <v>-8.075235054848977e-05</v>
+        <v>-0.4372792840003967</v>
       </c>
       <c r="AG21" t="n">
-        <v>-0.002085594470669127</v>
+        <v>-0.5111992359161377</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.001371391458759692</v>
+        <v>-0.3703950643539429</v>
       </c>
       <c r="AI21" t="n">
-        <v>-0.0006511223709078392</v>
+        <v>-0.1188627183437347</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.001859771343087657</v>
+        <v>0.2123268693685532</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.000703625144231633</v>
+        <v>-0.01815349049866199</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.001183266315500854</v>
+        <v>-0.8706467747688293</v>
       </c>
       <c r="AM21" t="n">
-        <v>-0.0003950251742011582</v>
+        <v>-0.1666726917028427</v>
       </c>
       <c r="AN21" t="n">
-        <v>-0.002503409904642007</v>
+        <v>-0.02999862469732761</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.0005524976727315584</v>
+        <v>0.3015572130680084</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.0007652505770243221</v>
+        <v>0.0446903295814991</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.0009134929724436716</v>
+        <v>0.1354841142892838</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.0001788550911831077</v>
+        <v>0.1274487674236298</v>
       </c>
       <c r="AS21" t="n">
-        <v>-0.0005591369729098622</v>
+        <v>-0.04994235932826996</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.000231990734586058</v>
+        <v>0.1181152537465096</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.001183075297464318</v>
+        <v>-0.2068630307912827</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.002719080824481257</v>
+        <v>0.6715161800384521</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.001640707021991968</v>
+        <v>0.2191936671733856</v>
       </c>
       <c r="AX21" t="n">
-        <v>-0.002293656346694953</v>
+        <v>0.05425206944346428</v>
       </c>
       <c r="AY21" t="n">
         <v>1</v>
@@ -3787,154 +3787,154 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-0.0006050431555509434</v>
+        <v>-0.3385410606861115</v>
       </c>
       <c r="B22" t="n">
-        <v>0.003840539220687291</v>
+        <v>-0.4996834993362427</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.002986360643999704</v>
+        <v>-0.003127646166831255</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0001478362886988627</v>
+        <v>-0.2599624693393707</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0002815999180704334</v>
+        <v>0.1267049759626389</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.001802316160624066</v>
+        <v>-0.2567289173603058</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0008064560680757196</v>
+        <v>-0.2636237740516663</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0005699892328085766</v>
+        <v>-0.01631292700767517</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.001833738693515187</v>
+        <v>-0.4837058782577515</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0007223680615245549</v>
+        <v>0.04444126784801483</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.001912759179869643</v>
+        <v>-0.1982197761535645</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.001288093442994302</v>
+        <v>-0.1207029074430466</v>
       </c>
       <c r="M22" t="n">
-        <v>0.001767244583369949</v>
+        <v>0.03406167775392532</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0001045321477154242</v>
+        <v>0.4401199221611023</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.001217629092766454</v>
+        <v>0.1480213552713394</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.00182264326093319</v>
+        <v>0.1173119023442268</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.002755109161949856</v>
+        <v>0.1271793991327286</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.001136693703023848</v>
+        <v>-0.5985086560249329</v>
       </c>
       <c r="S22" t="n">
-        <v>0.002296780031711842</v>
+        <v>-0.1367150247097015</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.001591343492936213</v>
+        <v>0.1423139572143555</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.001803149249261417</v>
+        <v>0.06654992699623108</v>
       </c>
       <c r="V22" t="n">
-        <v>0.0004763488888050266</v>
+        <v>-0.1561279445886612</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.0003956947587167997</v>
+        <v>-0.2723898887634277</v>
       </c>
       <c r="X22" t="n">
-        <v>0.001033223070763833</v>
+        <v>0.1470099091529846</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.001235044883433018</v>
+        <v>0.5949972867965698</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.002656419399644795</v>
+        <v>0.06292214244604111</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.0004480036983887578</v>
+        <v>-0.05534977465867996</v>
       </c>
       <c r="AB22" t="n">
-        <v>-0.0005042629876329113</v>
+        <v>0.1366613209247589</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.001625737725441173</v>
+        <v>-0.09140238910913467</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.0006725525121265068</v>
+        <v>-0.266657680273056</v>
       </c>
       <c r="AE22" t="n">
-        <v>-0.0008573384971489093</v>
+        <v>0.06129347532987595</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.003237718056586738</v>
+        <v>-0.01413971744477749</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.002068993448782067</v>
+        <v>-0.1648420542478561</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.003451705953752205</v>
+        <v>-0.2208179533481598</v>
       </c>
       <c r="AI22" t="n">
-        <v>-0.0008373230787499294</v>
+        <v>-0.1318032294511795</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.002095827676702615</v>
+        <v>0.09353777021169662</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.001842620866009883</v>
+        <v>-0.03535233810544014</v>
       </c>
       <c r="AL22" t="n">
-        <v>-0.0004767743241083654</v>
+        <v>-0.655457079410553</v>
       </c>
       <c r="AM22" t="n">
-        <v>-0.0004300351610836065</v>
+        <v>-0.1809704154729843</v>
       </c>
       <c r="AN22" t="n">
-        <v>0.000603084690169374</v>
+        <v>0.22132308781147</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.001186143594266415</v>
+        <v>-0.0799419954419136</v>
       </c>
       <c r="AP22" t="n">
-        <v>-0.001711352597844737</v>
+        <v>0.09347193688154221</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.002669965393849626</v>
+        <v>0.1565108895301819</v>
       </c>
       <c r="AR22" t="n">
-        <v>-0.002154807442873363</v>
+        <v>-0.1659745126962662</v>
       </c>
       <c r="AS22" t="n">
-        <v>-0.001276104707966681</v>
+        <v>0.2944608628749847</v>
       </c>
       <c r="AT22" t="n">
-        <v>-0.001472545494392588</v>
+        <v>0.3194743394851685</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.0006894749739862811</v>
+        <v>-0.21778205037117</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.0006638140063527863</v>
+        <v>0.4099045097827911</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.0004925990180854521</v>
+        <v>0.232814684510231</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.001137129217171262</v>
+        <v>-0.3315820395946503</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
@@ -3942,1084 +3942,1084 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.001436800952187578</v>
+        <v>-0.267082005739212</v>
       </c>
       <c r="B23" t="n">
-        <v>0.002327828212960005</v>
+        <v>-0.5296873450279236</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.001808672856486965</v>
+        <v>0.02500716410577297</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0005067102698413873</v>
+        <v>-0.2201178967952728</v>
       </c>
       <c r="E23" t="n">
-        <v>9.924704885060013e-05</v>
+        <v>0.09362060576677322</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.002551591597429259</v>
+        <v>-0.1970401704311371</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.873343676693073e-05</v>
+        <v>-0.1869913339614868</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0007444661654189734</v>
+        <v>0.006805824115872383</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.002251025327148349</v>
+        <v>-0.4242529273033142</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0002903673868742003</v>
+        <v>0.04936904087662697</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.002174995371297151</v>
+        <v>-0.1547785252332687</v>
       </c>
       <c r="L23" t="n">
-        <v>0.001443433345098215</v>
+        <v>-0.1152768805623055</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0009544899871323094</v>
+        <v>-0.07666333019733429</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.002900714404706811</v>
+        <v>0.4353578984737396</v>
       </c>
       <c r="O23" t="n">
-        <v>0.000295420823806557</v>
+        <v>0.07871786504983902</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.00117686306313071</v>
+        <v>0.1608445048332214</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.003167903551895823</v>
+        <v>0.1249516531825066</v>
       </c>
       <c r="R23" t="n">
-        <v>3.477346455105625e-05</v>
+        <v>-0.6200152635574341</v>
       </c>
       <c r="S23" t="n">
-        <v>0.003955979969932884</v>
+        <v>-0.1969414949417114</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0002345286026274314</v>
+        <v>0.1298616677522659</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.001385353538637783</v>
+        <v>0.07600489258766174</v>
       </c>
       <c r="V23" t="n">
-        <v>0.0004075316178085758</v>
+        <v>-0.220648854970932</v>
       </c>
       <c r="W23" t="n">
-        <v>0.0008183082939746091</v>
+        <v>-0.2595778405666351</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.0004999153855388447</v>
+        <v>0.1028428077697754</v>
       </c>
       <c r="Y23" t="n">
-        <v>-0.0004427160469686505</v>
+        <v>0.4956752359867096</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.0001750753636220836</v>
+        <v>0.02569985389709473</v>
       </c>
       <c r="AA23" t="n">
-        <v>-0.0007165608470985794</v>
+        <v>-0.2128159999847412</v>
       </c>
       <c r="AB23" t="n">
-        <v>-0.00311896922331049</v>
+        <v>0.02528741210699081</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.00167448880212949</v>
+        <v>-0.02783604525029659</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.0004966622895768367</v>
+        <v>-0.2507124841213226</v>
       </c>
       <c r="AE23" t="n">
-        <v>-0.0003280091068110956</v>
+        <v>-0.02944107353687286</v>
       </c>
       <c r="AF23" t="n">
-        <v>-0.0005373287965922712</v>
+        <v>-0.05305900424718857</v>
       </c>
       <c r="AG23" t="n">
-        <v>-0.0003468302512065102</v>
+        <v>-0.1276378929615021</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.003043386411620538</v>
+        <v>-0.2104126214981079</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.0001210567000318905</v>
+        <v>-0.1540760099887848</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.0009936159853024225</v>
+        <v>0.09077014774084091</v>
       </c>
       <c r="AK23" t="n">
-        <v>0.0001065325114861177</v>
+        <v>-0.1160665899515152</v>
       </c>
       <c r="AL23" t="n">
-        <v>-0.001365908468528715</v>
+        <v>-0.6674036979675293</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.001163469268978556</v>
+        <v>-0.2468334436416626</v>
       </c>
       <c r="AN23" t="n">
-        <v>-0.0005329311374532137</v>
+        <v>0.09492995589971542</v>
       </c>
       <c r="AO23" t="n">
-        <v>-0.0005982740425329397</v>
+        <v>-0.05097666755318642</v>
       </c>
       <c r="AP23" t="n">
-        <v>-0.0003821793930799747</v>
+        <v>0.1276648193597794</v>
       </c>
       <c r="AQ23" t="n">
-        <v>-0.001372974671515697</v>
+        <v>0.1174137219786644</v>
       </c>
       <c r="AR23" t="n">
-        <v>-0.0003243267367522018</v>
+        <v>-0.1733789294958115</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.0006495258055906177</v>
+        <v>0.260701060295105</v>
       </c>
       <c r="AT23" t="n">
-        <v>-0.001226618064503385</v>
+        <v>0.3933223485946655</v>
       </c>
       <c r="AU23" t="n">
-        <v>0.0005734403290361926</v>
+        <v>-0.3089819848537445</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.001068767206014609</v>
+        <v>0.3301823437213898</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.00152088500046775</v>
+        <v>0.2695384621620178</v>
       </c>
       <c r="AX23" t="n">
-        <v>-0.001809735825307633</v>
+        <v>-0.2118541151285172</v>
       </c>
       <c r="AY23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.0004044233845290717</v>
+        <v>-0.04936674237251282</v>
       </c>
       <c r="B24" t="n">
-        <v>0.001452725044841458</v>
+        <v>-0.6710317730903625</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.001241858866375606</v>
+        <v>0.2000088393688202</v>
       </c>
       <c r="D24" t="n">
-        <v>0.00139836541503306</v>
+        <v>-0.02128658257424831</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0008687146490512818</v>
+        <v>0.1206893399357796</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.001497264679612903</v>
+        <v>0.00840369425714016</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.001563808746778656</v>
+        <v>-0.1262428760528564</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.003195520354976346</v>
+        <v>-0.01418863888829947</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0006869706454795806</v>
+        <v>-0.6112223863601685</v>
       </c>
       <c r="J24" t="n">
-        <v>0.002133535718027796</v>
+        <v>0.1740689128637314</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.0004155957315115826</v>
+        <v>-0.1071518212556839</v>
       </c>
       <c r="L24" t="n">
-        <v>0.001197847192380185</v>
+        <v>-0.04964950680732727</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0001647709364025861</v>
+        <v>-0.3154691755771637</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.0001844813752665405</v>
+        <v>0.5022172331809998</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.0003504310353613699</v>
+        <v>-0.1731659471988678</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.001629282458020366</v>
+        <v>0.01977868191897869</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.001970601759072394</v>
+        <v>0.2810356616973877</v>
       </c>
       <c r="R24" t="n">
-        <v>0.001218607977018424</v>
+        <v>-0.3318230211734772</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0004823278682062262</v>
+        <v>-0.4654057919979095</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.001626019940652262</v>
+        <v>-0.1213575378060341</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.00157894834682357</v>
+        <v>0.06824611127376556</v>
       </c>
       <c r="V24" t="n">
-        <v>0.0002156151192946283</v>
+        <v>-0.1890594065189362</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.0008794991138008594</v>
+        <v>-0.3869051337242126</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.0002989080277509801</v>
+        <v>0.2532072365283966</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.0009146169147276117</v>
+        <v>0.4898762404918671</v>
       </c>
       <c r="Z24" t="n">
-        <v>-0.001601986717328903</v>
+        <v>0.2191199511289597</v>
       </c>
       <c r="AA24" t="n">
-        <v>-0.001628059629555152</v>
+        <v>-0.2954033017158508</v>
       </c>
       <c r="AB24" t="n">
-        <v>-0.002610363292271899</v>
+        <v>-0.1633576303720474</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.0003360905679777118</v>
+        <v>-0.04406379535794258</v>
       </c>
       <c r="AD24" t="n">
-        <v>-0.0007716357000653944</v>
+        <v>-0.06655139476060867</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.0002250458332063977</v>
+        <v>-0.1337798535823822</v>
       </c>
       <c r="AF24" t="n">
-        <v>-2.149421096621919e-05</v>
+        <v>-0.002530470490455627</v>
       </c>
       <c r="AG24" t="n">
-        <v>-0.004512876710009582</v>
+        <v>-0.1110002249479294</v>
       </c>
       <c r="AH24" t="n">
-        <v>-0.0006845780692217252</v>
+        <v>-0.4980013072490692</v>
       </c>
       <c r="AI24" t="n">
-        <v>-0.0001661813921535244</v>
+        <v>-0.2734351456165314</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.001532067809107389</v>
+        <v>0.05743840709328651</v>
       </c>
       <c r="AK24" t="n">
-        <v>-0.00117123093672105</v>
+        <v>-0.1055457442998886</v>
       </c>
       <c r="AL24" t="n">
-        <v>0.001308666550203238</v>
+        <v>-0.5002048015594482</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.000479110729838345</v>
+        <v>-0.3965529799461365</v>
       </c>
       <c r="AN24" t="n">
-        <v>6.720630496274331e-06</v>
+        <v>0.09993902593851089</v>
       </c>
       <c r="AO24" t="n">
-        <v>2.479689828165093e-05</v>
+        <v>0.08842927217483521</v>
       </c>
       <c r="AP24" t="n">
-        <v>-0.0003337168655005144</v>
+        <v>0.1439121812582016</v>
       </c>
       <c r="AQ24" t="n">
-        <v>-0.001018468171655144</v>
+        <v>0.3338808417320251</v>
       </c>
       <c r="AR24" t="n">
-        <v>-0.002107269432747329</v>
+        <v>-0.138912171125412</v>
       </c>
       <c r="AS24" t="n">
-        <v>-0.002494433836043792</v>
+        <v>0.3779410421848297</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.0008153789060222313</v>
+        <v>-0.004921112675219774</v>
       </c>
       <c r="AU24" t="n">
-        <v>-0.0005608338146372297</v>
+        <v>-0.4150891602039337</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.001368316275703342</v>
+        <v>0.03814980015158653</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.0003840158801601182</v>
+        <v>0.3590262234210968</v>
       </c>
       <c r="AX24" t="n">
-        <v>-0.001646411775898065</v>
+        <v>-0.2878860831260681</v>
       </c>
       <c r="AY24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-0.0002153560520937627</v>
+        <v>-0.391970694065094</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.0008232894142938381</v>
+        <v>-0.5977723598480225</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.00205308789401264</v>
+        <v>-0.07078070193529129</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.002169281812369107</v>
+        <v>-0.1344606429338455</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0006825903105141375</v>
+        <v>0.07704944163560867</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0002580119689373938</v>
+        <v>-0.03487662598490715</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002094653688843496</v>
+        <v>-0.3410482406616211</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.001742652186640468</v>
+        <v>0.1246640533208847</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.00685130781705969</v>
+        <v>-0.7617467641830444</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.001075846375224106</v>
+        <v>-0.07341723144054413</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.001288964017146547</v>
+        <v>-0.2275760024785995</v>
       </c>
       <c r="L25" t="n">
-        <v>0.001540613432341724</v>
+        <v>-0.07866667956113815</v>
       </c>
       <c r="M25" t="n">
-        <v>0.004352896473895413</v>
+        <v>-0.03823450952768326</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.002956805342417631</v>
+        <v>0.47630575299263</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.0004905185494217816</v>
+        <v>0.119773767888546</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.0007056683624560597</v>
+        <v>0.05941398441791534</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.001713252883735075</v>
+        <v>0.2415701150894165</v>
       </c>
       <c r="R25" t="n">
-        <v>0.001094199840221725</v>
+        <v>-0.5681542158126831</v>
       </c>
       <c r="S25" t="n">
-        <v>0.003484203733254309</v>
+        <v>-0.5085697770118713</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0007344544184812842</v>
+        <v>0.1508659422397614</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.001403026553863817</v>
+        <v>-0.1462471485137939</v>
       </c>
       <c r="V25" t="n">
-        <v>7.591326276843431e-05</v>
+        <v>-0.2764788866043091</v>
       </c>
       <c r="W25" t="n">
-        <v>0.002025506860563907</v>
+        <v>-0.03808166086673737</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.001203578331762274</v>
+        <v>0.1017851084470749</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.0007030311254260476</v>
+        <v>0.7726514339447021</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.0009954008445080295</v>
+        <v>-0.2721984386444092</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.0002867784962936038</v>
+        <v>-0.1226033493876457</v>
       </c>
       <c r="AB25" t="n">
-        <v>-6.160938750867047e-06</v>
+        <v>-0.07990779727697372</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.0002880457819312386</v>
+        <v>-0.09131275862455368</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.000705725539947411</v>
+        <v>-0.3413402736186981</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0.000387025680370577</v>
+        <v>-0.0251733586192131</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.0005652684906601053</v>
+        <v>-0.06164930388331413</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.003585626534318441</v>
+        <v>-0.3080572485923767</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.003649619700943398</v>
+        <v>-0.3364243805408478</v>
       </c>
       <c r="AI25" t="n">
-        <v>-0.001558710997352743</v>
+        <v>-0.0534418523311615</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.001444676272625387</v>
+        <v>0.2735827267169952</v>
       </c>
       <c r="AK25" t="n">
-        <v>0.001100417504189448</v>
+        <v>0.02581308223307133</v>
       </c>
       <c r="AL25" t="n">
-        <v>0.001561712588680893</v>
+        <v>-0.8007020354270935</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.002577204317754619</v>
+        <v>-0.04009274765849113</v>
       </c>
       <c r="AN25" t="n">
-        <v>0.003238987660715062</v>
+        <v>0.1424403190612793</v>
       </c>
       <c r="AO25" t="n">
-        <v>-0.002234353742168828</v>
+        <v>-0.08548267930746078</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.0002226713011918834</v>
+        <v>0.1619270145893097</v>
       </c>
       <c r="AQ25" t="n">
-        <v>-0.002386831790890586</v>
+        <v>0.2351751029491425</v>
       </c>
       <c r="AR25" t="n">
-        <v>-0.001227643059018024</v>
+        <v>-0.4136132895946503</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.001575999123532274</v>
+        <v>0.3962598741054535</v>
       </c>
       <c r="AT25" t="n">
-        <v>-0.001655424984267246</v>
+        <v>0.213274359703064</v>
       </c>
       <c r="AU25" t="n">
-        <v>0.001772969144525041</v>
+        <v>-0.01377827860414982</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.001677637190931787</v>
+        <v>0.4876838326454163</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.0004435697286268526</v>
+        <v>0.2323997765779495</v>
       </c>
       <c r="AX25" t="n">
-        <v>-0.003358884988051044</v>
+        <v>-0.4200984835624695</v>
       </c>
       <c r="AY25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-0.001343912778447115</v>
+        <v>-0.3510980606079102</v>
       </c>
       <c r="B26" t="n">
-        <v>0.002230260885617097</v>
+        <v>-0.4954645931720734</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.001568223099778492</v>
+        <v>0.02862528525292873</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0001795188520290812</v>
+        <v>-0.2379080355167389</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0003686410012292367</v>
+        <v>0.07773176580667496</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.001974831859023736</v>
+        <v>-0.2769072353839874</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.001195312199923668</v>
+        <v>-0.2624692022800446</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.001663959850617759</v>
+        <v>-0.003120865672826767</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.002524122505409274</v>
+        <v>-0.5567834377288818</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0012251623696915</v>
+        <v>-0.04091806337237358</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.0003979505123308969</v>
+        <v>-0.2631950974464417</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0006666117499422953</v>
+        <v>-0.07852966338396072</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0007684052579607159</v>
+        <v>-0.02104537934064865</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.0004494352719509296</v>
+        <v>0.4249224066734314</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.0003957593113348953</v>
+        <v>0.2039458751678467</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.001486333512809895</v>
+        <v>0.03055770508944988</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.002366960364605585</v>
+        <v>0.2035839259624481</v>
       </c>
       <c r="R26" t="n">
-        <v>0.0007552942103188698</v>
+        <v>-0.5761054754257202</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002134466522724347</v>
+        <v>-0.2100639790296555</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0005650428941480068</v>
+        <v>0.12094596773386</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.002002377488345285</v>
+        <v>0.08566523343324661</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.861161965304461e-05</v>
+        <v>-0.2530635595321655</v>
       </c>
       <c r="W26" t="n">
-        <v>0.0008853111263806438</v>
+        <v>-0.2087256759405136</v>
       </c>
       <c r="X26" t="n">
-        <v>0.0007272802470345614</v>
+        <v>0.09553318470716476</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.001201692516766649</v>
+        <v>0.6649089455604553</v>
       </c>
       <c r="Z26" t="n">
-        <v>-0.001444740963952979</v>
+        <v>-0.01076787989586592</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.0009950117094551865</v>
+        <v>-0.02542180754244328</v>
       </c>
       <c r="AB26" t="n">
-        <v>-0.002978363734488149</v>
+        <v>0.1365130096673965</v>
       </c>
       <c r="AC26" t="n">
-        <v>-0.0007092723794189171</v>
+        <v>-0.1106951981782913</v>
       </c>
       <c r="AD26" t="n">
-        <v>-0.0008574923804870603</v>
+        <v>-0.2132450044155121</v>
       </c>
       <c r="AE26" t="n">
-        <v>-0.0002563307129290665</v>
+        <v>0.05234352499246597</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.0004303076945429131</v>
+        <v>-0.08212464302778244</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.003310346055705898</v>
+        <v>-0.2069856077432632</v>
       </c>
       <c r="AH26" t="n">
-        <v>-0.001503928249493685</v>
+        <v>-0.3062448501586914</v>
       </c>
       <c r="AI26" t="n">
-        <v>-0.0005698258202427818</v>
+        <v>-0.09314931929111481</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.001280057491939439</v>
+        <v>0.1191659495234489</v>
       </c>
       <c r="AK26" t="n">
-        <v>-0.0006793395246510768</v>
+        <v>0.08070112764835358</v>
       </c>
       <c r="AL26" t="n">
-        <v>0.0008243575630983737</v>
+        <v>-0.6993788480758667</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.0008500444272926163</v>
+        <v>-0.1671895980834961</v>
       </c>
       <c r="AN26" t="n">
-        <v>-0.001040281019303857</v>
+        <v>0.1312292218208313</v>
       </c>
       <c r="AO26" t="n">
-        <v>-0.0004063948228608349</v>
+        <v>-0.1218713223934174</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.001487605335745355</v>
+        <v>0.1315594166517258</v>
       </c>
       <c r="AQ26" t="n">
-        <v>-9.962835023729705e-05</v>
+        <v>0.131293311715126</v>
       </c>
       <c r="AR26" t="n">
-        <v>-0.001142794946996754</v>
+        <v>-0.2464388459920883</v>
       </c>
       <c r="AS26" t="n">
-        <v>-0.001150116780796032</v>
+        <v>0.3429737985134125</v>
       </c>
       <c r="AT26" t="n">
-        <v>-0.0001141308664884181</v>
+        <v>0.2803975641727448</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.002092805554206861</v>
+        <v>-0.212358295917511</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.001760101706309141</v>
+        <v>0.4416374862194061</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.001359453948061955</v>
+        <v>0.2001136541366577</v>
       </c>
       <c r="AX26" t="n">
-        <v>-0.0004073922072858912</v>
+        <v>-0.3736947476863861</v>
       </c>
       <c r="AY26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-0.001739719997306889</v>
+        <v>-0.2437709867954254</v>
       </c>
       <c r="B27" t="n">
-        <v>0.0007418823760489405</v>
+        <v>-0.5407042503356934</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.001685818902222849</v>
+        <v>0.2035035640001297</v>
       </c>
       <c r="D27" t="n">
-        <v>2.88499363901841e-05</v>
+        <v>0.02210632339119911</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0003242978799932629</v>
+        <v>0.02876966260373592</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.004086551808543507</v>
+        <v>-0.2082221359014511</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0001210974989780866</v>
+        <v>0.135947197675705</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0001494720015162351</v>
+        <v>0.3833543658256531</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.001273484109806973</v>
+        <v>-0.7518293857574463</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.002742575254810953</v>
+        <v>-0.1176456362009048</v>
       </c>
       <c r="K27" t="n">
-        <v>0.002718385686424021</v>
+        <v>-0.2885052859783173</v>
       </c>
       <c r="L27" t="n">
-        <v>0.000798557925813927</v>
+        <v>-0.01191818248480558</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0008821023593649643</v>
+        <v>-0.3974389433860779</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.0007916772416085496</v>
+        <v>0.5442848801612854</v>
       </c>
       <c r="O27" t="n">
-        <v>0.001344884276828104</v>
+        <v>0.1907912641763687</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.0005507172780428338</v>
+        <v>0.2110827565193176</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.001080595985346385</v>
+        <v>0.3397346138954163</v>
       </c>
       <c r="R27" t="n">
-        <v>0.001708326399056057</v>
+        <v>-0.6143810153007507</v>
       </c>
       <c r="S27" t="n">
-        <v>0.002569271483323673</v>
+        <v>-0.3087485432624817</v>
       </c>
       <c r="T27" t="n">
-        <v>0.002400327389218359</v>
+        <v>-0.1361393183469772</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.0021316416130996</v>
+        <v>0.04975127428770065</v>
       </c>
       <c r="V27" t="n">
-        <v>0.002372694482526524</v>
+        <v>-0.6686561703681946</v>
       </c>
       <c r="W27" t="n">
-        <v>0.00170667935703944</v>
+        <v>-0.3670613765716553</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.0002485361643545504</v>
+        <v>0.3428469598293304</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.0004737983310957487</v>
+        <v>0.7208377122879028</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.001010836930018369</v>
+        <v>-0.09718070924282074</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.001578518492116548</v>
+        <v>-0.1843413561582565</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.001881117963552251</v>
+        <v>-0.5171297788619995</v>
       </c>
       <c r="AC27" t="n">
-        <v>-0.001013646121133765</v>
+        <v>-0.1708753556013107</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.001173164892814718</v>
+        <v>-0.2236355543136597</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.001287640396896108</v>
+        <v>-0.07683888822793961</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.0004723184896318181</v>
+        <v>-0.2319940328598022</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.002193971706494248</v>
+        <v>-0.2569887936115265</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.003179392034483953</v>
+        <v>-0.09137926250696182</v>
       </c>
       <c r="AI27" t="n">
-        <v>-0.0002933885602801913</v>
+        <v>-0.2165560275316238</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.001725512424144616</v>
+        <v>0.1510012894868851</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.0005763615409594583</v>
+        <v>-0.3015572130680084</v>
       </c>
       <c r="AL27" t="n">
-        <v>-0.001063372319581371</v>
+        <v>-0.9221499562263489</v>
       </c>
       <c r="AM27" t="n">
-        <v>-0.0003588039574944003</v>
+        <v>-0.2203744649887085</v>
       </c>
       <c r="AN27" t="n">
-        <v>-0.0006369757903233704</v>
+        <v>-0.3665894865989685</v>
       </c>
       <c r="AO27" t="n">
-        <v>0.0005689538293970533</v>
+        <v>0.2097559869289398</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.0006636626846807987</v>
+        <v>0.2096383422613144</v>
       </c>
       <c r="AQ27" t="n">
-        <v>-0.001395422895712862</v>
+        <v>0.02468932047486305</v>
       </c>
       <c r="AR27" t="n">
-        <v>-0.001231091375471748</v>
+        <v>-0.3875883519649506</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.001021504888970862</v>
+        <v>0.3374662399291992</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.0002783450437752621</v>
+        <v>0.04417189583182335</v>
       </c>
       <c r="AU27" t="n">
-        <v>0.001819482841653565</v>
+        <v>0.0947597473859787</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.001603679244431751</v>
+        <v>0.2542013823986053</v>
       </c>
       <c r="AW27" t="n">
-        <v>-0.0004959018930205475</v>
+        <v>0.5587210655212402</v>
       </c>
       <c r="AX27" t="n">
-        <v>-0.002641590890488621</v>
+        <v>-0.1421733051538467</v>
       </c>
       <c r="AY27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-0.004498326799723296</v>
+        <v>-0.295509546995163</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.0002533011005771062</v>
+        <v>-0.5445173978805542</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.002406626669972029</v>
+        <v>0.082383893430233</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.001337011759895347</v>
+        <v>-0.1789524257183075</v>
       </c>
       <c r="E28" t="n">
-        <v>0.001838210994214237</v>
+        <v>0.09836610406637192</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.002567308900647159</v>
+        <v>-0.1967998892068863</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0005815397676742859</v>
+        <v>-0.1993197649717331</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0001249793772095277</v>
+        <v>0.03360320627689362</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.002511228884758478</v>
+        <v>-0.4771147668361664</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.001431819980481768</v>
+        <v>0.0639406144618988</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0006307292200791322</v>
+        <v>-0.1325581520795822</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.000919230801957725</v>
+        <v>-0.07042437046766281</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.001647030240538522</v>
+        <v>-0.09994402527809143</v>
       </c>
       <c r="N28" t="n">
-        <v>0.0003798909815668057</v>
+        <v>0.4297729730606079</v>
       </c>
       <c r="O28" t="n">
-        <v>0.0002740738482457053</v>
+        <v>0.0766649916768074</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.0004349961168581559</v>
+        <v>0.1364618241786957</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.0001705447816967443</v>
+        <v>0.1583127379417419</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.002816481387650974</v>
+        <v>-0.5412799715995789</v>
       </c>
       <c r="S28" t="n">
-        <v>0.001812030362222907</v>
+        <v>-0.2711332440376282</v>
       </c>
       <c r="T28" t="n">
-        <v>0.001031069862951042</v>
+        <v>0.09354328364133835</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.001670103340136695</v>
+        <v>0.0651305690407753</v>
       </c>
       <c r="V28" t="n">
-        <v>0.003682377907873045</v>
+        <v>-0.2621066272258759</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.0008024516442465977</v>
+        <v>-0.29387566447258</v>
       </c>
       <c r="X28" t="n">
-        <v>-0.001316624998418492</v>
+        <v>0.09760574251413345</v>
       </c>
       <c r="Y28" t="n">
-        <v>-6.551848441184125e-05</v>
+        <v>0.5258830785751343</v>
       </c>
       <c r="Z28" t="n">
-        <v>-0.0001070746952310632</v>
+        <v>0.04067469388246536</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.000502046639242633</v>
+        <v>-0.0662781298160553</v>
       </c>
       <c r="AB28" t="n">
-        <v>-3.191371246012389e-05</v>
+        <v>0.02481075935065746</v>
       </c>
       <c r="AC28" t="n">
-        <v>-0.001412122549761303</v>
+        <v>0.003759089391678572</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.002383379420981527</v>
+        <v>-0.175236701965332</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.000828967887935192</v>
+        <v>-0.006930746138095856</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.00048350172908403</v>
+        <v>-0.03690135851502419</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.002012227353515794</v>
+        <v>-0.150145947933197</v>
       </c>
       <c r="AH28" t="n">
-        <v>-0.001368340133457526</v>
+        <v>-0.2869992256164551</v>
       </c>
       <c r="AI28" t="n">
-        <v>-0.002303981313740254</v>
+        <v>-0.1557068377733231</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-0.000513733729806882</v>
+        <v>0.09787217527627945</v>
       </c>
       <c r="AK28" t="n">
-        <v>0.0006857452458921208</v>
+        <v>-0.05147799849510193</v>
       </c>
       <c r="AL28" t="n">
-        <v>-0.0002894801566497649</v>
+        <v>-0.5963535308837891</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.001521989332147018</v>
+        <v>-0.2234586179256439</v>
       </c>
       <c r="AN28" t="n">
-        <v>-0.0008637828431580527</v>
+        <v>0.1260510385036469</v>
       </c>
       <c r="AO28" t="n">
-        <v>-0.0006628636151226501</v>
+        <v>-0.05557646602392197</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.004250680897415945</v>
+        <v>0.1785652637481689</v>
       </c>
       <c r="AQ28" t="n">
-        <v>-0.001201031570646357</v>
+        <v>0.2088589668273926</v>
       </c>
       <c r="AR28" t="n">
-        <v>-0.002537654354102266</v>
+        <v>-0.1891853958368301</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.003511242487068286</v>
+        <v>0.2876235842704773</v>
       </c>
       <c r="AT28" t="n">
-        <v>-0.003581838738729759</v>
+        <v>0.1938318014144897</v>
       </c>
       <c r="AU28" t="n">
-        <v>0.003496993758783425</v>
+        <v>-0.2801653742790222</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.0001418750510081731</v>
+        <v>0.287970632314682</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.001076745972486058</v>
+        <v>0.2825904190540314</v>
       </c>
       <c r="AX28" t="n">
-        <v>-0.003053782958668802</v>
+        <v>-0.2677344083786011</v>
       </c>
       <c r="AY28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.0006170980339247721</v>
+        <v>-0.3368038833141327</v>
       </c>
       <c r="B29" t="n">
-        <v>0.002346000263482748</v>
+        <v>-0.4591620266437531</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.001295092611976706</v>
+        <v>-0.01517118606716394</v>
       </c>
       <c r="D29" t="n">
-        <v>0.001784759287174371</v>
+        <v>-0.2694836258888245</v>
       </c>
       <c r="E29" t="n">
-        <v>0.001076682391941572</v>
+        <v>0.001143125118687749</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.000649148208566762</v>
+        <v>-0.3498294055461884</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.001345075884711953</v>
+        <v>-0.2438530921936035</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.00151997438260242</v>
+        <v>0.03997509554028511</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0008730929208305668</v>
+        <v>-0.5222368836402893</v>
       </c>
       <c r="J29" t="n">
-        <v>7.007147671382774e-05</v>
+        <v>0.0208334531635046</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.000828185116458556</v>
+        <v>-0.2779229581356049</v>
       </c>
       <c r="L29" t="n">
-        <v>0.001047410428156086</v>
+        <v>-0.1183900311589241</v>
       </c>
       <c r="M29" t="n">
-        <v>0.00122906022803144</v>
+        <v>0.0312843956053257</v>
       </c>
       <c r="N29" t="n">
-        <v>9.210459030600673e-06</v>
+        <v>0.4846958518028259</v>
       </c>
       <c r="O29" t="n">
-        <v>0.0007708872018204305</v>
+        <v>0.1754824668169022</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.001116493932520277</v>
+        <v>0.05378749221563339</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.001459618693323955</v>
+        <v>0.1523181051015854</v>
       </c>
       <c r="R29" t="n">
-        <v>0.0002249713272725155</v>
+        <v>-0.6417025327682495</v>
       </c>
       <c r="S29" t="n">
-        <v>0.001260747462024711</v>
+        <v>-0.1548382639884949</v>
       </c>
       <c r="T29" t="n">
-        <v>0.0003734037636522284</v>
+        <v>0.155961811542511</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.001172925294900644</v>
+        <v>0.1218288093805313</v>
       </c>
       <c r="V29" t="n">
-        <v>0.0009921074939893326</v>
+        <v>-0.1839580088853836</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.0018726889527096</v>
+        <v>-0.1823417097330093</v>
       </c>
       <c r="X29" t="n">
-        <v>0.0002433130051247638</v>
+        <v>0.1084411516785622</v>
       </c>
       <c r="Y29" t="n">
-        <v>-0.0004946806259064345</v>
+        <v>0.6364014744758606</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.002266106794599074</v>
+        <v>0.07542454451322556</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.002521374324407551</v>
+        <v>0.03238599002361298</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.0009197578088973625</v>
+        <v>0.1975035667419434</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.0008562576826662006</v>
+        <v>-0.1423897296190262</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.0004085129135142349</v>
+        <v>-0.2824976146221161</v>
       </c>
       <c r="AE29" t="n">
-        <v>-0.0008171586396780121</v>
+        <v>0.05977290123701096</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.0001656903174441315</v>
+        <v>-0.0675317719578743</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.0009847001061668455</v>
+        <v>-0.1649223417043686</v>
       </c>
       <c r="AH29" t="n">
-        <v>-0.0001170745277858319</v>
+        <v>-0.3099880814552307</v>
       </c>
       <c r="AI29" t="n">
-        <v>-0.0002371605201055471</v>
+        <v>-0.1034825295209885</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.001588299863582829</v>
+        <v>0.0803525522351265</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.000637657916657724</v>
+        <v>0.07782029360532761</v>
       </c>
       <c r="AL29" t="n">
-        <v>4.237410472461798e-05</v>
+        <v>-0.6854294538497925</v>
       </c>
       <c r="AM29" t="n">
-        <v>-0.001118988678422829</v>
+        <v>-0.1589806526899338</v>
       </c>
       <c r="AN29" t="n">
-        <v>0.0003049468129517027</v>
+        <v>0.137886255979538</v>
       </c>
       <c r="AO29" t="n">
-        <v>0.0007670704777421032</v>
+        <v>-0.163948580622673</v>
       </c>
       <c r="AP29" t="n">
-        <v>-0.0001035921299256301</v>
+        <v>0.1293198317289352</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.0005457371362846095</v>
+        <v>0.1172235980629921</v>
       </c>
       <c r="AR29" t="n">
-        <v>-0.001212904676955671</v>
+        <v>-0.2267193198204041</v>
       </c>
       <c r="AS29" t="n">
-        <v>-0.0007187074418785658</v>
+        <v>0.3373293280601501</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.001282542894670659</v>
+        <v>0.2883453369140625</v>
       </c>
       <c r="AU29" t="n">
-        <v>2.707032623286275e-05</v>
+        <v>-0.2156551480293274</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.002472206584254918</v>
+        <v>0.3899125456809998</v>
       </c>
       <c r="AW29" t="n">
-        <v>-0.00109525040978261</v>
+        <v>0.152479812502861</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.0004956835220040375</v>
+        <v>-0.390791267156601</v>
       </c>
       <c r="AY29" t="n">
         <v>0</v>
@@ -5027,309 +5027,309 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.0001128068935730705</v>
+        <v>-0.2544001042842865</v>
       </c>
       <c r="B30" t="n">
-        <v>0.001002302721432644</v>
+        <v>-0.5364010334014893</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.001147244510204234</v>
+        <v>-0.009678810834884644</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0008263754314122831</v>
+        <v>-0.2552158832550049</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0002951042458641831</v>
+        <v>0.03591815754771233</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0005481146182568779</v>
+        <v>-0.139263242483139</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.002101171790688082</v>
+        <v>-0.2183225601911545</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.001331860474012485</v>
+        <v>0.02755152992904186</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.001135979567816508</v>
+        <v>-0.4370448887348175</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.000592840465362847</v>
+        <v>0.04782230034470558</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.0004577179802065697</v>
+        <v>-0.1857647150754929</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0001310837479566993</v>
+        <v>-0.137920930981636</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0009708968050619131</v>
+        <v>-0.02994443848729134</v>
       </c>
       <c r="N30" t="n">
-        <v>-5.759354106939631e-05</v>
+        <v>0.3984327018260956</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.001315082846267597</v>
+        <v>0.02143481932580471</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.0007682972498291044</v>
+        <v>0.1667680293321609</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.0004448809522439378</v>
+        <v>0.1503743380308151</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.001329815792846818</v>
+        <v>-0.6435976028442383</v>
       </c>
       <c r="S30" t="n">
-        <v>0.001551915668209522</v>
+        <v>-0.1888643503189087</v>
       </c>
       <c r="T30" t="n">
-        <v>-6.500918923435411e-05</v>
+        <v>0.1908001005649567</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.00289276409302237</v>
+        <v>0.08243545144796371</v>
       </c>
       <c r="V30" t="n">
-        <v>-0.0001295237332136944</v>
+        <v>-0.2222974300384521</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.0007573009934070863</v>
+        <v>-0.1999359130859375</v>
       </c>
       <c r="X30" t="n">
-        <v>0.001305776374071721</v>
+        <v>0.130389392375946</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.0009821022130762005</v>
+        <v>0.5093063116073608</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.001544574235580586</v>
+        <v>0.06165532395243645</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.0007311775022674049</v>
+        <v>-0.1433292776346207</v>
       </c>
       <c r="AB30" t="n">
-        <v>-0.001357650838077353</v>
+        <v>0.000111280387500301</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.0005390572271017659</v>
+        <v>-0.06016863882541656</v>
       </c>
       <c r="AD30" t="n">
-        <v>-9.332130929181881e-05</v>
+        <v>-0.352295994758606</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.000651841105265889</v>
+        <v>-0.02965192310512066</v>
       </c>
       <c r="AF30" t="n">
-        <v>-0.0005576948672400319</v>
+        <v>0.00349548296071589</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.0006589249622495512</v>
+        <v>-0.1342828422784805</v>
       </c>
       <c r="AH30" t="n">
-        <v>-0.0007756822674150239</v>
+        <v>-0.2125719487667084</v>
       </c>
       <c r="AI30" t="n">
-        <v>-0.001977229756860606</v>
+        <v>-0.1292978823184967</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.001895964704833019</v>
+        <v>0.1109673380851746</v>
       </c>
       <c r="AK30" t="n">
-        <v>-0.000348547233134772</v>
+        <v>-0.1327672898769379</v>
       </c>
       <c r="AL30" t="n">
-        <v>-6.273060088278734e-05</v>
+        <v>-0.6860457062721252</v>
       </c>
       <c r="AM30" t="n">
-        <v>-0.0005653156657675883</v>
+        <v>-0.2042293697595596</v>
       </c>
       <c r="AN30" t="n">
-        <v>-7.797752271486804e-05</v>
+        <v>0.1877136379480362</v>
       </c>
       <c r="AO30" t="n">
-        <v>8.560806854253861e-05</v>
+        <v>-0.0004706860345322639</v>
       </c>
       <c r="AP30" t="n">
-        <v>-0.0005645206512440187</v>
+        <v>0.1078546643257141</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.0005656925439544479</v>
+        <v>0.08432508260011673</v>
       </c>
       <c r="AR30" t="n">
-        <v>-0.001128885815959158</v>
+        <v>-0.1625520288944244</v>
       </c>
       <c r="AS30" t="n">
-        <v>-0.001705511069947134</v>
+        <v>0.2840904891490936</v>
       </c>
       <c r="AT30" t="n">
-        <v>-0.0001845952337788527</v>
+        <v>0.3995945751667023</v>
       </c>
       <c r="AU30" t="n">
-        <v>7.32301500567045e-05</v>
+        <v>-0.3004270792007446</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.002386262694174576</v>
+        <v>0.3340096473693848</v>
       </c>
       <c r="AW30" t="n">
-        <v>-0.000628804541284671</v>
+        <v>0.2763828933238983</v>
       </c>
       <c r="AX30" t="n">
-        <v>-7.381786717087681e-05</v>
+        <v>-0.208742767572403</v>
       </c>
       <c r="AY30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-0.0006748769056420774</v>
+        <v>-0.2820712924003601</v>
       </c>
       <c r="B31" t="n">
-        <v>0.0008104458886058712</v>
+        <v>-0.5403656959533691</v>
       </c>
       <c r="C31" t="n">
-        <v>1.074104436250786e-05</v>
+        <v>0.02817724272608757</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0005935318819648256</v>
+        <v>-0.1271692216396332</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0010889032579202</v>
+        <v>0.1372807770967484</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0005417884392015583</v>
+        <v>-0.1929183304309845</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.001846659143267037</v>
+        <v>-0.263689249753952</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.0009981598021217267</v>
+        <v>-0.006190774030983448</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.001140957101526768</v>
+        <v>-0.5569882988929749</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.000299270990539962</v>
+        <v>0.07905469089746475</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.0002501672987475492</v>
+        <v>-0.1619345992803574</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0005673672193717641</v>
+        <v>-0.02453642152249813</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0007610374834936976</v>
+        <v>-0.139511913061142</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.0006320350943944091</v>
+        <v>0.5067102909088135</v>
       </c>
       <c r="O31" t="n">
-        <v>-0.0002238583490689591</v>
+        <v>0.1487134397029877</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.0003869755912729077</v>
+        <v>0.1563949435949326</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0006082326341249276</v>
+        <v>0.1083179414272308</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.0009548864679754241</v>
+        <v>-0.4811441898345947</v>
       </c>
       <c r="S31" t="n">
-        <v>0.002462934516520116</v>
+        <v>-0.2164649665355682</v>
       </c>
       <c r="T31" t="n">
-        <v>0.0006498793741089511</v>
+        <v>0.01382806245237589</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.0001152799919710743</v>
+        <v>0.08330308645963669</v>
       </c>
       <c r="V31" t="n">
-        <v>7.967363980878773e-05</v>
+        <v>-0.2489459067583084</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.001897534628515676</v>
+        <v>-0.259998619556427</v>
       </c>
       <c r="X31" t="n">
-        <v>-0.0001344465031982281</v>
+        <v>0.1672226935625076</v>
       </c>
       <c r="Y31" t="n">
-        <v>-0.0006486612162980293</v>
+        <v>0.5294957160949707</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.001019680402895293</v>
+        <v>0.05477802455425262</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.001881273097200413</v>
+        <v>-0.1392858922481537</v>
       </c>
       <c r="AB31" t="n">
-        <v>4.861121506207874e-05</v>
+        <v>0.06514950096607208</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.0003716347230277189</v>
+        <v>-0.03153597190976143</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.0006871410502703706</v>
+        <v>-0.2194433063268661</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.0001753867289870703</v>
+        <v>-0.02476072870194912</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.0007246770247704292</v>
+        <v>-0.0985102504491806</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.001455591862802221</v>
+        <v>-0.1993050873279572</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.0003443860353850056</v>
+        <v>-0.2160748243331909</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.0004977348989942157</v>
+        <v>-0.1996743083000183</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-0.0002881027273136297</v>
+        <v>0.09200087934732437</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.001571582403122035</v>
+        <v>-0.0818214938044548</v>
       </c>
       <c r="AL31" t="n">
-        <v>0.0002397321430218105</v>
+        <v>-0.6133798956871033</v>
       </c>
       <c r="AM31" t="n">
-        <v>-0.0005275785344412183</v>
+        <v>-0.2533270120620728</v>
       </c>
       <c r="AN31" t="n">
-        <v>-0.0001541943009965333</v>
+        <v>0.07744685560464859</v>
       </c>
       <c r="AO31" t="n">
-        <v>0.001808877930252637</v>
+        <v>-0.09012067317962646</v>
       </c>
       <c r="AP31" t="n">
-        <v>-0.0006624125037603826</v>
+        <v>0.1859003603458405</v>
       </c>
       <c r="AQ31" t="n">
-        <v>-0.0001309390127669318</v>
+        <v>0.267850935459137</v>
       </c>
       <c r="AR31" t="n">
-        <v>-0.000431540634677604</v>
+        <v>-0.2063415795564651</v>
       </c>
       <c r="AS31" t="n">
-        <v>-0.001373487593884169</v>
+        <v>0.2774916887283325</v>
       </c>
       <c r="AT31" t="n">
-        <v>-0.0003032345696649885</v>
+        <v>0.2980066537857056</v>
       </c>
       <c r="AU31" t="n">
-        <v>0.001780117898019047</v>
+        <v>-0.2489627301692963</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.0004059092641817628</v>
+        <v>0.3177759349346161</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.0001125084724208732</v>
+        <v>0.2310097515583038</v>
       </c>
       <c r="AX31" t="n">
-        <v>-0.0001389043018420062</v>
+        <v>-0.2906952500343323</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
@@ -5337,309 +5337,309 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-0.0004274221355605664</v>
+        <v>-0.2756674289703369</v>
       </c>
       <c r="B32" t="n">
-        <v>0.0001275069708427312</v>
+        <v>-0.5296071171760559</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001331614533631019</v>
+        <v>0.0197102315723896</v>
       </c>
       <c r="D32" t="n">
-        <v>5.61939987805893e-05</v>
+        <v>-0.296490490436554</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0008619188329800626</v>
+        <v>0.1126031950116158</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.001191383356982069</v>
+        <v>-0.1470761895179749</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.0005751726747546908</v>
+        <v>-0.2391299456357956</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0004884907642113442</v>
+        <v>0.00522942841053009</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.00054191003901107</v>
+        <v>-0.3770991563796997</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.0005419058353133483</v>
+        <v>0.07590923458337784</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0002393057983678421</v>
+        <v>-0.1641078442335129</v>
       </c>
       <c r="L32" t="n">
-        <v>0.001618592175611691</v>
+        <v>-0.1254385709762573</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0002678729706116793</v>
+        <v>0.01815841719508171</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.0003173895444910836</v>
+        <v>0.4076916575431824</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.0003413046710813192</v>
+        <v>0.0217705462127924</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.0002767520399803229</v>
+        <v>0.2370924055576324</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.0003259910494219825</v>
+        <v>0.1230079904198647</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.0003283742363219819</v>
+        <v>-0.6452858448028564</v>
       </c>
       <c r="S32" t="n">
-        <v>0.0008054330768131205</v>
+        <v>-0.195075586438179</v>
       </c>
       <c r="T32" t="n">
-        <v>0.0004754789655046961</v>
+        <v>0.1740953028202057</v>
       </c>
       <c r="U32" t="n">
-        <v>-0.000870632149358327</v>
+        <v>0.04773780331015587</v>
       </c>
       <c r="V32" t="n">
-        <v>-0.0002823218974776954</v>
+        <v>-0.211074635386467</v>
       </c>
       <c r="W32" t="n">
-        <v>0.001436481003538565</v>
+        <v>-0.2896923720836639</v>
       </c>
       <c r="X32" t="n">
-        <v>0.0002232753408151905</v>
+        <v>0.02688405476510525</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.000765420591606118</v>
+        <v>0.4794144332408905</v>
       </c>
       <c r="Z32" t="n">
-        <v>-0.0003226292233089129</v>
+        <v>0.1003019511699677</v>
       </c>
       <c r="AA32" t="n">
-        <v>-0.0006725477573706563</v>
+        <v>-0.1859513521194458</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0.001514332135747027</v>
+        <v>0.1164112165570259</v>
       </c>
       <c r="AC32" t="n">
-        <v>-9.710669904413158e-05</v>
+        <v>0.008350221440196037</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.001275459444973824</v>
+        <v>-0.272758424282074</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.0011637340586756</v>
+        <v>-0.04786698892712593</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.0004425841813608727</v>
+        <v>-0.008182738907635212</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.001700404806093582</v>
+        <v>-0.08557769656181335</v>
       </c>
       <c r="AH32" t="n">
-        <v>-0.0003024023242474966</v>
+        <v>-0.203723356127739</v>
       </c>
       <c r="AI32" t="n">
-        <v>-0.001192058841887399</v>
+        <v>-0.1608547121286392</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-2.953172474211922e-05</v>
+        <v>0.04683481156826019</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.00047186119554376</v>
+        <v>-0.09284819662570953</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.0008591407902959208</v>
+        <v>-0.6325212717056274</v>
       </c>
       <c r="AM32" t="n">
-        <v>-9.872740045395734e-06</v>
+        <v>-0.2678967714309692</v>
       </c>
       <c r="AN32" t="n">
-        <v>-1.677223804926483e-05</v>
+        <v>0.1808481067419052</v>
       </c>
       <c r="AO32" t="n">
-        <v>-0.0008122191914604638</v>
+        <v>-0.07806981354951859</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.00033280193894702</v>
+        <v>0.1652644574642181</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.0004527078878878986</v>
+        <v>0.1064582988619804</v>
       </c>
       <c r="AR32" t="n">
-        <v>-0.0008653793891750969</v>
+        <v>-0.1629941016435623</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.0001531525116622927</v>
+        <v>0.2270033359527588</v>
       </c>
       <c r="AT32" t="n">
-        <v>7.196444620491192e-05</v>
+        <v>0.4128548204898834</v>
       </c>
       <c r="AU32" t="n">
-        <v>0.0009129602551496303</v>
+        <v>-0.3311153948307037</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.0006693166255111617</v>
+        <v>0.2734715044498444</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.0006372188091937076</v>
+        <v>0.2933557033538818</v>
       </c>
       <c r="AX32" t="n">
-        <v>-0.001217768394262111</v>
+        <v>-0.1651518940925598</v>
       </c>
       <c r="AY32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-0.0004690709348915907</v>
+        <v>-0.397477000951767</v>
       </c>
       <c r="B33" t="n">
-        <v>0.00121981466741869</v>
+        <v>-0.4739836156368256</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.000575441923160842</v>
+        <v>0.07789052277803421</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0005835763276254655</v>
+        <v>-0.1283562183380127</v>
       </c>
       <c r="E33" t="n">
-        <v>0.00201351285998679</v>
+        <v>0.1573589891195297</v>
       </c>
       <c r="F33" t="n">
-        <v>-4.417032858088251e-05</v>
+        <v>0.02907702513039112</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.001239802044319288</v>
+        <v>-0.06139378249645233</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.002155318975582605</v>
+        <v>0.1596910655498505</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.001045106985556366</v>
+        <v>-0.5777111053466797</v>
       </c>
       <c r="J33" t="n">
-        <v>1.916541602237683e-05</v>
+        <v>-4.394197458168492e-05</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.0007770607798034329</v>
+        <v>-0.006820742040872574</v>
       </c>
       <c r="L33" t="n">
-        <v>0.001025772234460885</v>
+        <v>-0.2014432847499847</v>
       </c>
       <c r="M33" t="n">
-        <v>0.003066135521283394</v>
+        <v>-0.03592783957719803</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.000497847518233418</v>
+        <v>0.5233867168426514</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.0002092258460773414</v>
+        <v>0.1975567936897278</v>
       </c>
       <c r="P33" t="n">
-        <v>-0.0009954493868160404</v>
+        <v>0.3315143585205078</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.0005149085037842891</v>
+        <v>0.3349686563014984</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.001182910877224235</v>
+        <v>-0.5595851540565491</v>
       </c>
       <c r="S33" t="n">
-        <v>0.001611029039470265</v>
+        <v>-0.451510101556778</v>
       </c>
       <c r="T33" t="n">
-        <v>0.0001058140399850607</v>
+        <v>0.1324636191129684</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.000117033395539694</v>
+        <v>-0.131353497505188</v>
       </c>
       <c r="V33" t="n">
-        <v>-0.000931531984899115</v>
+        <v>-0.417164534330368</v>
       </c>
       <c r="W33" t="n">
-        <v>-0.0002782095370607304</v>
+        <v>-0.2168330401182175</v>
       </c>
       <c r="X33" t="n">
-        <v>-8.912431759919634e-05</v>
+        <v>0.1562396436929703</v>
       </c>
       <c r="Y33" t="n">
-        <v>-0.00195500404637442</v>
+        <v>0.6342669129371643</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.0014840530793124</v>
+        <v>-0.09698174148797989</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.002356562279369142</v>
+        <v>-0.05806320533156395</v>
       </c>
       <c r="AB33" t="n">
-        <v>-0.0007550058680748903</v>
+        <v>-0.1905626505613327</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.0006771981539654282</v>
+        <v>0.07266253232955933</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.0007394895725249285</v>
+        <v>-0.2194509357213974</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.000642183675346753</v>
+        <v>-0.01683482527732849</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.0006088883845536215</v>
+        <v>-0.3250482678413391</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.003006134426103509</v>
+        <v>-0.2045860588550568</v>
       </c>
       <c r="AH33" t="n">
-        <v>-0.0008715301504630481</v>
+        <v>-0.2405297160148621</v>
       </c>
       <c r="AI33" t="n">
-        <v>-0.0003074540908039924</v>
+        <v>-0.2901831865310669</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.001619131139347774</v>
+        <v>0.3231562077999115</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.001080340521636105</v>
+        <v>0.1111352071166039</v>
       </c>
       <c r="AL33" t="n">
-        <v>-0.000197181231383209</v>
+        <v>-0.6362254023551941</v>
       </c>
       <c r="AM33" t="n">
-        <v>-0.0008049830589097455</v>
+        <v>-0.05356269702315331</v>
       </c>
       <c r="AN33" t="n">
-        <v>0.000201697997727139</v>
+        <v>-0.1442511230707169</v>
       </c>
       <c r="AO33" t="n">
-        <v>0.0009570608337326767</v>
+        <v>-0.1278512179851532</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.634133157734796e-05</v>
+        <v>0.2153482139110565</v>
       </c>
       <c r="AQ33" t="n">
-        <v>7.507271986478068e-05</v>
+        <v>0.2108907550573349</v>
       </c>
       <c r="AR33" t="n">
-        <v>-0.0005111105700214802</v>
+        <v>-0.4162647128105164</v>
       </c>
       <c r="AS33" t="n">
-        <v>-0.002391880206036055</v>
+        <v>0.1712823659181595</v>
       </c>
       <c r="AT33" t="n">
-        <v>-2.357831434381685e-05</v>
+        <v>0.1235609278082848</v>
       </c>
       <c r="AU33" t="n">
-        <v>0.002320384777038517</v>
+        <v>-0.1431176215410233</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.0001601122968174823</v>
+        <v>0.205217644572258</v>
       </c>
       <c r="AW33" t="n">
-        <v>-0.0003883016936199346</v>
+        <v>0.340173602104187</v>
       </c>
       <c r="AX33" t="n">
-        <v>-8.639301535408171e-05</v>
+        <v>-0.1160770133137703</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
@@ -5647,154 +5647,154 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.0002235050657351906</v>
+        <v>-0.2829754650592804</v>
       </c>
       <c r="B34" t="n">
-        <v>0.002106468380029188</v>
+        <v>-0.5812587738037109</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.001581222558499813</v>
+        <v>0.05888726562261581</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0008856381068991981</v>
+        <v>-0.1664683222770691</v>
       </c>
       <c r="E34" t="n">
-        <v>-7.076198614482251e-05</v>
+        <v>0.1170173361897469</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.002067360542072594</v>
+        <v>-0.08232089132070541</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.0004919933923524172</v>
+        <v>-0.241151750087738</v>
       </c>
       <c r="H34" t="n">
-        <v>0.00018198832636135</v>
+        <v>-0.02117647975683212</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.001287415717972709</v>
+        <v>-0.5191332697868347</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.0007023357314682471</v>
+        <v>0.1086382940411568</v>
       </c>
       <c r="K34" t="n">
-        <v>0.0001352173415993564</v>
+        <v>-0.09194770455360413</v>
       </c>
       <c r="L34" t="n">
-        <v>0.001090887871350353</v>
+        <v>-0.04531850665807724</v>
       </c>
       <c r="M34" t="n">
-        <v>0.002237692526856005</v>
+        <v>-0.1746398061513901</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.0003051774490588353</v>
+        <v>0.4311169385910034</v>
       </c>
       <c r="O34" t="n">
-        <v>0.001105663159260881</v>
+        <v>0.08435730636119843</v>
       </c>
       <c r="P34" t="n">
-        <v>-0.0005296353909481863</v>
+        <v>0.141352191567421</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.001525387168787803</v>
+        <v>0.1656771004199982</v>
       </c>
       <c r="R34" t="n">
-        <v>0.001557559580006256</v>
+        <v>-0.5143737196922302</v>
       </c>
       <c r="S34" t="n">
-        <v>0.0005332630164229561</v>
+        <v>-0.3646314144134521</v>
       </c>
       <c r="T34" t="n">
-        <v>0.0009720023812557428</v>
+        <v>0.05245555937290192</v>
       </c>
       <c r="U34" t="n">
-        <v>-0.002058221717043337</v>
+        <v>0.05850829184055328</v>
       </c>
       <c r="V34" t="n">
-        <v>0.0007723728440143737</v>
+        <v>-0.2749247848987579</v>
       </c>
       <c r="W34" t="n">
-        <v>-4.453112379717254e-05</v>
+        <v>-0.2436417043209076</v>
       </c>
       <c r="X34" t="n">
-        <v>0.0006290560224296057</v>
+        <v>0.1920808702707291</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.0001412185257894519</v>
+        <v>0.6016882658004761</v>
       </c>
       <c r="Z34" t="n">
-        <v>-0.002674178324326152</v>
+        <v>0.01416959706693888</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.0004024755401146327</v>
+        <v>-0.08407275378704071</v>
       </c>
       <c r="AB34" t="n">
-        <v>-0.001477848717437835</v>
+        <v>-0.08510253578424454</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.000507530244716687</v>
+        <v>-0.02666456066071987</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.0002170950198921537</v>
+        <v>-0.1735179275274277</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.0002746770026539601</v>
+        <v>-0.01586988009512424</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.0005273601320660079</v>
+        <v>-0.1061442419886589</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.004476273169267585</v>
+        <v>-0.138386070728302</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.0003195123299318746</v>
+        <v>-0.2927269339561462</v>
       </c>
       <c r="AI34" t="n">
-        <v>-0.001074065478680571</v>
+        <v>-0.2006676644086838</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.001748588862610536</v>
+        <v>0.08520763367414474</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.0007836014633682708</v>
+        <v>-0.06725821644067764</v>
       </c>
       <c r="AL34" t="n">
-        <v>-0.00133858412263795</v>
+        <v>-0.5894542336463928</v>
       </c>
       <c r="AM34" t="n">
-        <v>-0.002111931236595803</v>
+        <v>-0.2194957584142685</v>
       </c>
       <c r="AN34" t="n">
-        <v>0.0002227297933982213</v>
+        <v>0.07793308049440384</v>
       </c>
       <c r="AO34" t="n">
-        <v>-0.0008119183191123161</v>
+        <v>-0.001963287126272917</v>
       </c>
       <c r="AP34" t="n">
-        <v>-0.00113656460594971</v>
+        <v>0.2091369479894638</v>
       </c>
       <c r="AQ34" t="n">
-        <v>-0.0005943053578443078</v>
+        <v>0.2945930659770966</v>
       </c>
       <c r="AR34" t="n">
-        <v>-0.002596595041927188</v>
+        <v>-0.2344335168600082</v>
       </c>
       <c r="AS34" t="n">
-        <v>-0.001162277569364423</v>
+        <v>0.2991396486759186</v>
       </c>
       <c r="AT34" t="n">
-        <v>-0.000484282037554075</v>
+        <v>0.1562467366456985</v>
       </c>
       <c r="AU34" t="n">
-        <v>0.0005628785894427983</v>
+        <v>-0.2334625720977783</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.0001211338945176849</v>
+        <v>0.2400321960449219</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.0003940748876772013</v>
+        <v>0.3284823298454285</v>
       </c>
       <c r="AX34" t="n">
-        <v>-0.0005537432430090513</v>
+        <v>-0.3209861516952515</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
@@ -5802,154 +5802,154 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-0.00128507325649926</v>
+        <v>-0.3029104769229889</v>
       </c>
       <c r="B35" t="n">
-        <v>0.002520369741082564</v>
+        <v>-0.4526813924312592</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.001057538436805971</v>
+        <v>0.01917929761111736</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0001982092592476605</v>
+        <v>-0.3343533873558044</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.0003209103072984825</v>
+        <v>0.01240204181522131</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0003322476843252183</v>
+        <v>-0.2820332646369934</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.000714479150224112</v>
+        <v>-0.1377004832029343</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.001943353039824024</v>
+        <v>0.064924456179142</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.003127798169534607</v>
+        <v>-0.4382400512695312</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.001118604519644367</v>
+        <v>0.0412713848054409</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.0004396911475882965</v>
+        <v>-0.2409214675426483</v>
       </c>
       <c r="L35" t="n">
-        <v>0.0004986435018822515</v>
+        <v>-0.2072818279266357</v>
       </c>
       <c r="M35" t="n">
-        <v>0.001987065598713505</v>
+        <v>-0.01047368347644806</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.001283763450009916</v>
+        <v>0.48173588514328</v>
       </c>
       <c r="O35" t="n">
-        <v>0.0008390629031881007</v>
+        <v>0.03790381923317909</v>
       </c>
       <c r="P35" t="n">
-        <v>-0.0004303245048046869</v>
+        <v>0.1459830403327942</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.0008453807175744719</v>
+        <v>0.2005191594362259</v>
       </c>
       <c r="R35" t="n">
-        <v>6.445590483115308e-05</v>
+        <v>-0.6809177994728088</v>
       </c>
       <c r="S35" t="n">
-        <v>0.001730174815012606</v>
+        <v>-0.1103726848959923</v>
       </c>
       <c r="T35" t="n">
-        <v>-0.0008295644791137374</v>
+        <v>0.154888316988945</v>
       </c>
       <c r="U35" t="n">
-        <v>-0.001023555463892506</v>
+        <v>0.08608164638280869</v>
       </c>
       <c r="V35" t="n">
-        <v>0.0007236669923795436</v>
+        <v>-0.2364650368690491</v>
       </c>
       <c r="W35" t="n">
-        <v>-0.001847771643984802</v>
+        <v>-0.2901802361011505</v>
       </c>
       <c r="X35" t="n">
-        <v>0.0003512061230039148</v>
+        <v>0.1615365743637085</v>
       </c>
       <c r="Y35" t="n">
-        <v>-0.001100753720312552</v>
+        <v>0.4831665456295013</v>
       </c>
       <c r="Z35" t="n">
-        <v>-0.003104506128241303</v>
+        <v>0.1278802305459976</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.0005387550490520801</v>
+        <v>-0.0994880273938179</v>
       </c>
       <c r="AB35" t="n">
-        <v>-0.00132090170818932</v>
+        <v>0.06010224297642708</v>
       </c>
       <c r="AC35" t="n">
-        <v>4.237518305800327e-05</v>
+        <v>-0.07090172171592712</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.0008497683240618374</v>
+        <v>-0.230266273021698</v>
       </c>
       <c r="AE35" t="n">
-        <v>-0.0009238466064409907</v>
+        <v>0.03752557560801506</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.001223909775084393</v>
+        <v>-0.08335259556770325</v>
       </c>
       <c r="AG35" t="n">
-        <v>-0.001056342194897658</v>
+        <v>-0.1639830470085144</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.0002216297775218389</v>
+        <v>-0.1988003849983215</v>
       </c>
       <c r="AI35" t="n">
-        <v>-0.001084308054643136</v>
+        <v>-0.1823399662971497</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.0004019726559815548</v>
+        <v>0.04917630925774574</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.000931341726187227</v>
+        <v>-0.0915771946310997</v>
       </c>
       <c r="AL35" t="n">
-        <v>0.00141138571459965</v>
+        <v>-0.5731701254844666</v>
       </c>
       <c r="AM35" t="n">
-        <v>-0.0004452256445314171</v>
+        <v>-0.157856673002243</v>
       </c>
       <c r="AN35" t="n">
-        <v>0.0004738458414516534</v>
+        <v>0.0598854161798954</v>
       </c>
       <c r="AO35" t="n">
-        <v>0.001147265607044844</v>
+        <v>-0.06727298349142075</v>
       </c>
       <c r="AP35" t="n">
-        <v>-0.0007847834878863331</v>
+        <v>0.07003334909677505</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.001321324531462431</v>
+        <v>0.09125779569149017</v>
       </c>
       <c r="AR35" t="n">
-        <v>-0.0001842627464635748</v>
+        <v>-0.191010445356369</v>
       </c>
       <c r="AS35" t="n">
-        <v>-0.0002935819607410514</v>
+        <v>0.2815387845039368</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.0009987607201947363</v>
+        <v>0.3380894660949707</v>
       </c>
       <c r="AU35" t="n">
-        <v>0.0005683603010760273</v>
+        <v>-0.3002738952636719</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.001261997208848833</v>
+        <v>0.2734273672103882</v>
       </c>
       <c r="AW35" t="n">
-        <v>-0.0006294553213824635</v>
+        <v>0.2327199578285217</v>
       </c>
       <c r="AX35" t="n">
-        <v>-0.0004564820340673248</v>
+        <v>-0.2731145322322845</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
@@ -5957,154 +5957,154 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.00019223796873335</v>
+        <v>-0.2989478707313538</v>
       </c>
       <c r="B36" t="n">
-        <v>0.004172127816304434</v>
+        <v>-0.5854966044425964</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0006971906095023645</v>
+        <v>0.1491034626960754</v>
       </c>
       <c r="D36" t="n">
-        <v>0.001339164535893941</v>
+        <v>-0.1360334157943726</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.001018558217358465</v>
+        <v>-0.01060913503170013</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0006529219438539183</v>
+        <v>-0.1423993408679962</v>
       </c>
       <c r="G36" t="n">
-        <v>-1.83478404801348e-05</v>
+        <v>0.1475146561861038</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.0002076774094259996</v>
+        <v>0.3661417663097382</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.001117542067927239</v>
+        <v>-0.5970767736434937</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0008188804356908715</v>
+        <v>-0.02883291058242321</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.0004278439274443425</v>
+        <v>-0.3288764953613281</v>
       </c>
       <c r="L36" t="n">
-        <v>0.0005736425028191785</v>
+        <v>-0.06419859826564789</v>
       </c>
       <c r="M36" t="n">
-        <v>0.001504352986906267</v>
+        <v>-0.3612057268619537</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.0005557249841125614</v>
+        <v>0.5697523355484009</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.001185742589457493</v>
+        <v>0.07961104810237885</v>
       </c>
       <c r="P36" t="n">
-        <v>-0.002055360210839312</v>
+        <v>0.1826402693986893</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.0008075223234734306</v>
+        <v>0.3025706708431244</v>
       </c>
       <c r="R36" t="n">
-        <v>0.000714949857009544</v>
+        <v>-0.6298701763153076</v>
       </c>
       <c r="S36" t="n">
-        <v>0.0007307861273669997</v>
+        <v>-0.3248213529586792</v>
       </c>
       <c r="T36" t="n">
-        <v>-0.001086265870594221</v>
+        <v>-0.02190804667770863</v>
       </c>
       <c r="U36" t="n">
-        <v>-0.001331376982293947</v>
+        <v>0.08597391843795776</v>
       </c>
       <c r="V36" t="n">
-        <v>-0.001279045268117932</v>
+        <v>-0.5352312922477722</v>
       </c>
       <c r="W36" t="n">
-        <v>-0.001169093305131973</v>
+        <v>-0.2986168265342712</v>
       </c>
       <c r="X36" t="n">
-        <v>0.0004787493820851895</v>
+        <v>0.2669108510017395</v>
       </c>
       <c r="Y36" t="n">
-        <v>-0.0004069253741911291</v>
+        <v>0.637919545173645</v>
       </c>
       <c r="Z36" t="n">
-        <v>-0.002702750416268426</v>
+        <v>-0.03778208419680595</v>
       </c>
       <c r="AA36" t="n">
-        <v>-0.0002406216559440781</v>
+        <v>-0.1396734416484833</v>
       </c>
       <c r="AB36" t="n">
-        <v>-0.002337187601087462</v>
+        <v>-0.3808220028877258</v>
       </c>
       <c r="AC36" t="n">
-        <v>-0.0009079179942458236</v>
+        <v>-0.1647203415632248</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.0003436601694315037</v>
+        <v>-0.2547014951705933</v>
       </c>
       <c r="AE36" t="n">
-        <v>-0.0005145622060493061</v>
+        <v>-0.02678355947136879</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.001194499799606795</v>
+        <v>-0.2255227416753769</v>
       </c>
       <c r="AG36" t="n">
-        <v>-0.001602966791822317</v>
+        <v>-0.2168167680501938</v>
       </c>
       <c r="AH36" t="n">
-        <v>-0.001119722286320352</v>
+        <v>-0.07802793383598328</v>
       </c>
       <c r="AI36" t="n">
-        <v>-0.0002286554011534729</v>
+        <v>-0.1754234731197357</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.000212426659197278</v>
+        <v>0.1394244283437729</v>
       </c>
       <c r="AK36" t="n">
-        <v>-0.0004957264242990685</v>
+        <v>-0.2731585800647736</v>
       </c>
       <c r="AL36" t="n">
-        <v>0.0003812109399079248</v>
+        <v>-0.8672270774841309</v>
       </c>
       <c r="AM36" t="n">
-        <v>-0.001317780785408611</v>
+        <v>-0.2314276099205017</v>
       </c>
       <c r="AN36" t="n">
-        <v>-0.0005391774027548632</v>
+        <v>-0.2983707785606384</v>
       </c>
       <c r="AO36" t="n">
-        <v>-4.234556697477018e-05</v>
+        <v>0.1986206471920013</v>
       </c>
       <c r="AP36" t="n">
-        <v>-0.001419670360622802</v>
+        <v>0.2421844005584717</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.0002225482712953415</v>
+        <v>0.1160577386617661</v>
       </c>
       <c r="AR36" t="n">
-        <v>-0.001142858845313755</v>
+        <v>-0.4203670024871826</v>
       </c>
       <c r="AS36" t="n">
-        <v>-0.001539702377631289</v>
+        <v>0.2785040438175201</v>
       </c>
       <c r="AT36" t="n">
-        <v>-0.0001907269479025012</v>
+        <v>0.1940527856349945</v>
       </c>
       <c r="AU36" t="n">
-        <v>0.001022870274636671</v>
+        <v>0.08428968489170074</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.001066599717813461</v>
+        <v>0.2410449087619781</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.0002343494962542457</v>
+        <v>0.5330981612205505</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.001048133335994168</v>
+        <v>-0.1451058238744736</v>
       </c>
       <c r="AY36" t="n">
         <v>0</v>
@@ -6112,154 +6112,154 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.0005426958919866331</v>
+        <v>-0.2416988015174866</v>
       </c>
       <c r="B37" t="n">
-        <v>0.002528220207492127</v>
+        <v>-0.5169363021850586</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.002290369288774802</v>
+        <v>-0.01036817207932472</v>
       </c>
       <c r="D37" t="n">
-        <v>0.001921469800861443</v>
+        <v>-0.2520093619823456</v>
       </c>
       <c r="E37" t="n">
-        <v>0.001355026970009561</v>
+        <v>0.0339818149805069</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0001792954274210595</v>
+        <v>-0.1754996031522751</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.001992785459582143</v>
+        <v>-0.2806483805179596</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.002019462748537294</v>
+        <v>-0.07500408589839935</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.001707006045829799</v>
+        <v>-0.4438445270061493</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.0007946040602181576</v>
+        <v>0.1454779207706451</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.004132863535498367</v>
+        <v>-0.2192174196243286</v>
       </c>
       <c r="L37" t="n">
-        <v>0.0004803376914585683</v>
+        <v>-0.06051874533295631</v>
       </c>
       <c r="M37" t="n">
-        <v>0.0006181167034894154</v>
+        <v>-0.07966187596321106</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.001131687399629895</v>
+        <v>0.4504259526729584</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.001058690192178543</v>
+        <v>0.0201425738632679</v>
       </c>
       <c r="P37" t="n">
-        <v>-0.001622191014503934</v>
+        <v>0.144773930311203</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.0004590596986779283</v>
+        <v>0.08837036043405533</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.00123492201851793</v>
+        <v>-0.5686401128768921</v>
       </c>
       <c r="S37" t="n">
-        <v>0.002090466332371078</v>
+        <v>-0.09758596122264862</v>
       </c>
       <c r="T37" t="n">
-        <v>-0.001102330236522546</v>
+        <v>0.09483075886964798</v>
       </c>
       <c r="U37" t="n">
-        <v>-0.002853096477940578</v>
+        <v>0.1311299204826355</v>
       </c>
       <c r="V37" t="n">
-        <v>0.0001495300906385734</v>
+        <v>-0.1964448690414429</v>
       </c>
       <c r="W37" t="n">
-        <v>0.0002293180752849197</v>
+        <v>-0.2713383138179779</v>
       </c>
       <c r="X37" t="n">
-        <v>0.0001140618435849805</v>
+        <v>0.1791675835847855</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.000857619682421951</v>
+        <v>0.4910305738449097</v>
       </c>
       <c r="Z37" t="n">
-        <v>-0.002034952344348832</v>
+        <v>0.1284313499927521</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.001625145533897228</v>
+        <v>-0.2115564346313477</v>
       </c>
       <c r="AB37" t="n">
-        <v>-0.0003486754946237674</v>
+        <v>0.08055852353572845</v>
       </c>
       <c r="AC37" t="n">
-        <v>-0.002158262809825219</v>
+        <v>-0.06025370210409164</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.001089001489016248</v>
+        <v>-0.2486923038959503</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.00115886354987753</v>
+        <v>0.02317661419510841</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.001043167800644924</v>
+        <v>-0.02469823136925697</v>
       </c>
       <c r="AG37" t="n">
-        <v>-0.003370326792056846</v>
+        <v>-0.160502627491951</v>
       </c>
       <c r="AH37" t="n">
-        <v>-0.003096362855226817</v>
+        <v>-0.1691611409187317</v>
       </c>
       <c r="AI37" t="n">
-        <v>-0.0001919837411182538</v>
+        <v>-0.2067453116178513</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.0008688137357624862</v>
+        <v>0.01074407063424587</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.0008549865548995635</v>
+        <v>-0.1517321169376373</v>
       </c>
       <c r="AL37" t="n">
-        <v>-0.0005753194494323055</v>
+        <v>-0.6470288634300232</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.001342494443501376</v>
+        <v>-0.3044677376747131</v>
       </c>
       <c r="AN37" t="n">
-        <v>0.0002846471384538275</v>
+        <v>0.1521272361278534</v>
       </c>
       <c r="AO37" t="n">
-        <v>0.001328427757659826</v>
+        <v>-0.09729535132646561</v>
       </c>
       <c r="AP37" t="n">
-        <v>-0.001313223030364542</v>
+        <v>0.1651150733232498</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.001127469460216279</v>
+        <v>0.22138312458992</v>
       </c>
       <c r="AR37" t="n">
-        <v>-0.0004470902949706586</v>
+        <v>-0.1492964178323746</v>
       </c>
       <c r="AS37" t="n">
-        <v>-0.00172113727057098</v>
+        <v>0.3030950129032135</v>
       </c>
       <c r="AT37" t="n">
-        <v>-0.0003608939731075339</v>
+        <v>0.391033947467804</v>
       </c>
       <c r="AU37" t="n">
-        <v>0.001467537553070466</v>
+        <v>-0.3037585020065308</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.002950432378638155</v>
+        <v>0.3102140128612518</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.0006895685509697405</v>
+        <v>0.2335153669118881</v>
       </c>
       <c r="AX37" t="n">
-        <v>-0.00116934914435591</v>
+        <v>-0.3270235061645508</v>
       </c>
       <c r="AY37" t="n">
         <v>0</v>
@@ -6267,154 +6267,154 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>7.338654955802607e-05</v>
+        <v>-0.3326835334300995</v>
       </c>
       <c r="B38" t="n">
-        <v>0.001224635355390587</v>
+        <v>-0.5189765691757202</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.00256724701971043</v>
+        <v>0.1381169259548187</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0001023044828671164</v>
+        <v>-0.05520812794566154</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.002186737587723143</v>
+        <v>-0.01363293547183275</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.001058502083941774</v>
+        <v>-0.119846798479557</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.001460419022704189</v>
+        <v>0.1182581409811974</v>
       </c>
       <c r="H38" t="n">
-        <v>0.000157704997827007</v>
+        <v>0.3570904135704041</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.001817230152375348</v>
+        <v>-0.7473089098930359</v>
       </c>
       <c r="J38" t="n">
-        <v>0.0008364015588009544</v>
+        <v>-0.09340233355760574</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.0005050408250097916</v>
+        <v>-0.3056637048721313</v>
       </c>
       <c r="L38" t="n">
-        <v>0.0001422080821339251</v>
+        <v>-0.07349171489477158</v>
       </c>
       <c r="M38" t="n">
-        <v>0.002584140855090851</v>
+        <v>-0.3327156901359558</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.002724815941670765</v>
+        <v>0.5624492764472961</v>
       </c>
       <c r="O38" t="n">
-        <v>-0.0005741538312878972</v>
+        <v>0.1756776571273804</v>
       </c>
       <c r="P38" t="n">
-        <v>-0.00110770901823266</v>
+        <v>0.2646318376064301</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.001430912513852086</v>
+        <v>0.3194511234760284</v>
       </c>
       <c r="R38" t="n">
-        <v>0.000404795031395993</v>
+        <v>-0.5293011665344238</v>
       </c>
       <c r="S38" t="n">
-        <v>0.002159885080382469</v>
+        <v>-0.3468296825885773</v>
       </c>
       <c r="T38" t="n">
-        <v>0.0001279318163595949</v>
+        <v>-0.09827952831983566</v>
       </c>
       <c r="U38" t="n">
-        <v>-0.001106766640422895</v>
+        <v>0.04670319333672523</v>
       </c>
       <c r="V38" t="n">
-        <v>-0.0001483553197003814</v>
+        <v>-0.5814578533172607</v>
       </c>
       <c r="W38" t="n">
-        <v>-0.001042557091790875</v>
+        <v>-0.2899639010429382</v>
       </c>
       <c r="X38" t="n">
-        <v>0.0008371542909231104</v>
+        <v>0.3275118172168732</v>
       </c>
       <c r="Y38" t="n">
-        <v>-0.0006881005725672095</v>
+        <v>0.657416820526123</v>
       </c>
       <c r="Z38" t="n">
-        <v>-0.002481788970441154</v>
+        <v>0.006208368111401796</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.001153929687205415</v>
+        <v>-0.1550299972295761</v>
       </c>
       <c r="AB38" t="n">
-        <v>-6.456834569450877e-05</v>
+        <v>-0.3945829272270203</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.0009760451610883691</v>
+        <v>-0.1506565660238266</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.000107252102807875</v>
+        <v>-0.2067701667547226</v>
       </c>
       <c r="AE38" t="n">
-        <v>-0.0006349919956589284</v>
+        <v>-0.01155429426580667</v>
       </c>
       <c r="AF38" t="n">
-        <v>-0.0009652543940626954</v>
+        <v>-0.2246699184179306</v>
       </c>
       <c r="AG38" t="n">
-        <v>-0.003873970906293053</v>
+        <v>-0.2762386798858643</v>
       </c>
       <c r="AH38" t="n">
-        <v>-0.001540362525673811</v>
+        <v>-0.1189357191324234</v>
       </c>
       <c r="AI38" t="n">
-        <v>-0.000489503737644334</v>
+        <v>-0.2716286480426788</v>
       </c>
       <c r="AJ38" t="n">
-        <v>-0.0004623309199197629</v>
+        <v>0.1433925628662109</v>
       </c>
       <c r="AK38" t="n">
-        <v>-0.0005278046796869163</v>
+        <v>-0.166794627904892</v>
       </c>
       <c r="AL38" t="n">
-        <v>0.0005524708124617996</v>
+        <v>-0.8266531825065613</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.00055295786823949</v>
+        <v>-0.197208359837532</v>
       </c>
       <c r="AN38" t="n">
-        <v>0.0006443981655898459</v>
+        <v>-0.3134572505950928</v>
       </c>
       <c r="AO38" t="n">
-        <v>0.001544907139861777</v>
+        <v>0.1535703390836716</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.000704962154038478</v>
+        <v>0.2196471393108368</v>
       </c>
       <c r="AQ38" t="n">
-        <v>-7.642291315884125e-05</v>
+        <v>0.1111677661538124</v>
       </c>
       <c r="AR38" t="n">
-        <v>-0.001681156485371597</v>
+        <v>-0.3967344462871552</v>
       </c>
       <c r="AS38" t="n">
-        <v>-0.001948069561319387</v>
+        <v>0.3125288486480713</v>
       </c>
       <c r="AT38" t="n">
-        <v>-0.001466338947265858</v>
+        <v>0.06596889346837997</v>
       </c>
       <c r="AU38" t="n">
-        <v>0.001669459899178568</v>
+        <v>0.07896637916564941</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.001915615307355885</v>
+        <v>0.2706463932991028</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.0002407197039555617</v>
+        <v>0.5676937103271484</v>
       </c>
       <c r="AX38" t="n">
-        <v>-0.001048600378460848</v>
+        <v>-0.1512783467769623</v>
       </c>
       <c r="AY38" t="n">
         <v>0</v>
@@ -6422,154 +6422,154 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>-1.930882716135729e-05</v>
+        <v>-0.367830216884613</v>
       </c>
       <c r="B39" t="n">
-        <v>0.003527293683429801</v>
+        <v>-0.5080340504646301</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.00199947760050772</v>
+        <v>0.05888637155294418</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.001664166456105885</v>
+        <v>-0.3079343736171722</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.001178345276372169</v>
+        <v>0.07190721482038498</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.000142515589043056</v>
+        <v>-0.2705967426300049</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.0009610563599428025</v>
+        <v>-0.2357620596885681</v>
       </c>
       <c r="H39" t="n">
-        <v>1.104002550283532e-05</v>
+        <v>-0.07349099963903427</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.002988099130084491</v>
+        <v>-0.4389378130435944</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.001958025856221751</v>
+        <v>0.04639851674437523</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.001678985305011969</v>
+        <v>-0.1425145715475082</v>
       </c>
       <c r="L39" t="n">
-        <v>9.306325583524378e-05</v>
+        <v>-0.162366196513176</v>
       </c>
       <c r="M39" t="n">
-        <v>0.001299861438264528</v>
+        <v>0.03378014639019966</v>
       </c>
       <c r="N39" t="n">
-        <v>0.000843508650143156</v>
+        <v>0.4063620269298553</v>
       </c>
       <c r="O39" t="n">
-        <v>0.000556006690594237</v>
+        <v>0.206300362944603</v>
       </c>
       <c r="P39" t="n">
-        <v>-0.002204420346342371</v>
+        <v>0.1523233950138092</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.0009082462059938029</v>
+        <v>0.1117041856050491</v>
       </c>
       <c r="R39" t="n">
-        <v>0.000853556788333335</v>
+        <v>-0.6564281582832336</v>
       </c>
       <c r="S39" t="n">
-        <v>0.002453437708800056</v>
+        <v>-0.08642835915088654</v>
       </c>
       <c r="T39" t="n">
-        <v>-0.001469685510769572</v>
+        <v>0.1499322354793549</v>
       </c>
       <c r="U39" t="n">
-        <v>-0.002074076533642163</v>
+        <v>0.07668736577033997</v>
       </c>
       <c r="V39" t="n">
-        <v>0.001141251055790797</v>
+        <v>-0.2701844274997711</v>
       </c>
       <c r="W39" t="n">
-        <v>-7.089227019854583e-05</v>
+        <v>-0.2909236550331116</v>
       </c>
       <c r="X39" t="n">
-        <v>0.0004451584819542539</v>
+        <v>0.1356330811977386</v>
       </c>
       <c r="Y39" t="n">
-        <v>9.105638964708912e-05</v>
+        <v>0.4960846304893494</v>
       </c>
       <c r="Z39" t="n">
-        <v>-0.002346258494002137</v>
+        <v>0.06718584895133972</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.001357784274835646</v>
+        <v>-0.03872755914926529</v>
       </c>
       <c r="AB39" t="n">
-        <v>-0.0007876676029820837</v>
+        <v>0.0920596569776535</v>
       </c>
       <c r="AC39" t="n">
-        <v>-0.0003662900837616282</v>
+        <v>0.004325494170188904</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.001546047731449039</v>
+        <v>-0.2674068212509155</v>
       </c>
       <c r="AE39" t="n">
-        <v>-0.0001589354677867422</v>
+        <v>0.05080434307456017</v>
       </c>
       <c r="AF39" t="n">
-        <v>-6.171103051837872e-05</v>
+        <v>-0.03399692475795746</v>
       </c>
       <c r="AG39" t="n">
-        <v>-0.003463396504397595</v>
+        <v>-0.1769796162843704</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.0009234693872233039</v>
+        <v>-0.2373056709766388</v>
       </c>
       <c r="AI39" t="n">
-        <v>-0.00173120319855443</v>
+        <v>-0.1743306517601013</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.001346507920470383</v>
+        <v>0.07409673184156418</v>
       </c>
       <c r="AK39" t="n">
-        <v>-0.0001087265891723117</v>
+        <v>-0.05566932260990143</v>
       </c>
       <c r="AL39" t="n">
-        <v>-0.0007117327640469666</v>
+        <v>-0.6256383061408997</v>
       </c>
       <c r="AM39" t="n">
-        <v>-3.692226167794138e-05</v>
+        <v>-0.2238987684249878</v>
       </c>
       <c r="AN39" t="n">
-        <v>0.001634132597262943</v>
+        <v>0.1871636062860489</v>
       </c>
       <c r="AO39" t="n">
-        <v>-0.0009143346796228541</v>
+        <v>-0.0716918557882309</v>
       </c>
       <c r="AP39" t="n">
-        <v>-0.001717983612090029</v>
+        <v>0.07202835381031036</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.0005704584393605243</v>
+        <v>0.1157756820321083</v>
       </c>
       <c r="AR39" t="n">
-        <v>-0.002236411266261552</v>
+        <v>-0.10550457239151</v>
       </c>
       <c r="AS39" t="n">
-        <v>-0.001335614566819526</v>
+        <v>0.2555217146873474</v>
       </c>
       <c r="AT39" t="n">
-        <v>-0.000851228333477939</v>
+        <v>0.3359315395355225</v>
       </c>
       <c r="AU39" t="n">
-        <v>-0.0001643726361609643</v>
+        <v>-0.29997518658638</v>
       </c>
       <c r="AV39" t="n">
-        <v>-0.0004892291602467543</v>
+        <v>0.3513432741165161</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.0001806918133829489</v>
+        <v>0.2164023816585541</v>
       </c>
       <c r="AX39" t="n">
-        <v>-0.001018098761143921</v>
+        <v>-0.2538371086120605</v>
       </c>
       <c r="AY39" t="n">
         <v>0</v>
@@ -6577,309 +6577,309 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>-6.849435815449726e-05</v>
+        <v>-0.2688199877738953</v>
       </c>
       <c r="B40" t="n">
-        <v>0.003451451598509524</v>
+        <v>-0.5050778388977051</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.001789237160640993</v>
+        <v>0.007099202834069729</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0003070237399760875</v>
+        <v>-0.2564099431037903</v>
       </c>
       <c r="E40" t="n">
-        <v>0.000527405342620843</v>
+        <v>0.01785651035606861</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0005007429671381852</v>
+        <v>-0.1697223484516144</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.001728071876374972</v>
+        <v>-0.2337913513183594</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.000586920710979537</v>
+        <v>-0.007775655947625637</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.002825226980447921</v>
+        <v>-0.3534662127494812</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0001579475736232722</v>
+        <v>0.08599857985973358</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.0006140955293342441</v>
+        <v>-0.1951316148042679</v>
       </c>
       <c r="L40" t="n">
-        <v>-4.829925081412454e-05</v>
+        <v>-0.1528410911560059</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.0004560676616222559</v>
+        <v>0.002748671220615506</v>
       </c>
       <c r="N40" t="n">
-        <v>-0.0009965613669431362</v>
+        <v>0.4179529249668121</v>
       </c>
       <c r="O40" t="n">
-        <v>-0.0002763554439472377</v>
+        <v>0.01189204026013613</v>
       </c>
       <c r="P40" t="n">
-        <v>-0.001955773574085215</v>
+        <v>0.1600283533334732</v>
       </c>
       <c r="Q40" t="n">
-        <v>8.618793823025086e-05</v>
+        <v>0.09257811307907104</v>
       </c>
       <c r="R40" t="n">
-        <v>0.0002613421801948902</v>
+        <v>-0.6334825754165649</v>
       </c>
       <c r="S40" t="n">
-        <v>0.002089864775390517</v>
+        <v>-0.1283081024885178</v>
       </c>
       <c r="T40" t="n">
-        <v>-0.0008278831400293078</v>
+        <v>0.250715434551239</v>
       </c>
       <c r="U40" t="n">
-        <v>-0.001558278599109762</v>
+        <v>0.06991345435380936</v>
       </c>
       <c r="V40" t="n">
-        <v>0.001011222288406609</v>
+        <v>-0.2024025917053223</v>
       </c>
       <c r="W40" t="n">
-        <v>-0.000540378612285918</v>
+        <v>-0.2030285745859146</v>
       </c>
       <c r="X40" t="n">
-        <v>-0.0003230582334052854</v>
+        <v>0.1023425906896591</v>
       </c>
       <c r="Y40" t="n">
-        <v>-0.0006653058153028314</v>
+        <v>0.4593113958835602</v>
       </c>
       <c r="Z40" t="n">
-        <v>-0.0008832141101623902</v>
+        <v>0.1181889399886131</v>
       </c>
       <c r="AA40" t="n">
-        <v>-0.0003660475868774321</v>
+        <v>-0.1721195131540298</v>
       </c>
       <c r="AB40" t="n">
-        <v>-0.0004371123161206859</v>
+        <v>0.0536762997508049</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.0004243886527696353</v>
+        <v>0.007877068594098091</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.00127051580590884</v>
+        <v>-0.2918579280376434</v>
       </c>
       <c r="AE40" t="n">
-        <v>8.473537754428328e-05</v>
+        <v>-0.01042984053492546</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.0003686612586053557</v>
+        <v>0.004113237839192152</v>
       </c>
       <c r="AG40" t="n">
-        <v>-0.001401169740921872</v>
+        <v>-0.1444292664527893</v>
       </c>
       <c r="AH40" t="n">
-        <v>-0.0007470190507042002</v>
+        <v>-0.1732827574014664</v>
       </c>
       <c r="AI40" t="n">
-        <v>-0.001085473078010879</v>
+        <v>-0.1580953299999237</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.001098152875234803</v>
+        <v>0.04724816977977753</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.0006385733690090663</v>
+        <v>-0.1024251282215118</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.000417717439866397</v>
+        <v>-0.6525943875312805</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.0003944413233491411</v>
+        <v>-0.278465747833252</v>
       </c>
       <c r="AN40" t="n">
-        <v>-0.002021599433524777</v>
+        <v>0.1421447545289993</v>
       </c>
       <c r="AO40" t="n">
-        <v>0.0001779581674384741</v>
+        <v>-0.06021718680858612</v>
       </c>
       <c r="AP40" t="n">
-        <v>-0.0005378456030797156</v>
+        <v>0.1345369964838028</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.0004586441551576184</v>
+        <v>0.07956631481647491</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.0001067985377571742</v>
+        <v>-0.1432603746652603</v>
       </c>
       <c r="AS40" t="n">
-        <v>-0.000876981694608403</v>
+        <v>0.249531015753746</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.000165010029792991</v>
+        <v>0.4205867946147919</v>
       </c>
       <c r="AU40" t="n">
-        <v>0.001659881844690723</v>
+        <v>-0.3187365233898163</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.0008947113730479279</v>
+        <v>0.3080988526344299</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.002531017992728135</v>
+        <v>0.2483475506305695</v>
       </c>
       <c r="AX40" t="n">
-        <v>-0.0009221416087349308</v>
+        <v>-0.2574918866157532</v>
       </c>
       <c r="AY40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-4.546399225929535e-05</v>
+        <v>-0.3325807750225067</v>
       </c>
       <c r="B41" t="n">
-        <v>0.003115498498552323</v>
+        <v>-0.4953594505786896</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.0006625466277023045</v>
+        <v>-0.01461939699947834</v>
       </c>
       <c r="D41" t="n">
-        <v>0.001259198817297358</v>
+        <v>-0.1767271608114243</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.000145506538450708</v>
+        <v>0.07985294610261917</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.0006023767384514277</v>
+        <v>-0.2952067852020264</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.001821367862938249</v>
+        <v>-0.2377571016550064</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.0008153447092747298</v>
+        <v>0.03271184116601944</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.00143423617630152</v>
+        <v>-0.4885692894458771</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.0007685180567595263</v>
+        <v>0.02514543943107128</v>
       </c>
       <c r="K41" t="n">
-        <v>0.0001832493408390371</v>
+        <v>-0.1929862946271896</v>
       </c>
       <c r="L41" t="n">
-        <v>0.0002162190615914313</v>
+        <v>-0.1064069122076035</v>
       </c>
       <c r="M41" t="n">
-        <v>0.001261788934021147</v>
+        <v>-0.04770160093903542</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.0007883876038654134</v>
+        <v>0.4510079622268677</v>
       </c>
       <c r="O41" t="n">
-        <v>0.0004818317960343112</v>
+        <v>0.1930055469274521</v>
       </c>
       <c r="P41" t="n">
-        <v>-0.001138179549507542</v>
+        <v>0.09287264943122864</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.0008600484041190161</v>
+        <v>0.09139886498451233</v>
       </c>
       <c r="R41" t="n">
-        <v>0.001366462282915303</v>
+        <v>-0.559172511100769</v>
       </c>
       <c r="S41" t="n">
-        <v>0.002312172611933958</v>
+        <v>-0.2374992221593857</v>
       </c>
       <c r="T41" t="n">
-        <v>-0.0007739462667311035</v>
+        <v>0.1388222426176071</v>
       </c>
       <c r="U41" t="n">
-        <v>0.0005194224253730848</v>
+        <v>0.1410912424325943</v>
       </c>
       <c r="V41" t="n">
-        <v>0.001182973223530591</v>
+        <v>-0.1677238941192627</v>
       </c>
       <c r="W41" t="n">
-        <v>-0.001572492046649008</v>
+        <v>-0.2413108795881271</v>
       </c>
       <c r="X41" t="n">
-        <v>-0.000312856226013092</v>
+        <v>0.1288006603717804</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.001457641605287815</v>
+        <v>0.6091123819351196</v>
       </c>
       <c r="Z41" t="n">
-        <v>-0.003230121713085277</v>
+        <v>0.05703698471188545</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.001382745127482478</v>
+        <v>-0.05087766796350479</v>
       </c>
       <c r="AB41" t="n">
-        <v>-0.0003786178984216601</v>
+        <v>0.1281103044748306</v>
       </c>
       <c r="AC41" t="n">
-        <v>-0.0002153207555278569</v>
+        <v>-0.09790325164794922</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.001158380048927062</v>
+        <v>-0.2617736458778381</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.0002745539978967024</v>
+        <v>0.04217225313186646</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.00164214704611363</v>
+        <v>-0.01817041262984276</v>
       </c>
       <c r="AG41" t="n">
-        <v>-0.001684088597748263</v>
+        <v>-0.1964940875768661</v>
       </c>
       <c r="AH41" t="n">
-        <v>-0.001442621301599166</v>
+        <v>-0.2623375952243805</v>
       </c>
       <c r="AI41" t="n">
-        <v>-0.001249252267088736</v>
+        <v>-0.1963546425104141</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.0005726447632583845</v>
+        <v>0.09201794117689133</v>
       </c>
       <c r="AK41" t="n">
-        <v>-0.0003730052585886116</v>
+        <v>-0.03740594163537025</v>
       </c>
       <c r="AL41" t="n">
-        <v>-0.0005308254194566985</v>
+        <v>-0.6402485370635986</v>
       </c>
       <c r="AM41" t="n">
-        <v>-0.001108418964243259</v>
+        <v>-0.1907812803983688</v>
       </c>
       <c r="AN41" t="n">
-        <v>0.000403375237728471</v>
+        <v>0.1441912800073624</v>
       </c>
       <c r="AO41" t="n">
-        <v>0.00176054799227369</v>
+        <v>-0.09242548793554306</v>
       </c>
       <c r="AP41" t="n">
-        <v>-0.001582618681152691</v>
+        <v>0.1621924191713333</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.001845461648678103</v>
+        <v>0.1622143238782883</v>
       </c>
       <c r="AR41" t="n">
-        <v>-0.002838761055058647</v>
+        <v>-0.2410827130079269</v>
       </c>
       <c r="AS41" t="n">
-        <v>-0.001841679020058614</v>
+        <v>0.2858326733112335</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.001429440506179986</v>
+        <v>0.2554358541965485</v>
       </c>
       <c r="AU41" t="n">
-        <v>0.0006319135556906692</v>
+        <v>-0.2367464900016785</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.0004985632660981267</v>
+        <v>0.4111754894256592</v>
       </c>
       <c r="AW41" t="n">
-        <v>6.862698859190883e-05</v>
+        <v>0.2394630610942841</v>
       </c>
       <c r="AX41" t="n">
-        <v>-0.0002624154223118028</v>
+        <v>-0.3272852897644043</v>
       </c>
       <c r="AY41" t="n">
         <v>0</v>

--- a/data_skipgram_testing.xlsx
+++ b/data_skipgram_testing.xlsx
@@ -687,154 +687,154 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0.4376794099807739</v>
+        <v>0.1376057416200638</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.6669853329658508</v>
+        <v>-0.4492151439189911</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1108608171343803</v>
+        <v>-0.05552054941654205</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.3955333232879639</v>
+        <v>-0.1718993335962296</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1039045676589012</v>
+        <v>-0.001749562215991318</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.466624915599823</v>
+        <v>0.07565882802009583</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.222147136926651</v>
+        <v>0.2760127484798431</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.05549504607915878</v>
+        <v>0.4890396296977997</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.449854850769043</v>
+        <v>-0.009861862286925316</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.002385182306170464</v>
+        <v>0.02580210380256176</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.07232334464788437</v>
+        <v>-0.3926407694816589</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.09250067174434662</v>
+        <v>0.1571214348077774</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1506260335445404</v>
+        <v>0.1228191629052162</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2318619042634964</v>
+        <v>-0.07108850032091141</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2807722985744476</v>
+        <v>0.2123800665140152</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0110613601282239</v>
+        <v>0.3331412971019745</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1575726866722107</v>
+        <v>0.07400991767644882</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.6026690602302551</v>
+        <v>-0.5851732492446899</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.05801428854465485</v>
+        <v>-0.2307776212692261</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2033176422119141</v>
+        <v>-0.3361762464046478</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1117400303483009</v>
+        <v>-0.2311574816703796</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.4343593418598175</v>
+        <v>0.01763386838138103</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.3467110991477966</v>
+        <v>0.3476446568965912</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1216372922062874</v>
+        <v>-0.05443610996007919</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5013274550437927</v>
+        <v>0.5151002407073975</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.04606025665998459</v>
+        <v>-0.1645829528570175</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.08906050026416779</v>
+        <v>0.1297692060470581</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.02949569188058376</v>
+        <v>-0.09489071369171143</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.06323827058076859</v>
+        <v>-0.3306916356086731</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.2241843789815903</v>
+        <v>-0.04094627872109413</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.01160466391593218</v>
+        <v>0.2668481171131134</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.2242250293493271</v>
+        <v>-0.02775112167000771</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.3543377220630646</v>
+        <v>-0.0991152822971344</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.2639521956443787</v>
+        <v>0.5176800489425659</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.1781814992427826</v>
+        <v>-0.1363761872053146</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1208892688155174</v>
+        <v>-0.08250980079174042</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.08101175725460052</v>
+        <v>0.1400194764137268</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.7230228185653687</v>
+        <v>-0.6610205769538879</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.1471943706274033</v>
+        <v>-0.1540485173463821</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.09038117527961731</v>
+        <v>0.5368000864982605</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.08718881756067276</v>
+        <v>0.1202109009027481</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.04761424288153648</v>
+        <v>0.322587251663208</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.1249570921063423</v>
+        <v>0.3793207705020905</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.02517778985202312</v>
+        <v>-0.3188237249851227</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.1746312826871872</v>
+        <v>0.09485311061143875</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.2051965594291687</v>
+        <v>-0.2218863070011139</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.2465875148773193</v>
+        <v>0.09283088147640228</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.5172117948532104</v>
+        <v>0.2595508992671967</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.2058839797973633</v>
+        <v>0.6239100098609924</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.28225177526474</v>
+        <v>-0.3303124606609344</v>
       </c>
       <c r="AY2" t="n">
         <v>1</v>
@@ -842,154 +842,154 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.2607400715351105</v>
+        <v>0.1850292533636093</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.7429633736610413</v>
+        <v>-0.3464216887950897</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08398856222629547</v>
+        <v>0.08025778084993362</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.4700574576854706</v>
+        <v>-0.1977645754814148</v>
       </c>
       <c r="E3" t="n">
-        <v>0.159291073679924</v>
+        <v>-0.06273042410612106</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4384904205799103</v>
+        <v>0.383264034986496</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1659969091415405</v>
+        <v>0.4460089504718781</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1062516197562218</v>
+        <v>0.4397930800914764</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4282546639442444</v>
+        <v>-0.03763717412948608</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008421625010669231</v>
+        <v>0.1010002046823502</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1119534894824028</v>
+        <v>-0.234390452504158</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1557355225086212</v>
+        <v>0.2829262316226959</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3227013945579529</v>
+        <v>0.204840824007988</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2293752282857895</v>
+        <v>-0.1843331307172775</v>
       </c>
       <c r="O3" t="n">
-        <v>0.291478157043457</v>
+        <v>0.2635260224342346</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.07834389805793762</v>
+        <v>0.5946188569068909</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2801605463027954</v>
+        <v>0.008407997898757458</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.61661696434021</v>
+        <v>-0.6686176061630249</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.02374829910695553</v>
+        <v>-0.2728115618228912</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1936531215906143</v>
+        <v>-0.3158917129039764</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2525511682033539</v>
+        <v>-0.2090707421302795</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.4789888560771942</v>
+        <v>-0.07248176634311676</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3248719871044159</v>
+        <v>0.4531809687614441</v>
       </c>
       <c r="X3" t="n">
-        <v>0.06840001046657562</v>
+        <v>-0.05587106943130493</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4876037538051605</v>
+        <v>0.6182625293731689</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.01297631114721298</v>
+        <v>-0.1973735243082047</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.2096331119537354</v>
+        <v>0.006990894675254822</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.1148270443081856</v>
+        <v>-0.09716234356164932</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1247165501117706</v>
+        <v>-0.3110160529613495</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.2254936099052429</v>
+        <v>-0.1733469814062119</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.005714231170713902</v>
+        <v>0.3910159766674042</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.4114654064178467</v>
+        <v>-0.02982116118073463</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.3965286612510681</v>
+        <v>-0.04209138453006744</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.3331825733184814</v>
+        <v>0.6688590049743652</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.1034622862935066</v>
+        <v>0.1068000048398972</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.1764350682497025</v>
+        <v>-0.0864860936999321</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.01439967378973961</v>
+        <v>0.1064338535070419</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.779029905796051</v>
+        <v>-0.6308591365814209</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.2222966551780701</v>
+        <v>-0.0235251784324646</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.05198205262422562</v>
+        <v>0.5489651560783386</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.212236762046814</v>
+        <v>0.1885308027267456</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.1172317489981651</v>
+        <v>0.2794070541858673</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.04287764057517052</v>
+        <v>0.5023890137672424</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.05011151731014252</v>
+        <v>-0.2607561945915222</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.06993597745895386</v>
+        <v>0.08400826901197433</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.2501054704189301</v>
+        <v>-0.2796415388584137</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.3071699738502502</v>
+        <v>0.1228652819991112</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.4634707570075989</v>
+        <v>0.1957411020994186</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.2385922223329544</v>
+        <v>0.5430899262428284</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.1275933086872101</v>
+        <v>-0.3687942028045654</v>
       </c>
       <c r="AY3" t="n">
         <v>1</v>
@@ -997,154 +997,154 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0.2851965725421906</v>
+        <v>0.1683632731437683</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.4455805718898773</v>
+        <v>-0.4571258127689362</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1659360080957413</v>
+        <v>-0.02663152292370796</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2772097587585449</v>
+        <v>-0.1582508087158203</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07135864347219467</v>
+        <v>0.08265499025583267</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3258165717124939</v>
+        <v>0.05652280151844025</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1150088757276535</v>
+        <v>0.2816532552242279</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.005745626054704189</v>
+        <v>0.3999314904212952</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4663284420967102</v>
+        <v>-0.09636350721120834</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.006704442203044891</v>
+        <v>0.1240522712469101</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0464642271399498</v>
+        <v>-0.2865742743015289</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1194339469075203</v>
+        <v>0.3007514476776123</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.04811515286564827</v>
+        <v>-0.0061943712644279</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4212293326854706</v>
+        <v>-0.05683185532689095</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1788919121026993</v>
+        <v>0.1174505278468132</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1585516780614853</v>
+        <v>0.1176690757274628</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1777128577232361</v>
+        <v>0.1403962224721909</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.6044647097587585</v>
+        <v>-0.4032581448554993</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1026172116398811</v>
+        <v>-0.06763491779565811</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1040594279766083</v>
+        <v>-0.1671825647354126</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1300135999917984</v>
+        <v>-0.1013456210494041</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3519763648509979</v>
+        <v>0.1320560276508331</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3034533262252808</v>
+        <v>0.1464194357395172</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1689444780349731</v>
+        <v>0.006532632745802402</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4930707216262817</v>
+        <v>0.4542108178138733</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.06547561287879944</v>
+        <v>-0.1359713971614838</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01590987667441368</v>
+        <v>0.07690726220607758</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.002910256385803223</v>
+        <v>-0.1527130156755447</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.02752806805074215</v>
+        <v>-0.2531395554542542</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.07336685061454773</v>
+        <v>0.01524309162050486</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.02232668735086918</v>
+        <v>0.1374882310628891</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.1536982506513596</v>
+        <v>-0.1041924804449081</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.2584252655506134</v>
+        <v>-0.168746143579483</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.2183492183685303</v>
+        <v>0.3209798038005829</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.1630683690309525</v>
+        <v>-0.09614846110343933</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.1362833827733994</v>
+        <v>-0.2714357078075409</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.04840843006968498</v>
+        <v>0.2005123496055603</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.5696082711219788</v>
+        <v>-0.6653673052787781</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.1028088703751564</v>
+        <v>-0.09743987768888474</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.06724578887224197</v>
+        <v>0.4857809245586395</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.01702936366200447</v>
+        <v>0.002658150624483824</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.04875670745968819</v>
+        <v>0.09218760579824448</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.002947199624031782</v>
+        <v>0.3417251408100128</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.1365523487329483</v>
+        <v>-0.2978313863277435</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.2331007868051529</v>
+        <v>0.09231619536876678</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.2929077744483948</v>
+        <v>-0.1188351213932037</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.317444771528244</v>
+        <v>0.1289610117673874</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.3243308067321777</v>
+        <v>0.1870431303977966</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.2391465455293655</v>
+        <v>0.4137458503246307</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.2554647326469421</v>
+        <v>-0.1971857994794846</v>
       </c>
       <c r="AY4" t="n">
         <v>1</v>
@@ -1152,154 +1152,154 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0.3807328641414642</v>
+        <v>0.1940364837646484</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.757359504699707</v>
+        <v>-0.3129012882709503</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2017263472080231</v>
+        <v>0.09910031408071518</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3856419920921326</v>
+        <v>-0.1552012115716934</v>
       </c>
       <c r="E5" t="n">
-        <v>0.14090895652771</v>
+        <v>-0.03950626775622368</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5020096898078918</v>
+        <v>0.2225302755832672</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1039757952094078</v>
+        <v>0.3289180994033813</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.07267353683710098</v>
+        <v>0.650349497795105</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4583375751972198</v>
+        <v>0.05241605266928673</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003629842074587941</v>
+        <v>0.1162301898002625</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1071151569485664</v>
+        <v>-0.1920573264360428</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.08667617291212082</v>
+        <v>0.1482277810573578</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2852366268634796</v>
+        <v>0.2562340497970581</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1494068652391434</v>
+        <v>-0.1783055514097214</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3978273570537567</v>
+        <v>0.2957695722579956</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.03235464170575142</v>
+        <v>0.5019922256469727</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2130731493234634</v>
+        <v>0.06294967979192734</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.6768657565116882</v>
+        <v>-0.607515811920166</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.009998905472457409</v>
+        <v>-0.3842725157737732</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1998831331729889</v>
+        <v>-0.3758305907249451</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2080437839031219</v>
+        <v>-0.2825717628002167</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.4949993491172791</v>
+        <v>-0.1145426332950592</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3142072558403015</v>
+        <v>0.3961154818534851</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1418488472700119</v>
+        <v>0.02264517359435558</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4709171652793884</v>
+        <v>0.6059656739234924</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.1468804478645325</v>
+        <v>-0.2322548776865005</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.173706904053688</v>
+        <v>0.1510953456163406</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.239596962928772</v>
+        <v>-0.1096029877662659</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.2295169979333878</v>
+        <v>-0.2688712477684021</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.2274740487337112</v>
+        <v>-0.1914133876562119</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.08322078734636307</v>
+        <v>0.3432993590831757</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.4131959676742554</v>
+        <v>-0.05687765404582024</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.4512740671634674</v>
+        <v>-0.09791324287652969</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.3545535504817963</v>
+        <v>0.7164478302001953</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.1613670587539673</v>
+        <v>-0.1198196262121201</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.1846732348203659</v>
+        <v>-0.05482566356658936</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.08171994239091873</v>
+        <v>0.0683007538318634</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.7607449889183044</v>
+        <v>-0.5562471747398376</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.1413888782262802</v>
+        <v>-0.1201007962226868</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.03774240240454674</v>
+        <v>0.5499551892280579</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.1953532993793488</v>
+        <v>0.1550974100828171</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.01735339500010014</v>
+        <v>0.4531056880950928</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.08965089172124863</v>
+        <v>0.5262596011161804</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.08412124216556549</v>
+        <v>-0.2868202328681946</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.09021931886672974</v>
+        <v>0.1636751890182495</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.2331555783748627</v>
+        <v>-0.3593288958072662</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.2194082289934158</v>
+        <v>0.153032973408699</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.5701063871383667</v>
+        <v>0.2191263884305954</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.09345061331987381</v>
+        <v>0.7470515966415405</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.1431385278701782</v>
+        <v>-0.3010393977165222</v>
       </c>
       <c r="AY5" t="n">
         <v>1</v>
@@ -1307,154 +1307,154 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0.493979811668396</v>
+        <v>0.2278605103492737</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.906187117099762</v>
+        <v>-0.2639465034008026</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3394304215908051</v>
+        <v>0.07898104190826416</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3037749230861664</v>
+        <v>-0.07950752973556519</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1430048495531082</v>
+        <v>-0.02462229877710342</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4796672463417053</v>
+        <v>0.1459846347570419</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1097825467586517</v>
+        <v>0.3545571565628052</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1977571547031403</v>
+        <v>0.6832776665687561</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4297157824039459</v>
+        <v>0.0207409393042326</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05806911364197731</v>
+        <v>0.0348130539059639</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2233830243349075</v>
+        <v>-0.1724397242069244</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1105020195245743</v>
+        <v>0.2607408463954926</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3041168451309204</v>
+        <v>0.2877028584480286</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1535240113735199</v>
+        <v>-0.2552085518836975</v>
       </c>
       <c r="O6" t="n">
-        <v>0.458317369222641</v>
+        <v>0.2633016705513</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02417317591607571</v>
+        <v>0.4400183260440826</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1195904016494751</v>
+        <v>0.1071834936738014</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.7738772034645081</v>
+        <v>-0.5547100901603699</v>
       </c>
       <c r="S6" t="n">
-        <v>0.07271300256252289</v>
+        <v>-0.445291668176651</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2183335870504379</v>
+        <v>-0.5361383557319641</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2571606636047363</v>
+        <v>-0.3566493093967438</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5687812566757202</v>
+        <v>-0.08064981549978256</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4194035232067108</v>
+        <v>0.3760299384593964</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1578142046928406</v>
+        <v>0.1507463753223419</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4956386089324951</v>
+        <v>0.8388687372207642</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.2064811885356903</v>
+        <v>-0.1746343970298767</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1471113413572311</v>
+        <v>0.2014164924621582</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.3282759487628937</v>
+        <v>-0.08871734142303467</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.4147102534770966</v>
+        <v>-0.1492316126823425</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.2258486598730087</v>
+        <v>-0.105029821395874</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.1477210521697998</v>
+        <v>0.2616086006164551</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.4099305272102356</v>
+        <v>-0.062706358730793</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.4887963533401489</v>
+        <v>-0.02215668186545372</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.3592402338981628</v>
+        <v>0.7198403477668762</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.180294468998909</v>
+        <v>-0.1429449021816254</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.2127759456634521</v>
+        <v>-0.1450579613447189</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.07176738977432251</v>
+        <v>0.1468252688646317</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.7720219492912292</v>
+        <v>-0.4464556574821472</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.1890179812908173</v>
+        <v>-0.1690447628498077</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.1989350765943527</v>
+        <v>0.4963953197002411</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.2573147416114807</v>
+        <v>0.09354862570762634</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.04032082483172417</v>
+        <v>0.342736542224884</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.09117253124713898</v>
+        <v>0.6618887782096863</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.06963425129652023</v>
+        <v>-0.4979900121688843</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.1611543595790863</v>
+        <v>0.2495053261518478</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.2294671535491943</v>
+        <v>-0.4400818049907684</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.3351448774337769</v>
+        <v>0.3220927715301514</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.3520559966564178</v>
+        <v>0.1695329248905182</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.02334628067910671</v>
+        <v>0.9461258053779602</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.1124632135033607</v>
+        <v>-0.2908749282360077</v>
       </c>
       <c r="AY6" t="n">
         <v>1</v>
@@ -1462,154 +1462,154 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0.4416503608226776</v>
+        <v>0.1921965181827545</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.816383421421051</v>
+        <v>-0.3117542862892151</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2310643345117569</v>
+        <v>-0.02945378795266151</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3123792707920074</v>
+        <v>-0.02589725516736507</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1464854180812836</v>
+        <v>-0.02403954230248928</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4033383131027222</v>
+        <v>0.119963102042675</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1376257091760635</v>
+        <v>0.2245929688215256</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.05800968408584595</v>
+        <v>0.5576638579368591</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4083372354507446</v>
+        <v>0.008941702544689178</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.005698347929865122</v>
+        <v>0.09624820947647095</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08976057916879654</v>
+        <v>-0.197742834687233</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.06452414393424988</v>
+        <v>0.1954782903194427</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2631322145462036</v>
+        <v>0.260784238576889</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2106028199195862</v>
+        <v>-0.1631380915641785</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3489574790000916</v>
+        <v>0.2415625005960464</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.01047379989176989</v>
+        <v>0.4466651678085327</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1628014147281647</v>
+        <v>0.1093510538339615</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.660418689250946</v>
+        <v>-0.528525710105896</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.03211230784654617</v>
+        <v>-0.3644881248474121</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2040765285491943</v>
+        <v>-0.3945916295051575</v>
       </c>
       <c r="U7" t="n">
-        <v>0.108354426920414</v>
+        <v>-0.4156752228736877</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.4649358093738556</v>
+        <v>-0.1028088480234146</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3259482979774475</v>
+        <v>0.3561696112155914</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1274779886007309</v>
+        <v>0.1087134778499603</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4749771654605865</v>
+        <v>0.7595949769020081</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.1405873596668243</v>
+        <v>-0.1519279927015305</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.1486401706933975</v>
+        <v>0.1296261847019196</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0.3258440792560577</v>
+        <v>-0.03195216506719589</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.3036745190620422</v>
+        <v>-0.2038550227880478</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.1996991634368896</v>
+        <v>-0.07391920685768127</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.06954924017190933</v>
+        <v>0.3308761119842529</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.3573387563228607</v>
+        <v>-0.04580950736999512</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.4707641899585724</v>
+        <v>-0.08816887438297272</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.3323400616645813</v>
+        <v>0.6651062369346619</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.1337276995182037</v>
+        <v>-0.09898697584867477</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.13520647585392</v>
+        <v>-0.1015320345759392</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.07974254339933395</v>
+        <v>0.09742508083581924</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.6464630961418152</v>
+        <v>-0.5123545527458191</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.172204002737999</v>
+        <v>-0.1971036642789841</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.1412772685289383</v>
+        <v>0.4452703893184662</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.2178712487220764</v>
+        <v>0.1078620478510857</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.03375809267163277</v>
+        <v>0.3623327314853668</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.1038702949881554</v>
+        <v>0.5924463272094727</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.004164182581007481</v>
+        <v>-0.3472417891025543</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.09724362939596176</v>
+        <v>0.2414969652891159</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.172182485461235</v>
+        <v>-0.3106650114059448</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.2119139581918716</v>
+        <v>0.1240334287285805</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.4257508516311646</v>
+        <v>0.2070003002882004</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.1635100096464157</v>
+        <v>0.7238883972167969</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.1113829463720322</v>
+        <v>-0.327737033367157</v>
       </c>
       <c r="AY7" t="n">
         <v>1</v>
@@ -1617,154 +1617,154 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0.3225782811641693</v>
+        <v>0.09864341467618942</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.5031809210777283</v>
+        <v>-0.4378990530967712</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1526766717433929</v>
+        <v>0.01883211545646191</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2753248810768127</v>
+        <v>-0.1931354403495789</v>
       </c>
       <c r="E8" t="n">
-        <v>0.07582160085439682</v>
+        <v>0.02171438559889793</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2768823206424713</v>
+        <v>0.06943138688802719</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1497514098882675</v>
+        <v>0.2305247485637665</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0004157331422902644</v>
+        <v>0.399269700050354</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4734157919883728</v>
+        <v>-0.09751477092504501</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.03046010062098503</v>
+        <v>0.1316075474023819</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.08337230980396271</v>
+        <v>-0.2950939834117889</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1475317031145096</v>
+        <v>0.221948117017746</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1623921245336533</v>
+        <v>-0.09139374643564224</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3317847847938538</v>
+        <v>0.006153854541480541</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1536774039268494</v>
+        <v>0.1196053549647331</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1236855313181877</v>
+        <v>0.09856094419956207</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1787065863609314</v>
+        <v>0.1667946726083755</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.4986359477043152</v>
+        <v>-0.3600623607635498</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1373085975646973</v>
+        <v>-0.06748781353235245</v>
       </c>
       <c r="T8" t="n">
-        <v>0.08016081899404526</v>
+        <v>-0.2609359920024872</v>
       </c>
       <c r="U8" t="n">
-        <v>0.09049596637487411</v>
+        <v>-0.08931419253349304</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3490438461303711</v>
+        <v>0.05944903194904327</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.2921131551265717</v>
+        <v>0.2006426453590393</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1421898603439331</v>
+        <v>0.01201671082526445</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.438051700592041</v>
+        <v>0.3782652914524078</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.02677181549370289</v>
+        <v>-0.1301987171173096</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.01423707231879234</v>
+        <v>0.07420801371335983</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.007325825747102499</v>
+        <v>-0.0800134688615799</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.00304233212955296</v>
+        <v>-0.2502435147762299</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0.09209765493869781</v>
+        <v>0.01285238657146692</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.02224242873489857</v>
+        <v>0.1092912182211876</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.1039642542600632</v>
+        <v>-0.06945441663265228</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.3016222715377808</v>
+        <v>-0.08827181905508041</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0.1662070006132126</v>
+        <v>0.3159633278846741</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.1316977292299271</v>
+        <v>-0.1422532498836517</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.09289585798978806</v>
+        <v>-0.1997995525598526</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.01766087859869003</v>
+        <v>0.230830579996109</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.583210825920105</v>
+        <v>-0.7088858485221863</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0.1449975818395615</v>
+        <v>-0.09357374906539917</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.1043941080570221</v>
+        <v>0.4090297818183899</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.02221334539353848</v>
+        <v>0.02769941277801991</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.1085151061415672</v>
+        <v>0.1106237024068832</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.09489854425191879</v>
+        <v>0.293301522731781</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.1409794688224792</v>
+        <v>-0.2914654612541199</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.2621213495731354</v>
+        <v>0.1127901673316956</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.2030261754989624</v>
+        <v>-0.05655401572585106</v>
       </c>
       <c r="AU8" t="n">
-        <v>-0.3110019862651825</v>
+        <v>0.07957623898983002</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.3297373056411743</v>
+        <v>0.2155064642429352</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.180753618478775</v>
+        <v>0.4531822502613068</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.2521210908889771</v>
+        <v>-0.1400676965713501</v>
       </c>
       <c r="AY8" t="n">
         <v>1</v>
@@ -1772,154 +1772,154 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0.4139147996902466</v>
+        <v>0.1711422950029373</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.7954563498497009</v>
+        <v>-0.3841588497161865</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2061206698417664</v>
+        <v>0.07004831731319427</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3564907014369965</v>
+        <v>-0.1820449233055115</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03119701147079468</v>
+        <v>-0.07219139486551285</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5226585268974304</v>
+        <v>0.1731982231140137</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1192100197076797</v>
+        <v>0.3342738449573517</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1102196723222733</v>
+        <v>0.5731635689735413</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.456668496131897</v>
+        <v>0.02759440056979656</v>
       </c>
       <c r="J9" t="n">
-        <v>0.005593256093561649</v>
+        <v>0.1141326278448105</v>
       </c>
       <c r="K9" t="n">
-        <v>0.07819119840860367</v>
+        <v>-0.1976532340049744</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.06085779145359993</v>
+        <v>0.150407686829567</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2880086600780487</v>
+        <v>0.2294432371854782</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1984082758426666</v>
+        <v>-0.1508919447660446</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3766690790653229</v>
+        <v>0.3193156719207764</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.07757074385881424</v>
+        <v>0.4890757203102112</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1740548759698868</v>
+        <v>0.06330053508281708</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.7191902995109558</v>
+        <v>-0.6419397592544556</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02665557526051998</v>
+        <v>-0.4396404922008514</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2353903651237488</v>
+        <v>-0.3629885911941528</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1718743890523911</v>
+        <v>-0.3064591288566589</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5095469951629639</v>
+        <v>-0.04336409643292427</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3141758143901825</v>
+        <v>0.3759046494960785</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1589548140764236</v>
+        <v>0.09138380736112595</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.524151086807251</v>
+        <v>0.67995285987854</v>
       </c>
       <c r="Z9" t="n">
-        <v>-0.1334067732095718</v>
+        <v>-0.2215172201395035</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.2399897873401642</v>
+        <v>0.1779483705759048</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0.1904216110706329</v>
+        <v>-0.1579791605472565</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1987936645746231</v>
+        <v>-0.223156675696373</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.2539132237434387</v>
+        <v>-0.1351024806499481</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.06550928950309753</v>
+        <v>0.3470567762851715</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.3618475198745728</v>
+        <v>-0.0359446294605732</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.4505641758441925</v>
+        <v>0.01375612895935774</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0.3626830875873566</v>
+        <v>0.6498700976371765</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.1731360703706741</v>
+        <v>-0.190811350941658</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.1968348920345306</v>
+        <v>-0.04473473131656647</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.1072264611721039</v>
+        <v>0.1092428117990494</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.7659903764724731</v>
+        <v>-0.5590247511863708</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.1342098116874695</v>
+        <v>-0.1240042671561241</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.03292392939329147</v>
+        <v>0.5628970861434937</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.1879492998123169</v>
+        <v>0.1643178313970566</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.03861472010612488</v>
+        <v>0.3953454494476318</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.04123151674866676</v>
+        <v>0.5069454312324524</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.001804073457606137</v>
+        <v>-0.3307529985904694</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.1272266060113907</v>
+        <v>0.09044694900512695</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.2589588463306427</v>
+        <v>-0.351396918296814</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.2364661991596222</v>
+        <v>0.1682498902082443</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.5444678068161011</v>
+        <v>0.2854860424995422</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.07831430435180664</v>
+        <v>0.7704437971115112</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.1609886139631271</v>
+        <v>-0.3333644568920135</v>
       </c>
       <c r="AY9" t="n">
         <v>1</v>
@@ -1927,154 +1927,154 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0.4474331736564636</v>
+        <v>0.08497323095798492</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.65813148021698</v>
+        <v>-0.3622755110263824</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2220528423786163</v>
+        <v>0.1269651800394058</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2422275245189667</v>
+        <v>-0.02180688455700874</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1672690361738205</v>
+        <v>-0.1017981320619583</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4392707347869873</v>
+        <v>0.1682167500257492</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1399498134851456</v>
+        <v>0.3186686336994171</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1286080479621887</v>
+        <v>0.5992261171340942</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4197312891483307</v>
+        <v>0.04116793349385262</v>
       </c>
       <c r="J10" t="n">
-        <v>0.05497275665402412</v>
+        <v>0.02945589646697044</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1239662021398544</v>
+        <v>-0.1965936124324799</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.08470830321311951</v>
+        <v>0.1895763278007507</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2831909358501434</v>
+        <v>0.1248552054166794</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3082621693611145</v>
+        <v>-0.1354023218154907</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3374238610267639</v>
+        <v>0.2588875591754913</v>
       </c>
       <c r="P10" t="n">
-        <v>0.07007688283920288</v>
+        <v>0.2536818087100983</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0265588816255331</v>
+        <v>0.1097049415111542</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.6087594032287598</v>
+        <v>-0.5004593729972839</v>
       </c>
       <c r="S10" t="n">
-        <v>0.04668018966913223</v>
+        <v>-0.2333022058010101</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2185011655092239</v>
+        <v>-0.3994410634040833</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1813826262950897</v>
+        <v>-0.2541222274303436</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.4481462836265564</v>
+        <v>-0.07920093834400177</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3399818539619446</v>
+        <v>0.3227469623088837</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2206493765115738</v>
+        <v>0.02413146942853928</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4475933909416199</v>
+        <v>0.5136481523513794</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.1335562914609909</v>
+        <v>-0.2046569883823395</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.1624075323343277</v>
+        <v>0.1574541032314301</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.1332186460494995</v>
+        <v>-0.1877672672271729</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1814530938863754</v>
+        <v>-0.1242010742425919</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.2046146541833878</v>
+        <v>-0.07892884314060211</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.05404436215758324</v>
+        <v>0.2342083156108856</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.2987118065357208</v>
+        <v>0.0217208880931139</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.4648769795894623</v>
+        <v>-0.03971148282289505</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.1857080310583115</v>
+        <v>0.5348752737045288</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.2078747749328613</v>
+        <v>-0.1658933907747269</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.1269083619117737</v>
+        <v>-0.1139752864837646</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.1643454730510712</v>
+        <v>0.2556123435497284</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.6727087497711182</v>
+        <v>-0.5645075440406799</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.1724907755851746</v>
+        <v>-0.1180269569158554</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.01558991428464651</v>
+        <v>0.446044921875</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.04083799198269844</v>
+        <v>0.02811296470463276</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.00112455862108618</v>
+        <v>0.2759655714035034</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.1057601943612099</v>
+        <v>0.4667892158031464</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.05077983066439629</v>
+        <v>-0.3500246405601501</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.1558593660593033</v>
+        <v>0.1100245267152786</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.2469978481531143</v>
+        <v>-0.2902041077613831</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.3335477113723755</v>
+        <v>0.2639221251010895</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.4485160708427429</v>
+        <v>0.1786880791187286</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.04956324025988579</v>
+        <v>0.7662691473960876</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.2139402776956558</v>
+        <v>-0.2289314866065979</v>
       </c>
       <c r="AY10" t="n">
         <v>1</v>
@@ -2082,154 +2082,154 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.3375508189201355</v>
+        <v>0.24405637383461</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.9660824537277222</v>
+        <v>-0.1946968734264374</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4393262267112732</v>
+        <v>0.1739061176776886</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.284423828125</v>
+        <v>-0.1881438344717026</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1739552468061447</v>
+        <v>-0.08966587483882904</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5529510378837585</v>
+        <v>0.1160827204585075</v>
       </c>
       <c r="G11" t="n">
-        <v>0.04933826997876167</v>
+        <v>0.3202769458293915</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.05486749857664108</v>
+        <v>0.5924068093299866</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4792252779006958</v>
+        <v>-0.1503993719816208</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.004477648064494133</v>
+        <v>0.2445359528064728</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1878903657197952</v>
+        <v>-0.04505839571356773</v>
       </c>
       <c r="L11" t="n">
-        <v>0.004350845701992512</v>
+        <v>0.2861150205135345</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4491163790225983</v>
+        <v>0.3277485966682434</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1775009781122208</v>
+        <v>-0.2004914581775665</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4607645869255066</v>
+        <v>0.4545537531375885</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.06019533798098564</v>
+        <v>0.6100082397460938</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1383921355009079</v>
+        <v>0.1084774509072304</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.7992656826972961</v>
+        <v>-0.6291171312332153</v>
       </c>
       <c r="S11" t="n">
-        <v>0.02028290554881096</v>
+        <v>-0.5748024582862854</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1847085505723953</v>
+        <v>-0.4297335147857666</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2871144413948059</v>
+        <v>-0.3964443802833557</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7274510860443115</v>
+        <v>-0.1306902468204498</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.4619045555591583</v>
+        <v>0.2875201106071472</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1527691334486008</v>
+        <v>0.230459913611412</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4879476130008698</v>
+        <v>0.9952514171600342</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.2279496788978577</v>
+        <v>-0.1072618141770363</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.2720246016979218</v>
+        <v>0.2516515254974365</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.3573585748672485</v>
+        <v>-0.1625591516494751</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.4697335660457611</v>
+        <v>-0.2234653383493423</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.2255748957395554</v>
+        <v>-0.1400629281997681</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.1878692060709</v>
+        <v>0.416235089302063</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.5594081878662109</v>
+        <v>-0.1327896267175674</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.6427844166755676</v>
+        <v>-0.06032919138669968</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0.4525806307792664</v>
+        <v>0.9051670432090759</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.1253995150327682</v>
+        <v>-0.1476999372243881</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.2920138537883759</v>
+        <v>-0.117171086370945</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.0007775829290039837</v>
+        <v>0.02534155175089836</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.8351773023605347</v>
+        <v>-0.5811840891838074</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0.1597317159175873</v>
+        <v>-0.230699747800827</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.3155811131000519</v>
+        <v>0.5159345865249634</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.4004271030426025</v>
+        <v>0.2293090969324112</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.02200699225068092</v>
+        <v>0.5358097553253174</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.05750659480690956</v>
+        <v>0.8202806711196899</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.01011199876666069</v>
+        <v>-0.4010699987411499</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.1128322705626488</v>
+        <v>0.1973160058259964</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.2167607098817825</v>
+        <v>-0.4794276654720306</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.2600299119949341</v>
+        <v>0.3968050479888916</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.364639550447464</v>
+        <v>0.1402915865182877</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.03310070186853409</v>
+        <v>0.9474507570266724</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.0586516298353672</v>
+        <v>-0.3638350069522858</v>
       </c>
       <c r="AY11" t="n">
         <v>1</v>
@@ -2237,154 +2237,154 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-0.2730807065963745</v>
+        <v>0.1071525514125824</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.7005878090858459</v>
+        <v>-0.5521482825279236</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3422141969203949</v>
+        <v>0.1650201380252838</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0006083181360736489</v>
+        <v>0.2275007516145706</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3125644326210022</v>
+        <v>0.003904419718310237</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1933600455522537</v>
+        <v>0.1614699959754944</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1234471425414085</v>
+        <v>0.3911300599575043</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1356116384267807</v>
+        <v>0.7978819012641907</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7128939628601074</v>
+        <v>-0.2705374360084534</v>
       </c>
       <c r="J12" t="n">
-        <v>0.01038550399243832</v>
+        <v>0.1218837648630142</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3221528232097626</v>
+        <v>-0.002937082434073091</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.1619267910718918</v>
+        <v>0.4555912017822266</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2514184713363647</v>
+        <v>-0.10798579454422</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5086818337440491</v>
+        <v>-0.05707670003175735</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4223620891571045</v>
+        <v>0.2042685002088547</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1439007073640823</v>
+        <v>0.03258975595235825</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.01473435573279858</v>
+        <v>-0.01050608232617378</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.4910756945610046</v>
+        <v>-0.688079297542572</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1294562369585037</v>
+        <v>-0.09970565885305405</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4775163531303406</v>
+        <v>-0.3590089976787567</v>
       </c>
       <c r="U12" t="n">
-        <v>0.198214203119278</v>
+        <v>-0.3128120005130768</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3368191123008728</v>
+        <v>-0.205104872584343</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3160361051559448</v>
+        <v>0.06641568243503571</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3950160145759583</v>
+        <v>0.2155610024929047</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.613580048084259</v>
+        <v>0.5951082110404968</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.01350946631282568</v>
+        <v>-0.1555963903665543</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1444632112979889</v>
+        <v>-0.03320716693997383</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0.2933333218097687</v>
+        <v>-0.3982686400413513</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.04942192509770393</v>
+        <v>-0.2265024185180664</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0.09333343803882599</v>
+        <v>-0.02875754237174988</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.1255511045455933</v>
+        <v>0.08414715528488159</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.2768644094467163</v>
+        <v>-0.0763743594288826</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.3785906434059143</v>
+        <v>-0.2011511921882629</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.1631979197263718</v>
+        <v>0.5330318212509155</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.1573414355516434</v>
+        <v>0.03989027440547943</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.1452436745166779</v>
+        <v>-0.1070671305060387</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.02660147473216057</v>
+        <v>0.4034883975982666</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.6000322699546814</v>
+        <v>-0.6507136821746826</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0.05802979692816734</v>
+        <v>0.004412932321429253</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.1166555732488632</v>
+        <v>0.3606606721878052</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.1710294932126999</v>
+        <v>0.2757435142993927</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.01509209908545017</v>
+        <v>0.08715543895959854</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.1004811748862267</v>
+        <v>0.4642923474311829</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.02525816857814789</v>
+        <v>-0.3829703330993652</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.2894142270088196</v>
+        <v>0.2289682924747467</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.207002729177475</v>
+        <v>-0.2570610046386719</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.3282931745052338</v>
+        <v>0.2165772467851639</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.3926712572574615</v>
+        <v>0.3597600162029266</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.2754518389701843</v>
+        <v>0.5990634560585022</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.3187676966190338</v>
+        <v>-0.4118400812149048</v>
       </c>
       <c r="AY12" t="n">
         <v>1</v>
@@ -2392,154 +2392,154 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-0.2613119184970856</v>
+        <v>0.1191664785146713</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.5231353640556335</v>
+        <v>-0.4254688024520874</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1445508003234863</v>
+        <v>-0.0189250111579895</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2549810409545898</v>
+        <v>-0.1380249261856079</v>
       </c>
       <c r="E13" t="n">
-        <v>0.07698151469230652</v>
+        <v>0.02735267020761967</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2328624427318573</v>
+        <v>0.1426717787981033</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2497898936271667</v>
+        <v>0.2497856020927429</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0626460462808609</v>
+        <v>0.3978517949581146</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4992201626300812</v>
+        <v>-0.1556874364614487</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01503492891788483</v>
+        <v>-0.003555115545168519</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.005216008983552456</v>
+        <v>-0.2047477215528488</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.08261369168758392</v>
+        <v>0.3414939343929291</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1879062801599503</v>
+        <v>-0.02432167530059814</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3504605889320374</v>
+        <v>0.02535818889737129</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1752933263778687</v>
+        <v>0.1550549119710922</v>
       </c>
       <c r="P13" t="n">
-        <v>0.118165947496891</v>
+        <v>0.1943991184234619</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1053741574287415</v>
+        <v>0.0929461270570755</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.5106444358825684</v>
+        <v>-0.5057937502861023</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1168060526251793</v>
+        <v>-0.02952056191861629</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1465958952903748</v>
+        <v>-0.2371190190315247</v>
       </c>
       <c r="U13" t="n">
-        <v>0.08906036615371704</v>
+        <v>-0.124426856637001</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3657196462154388</v>
+        <v>-0.02366991341114044</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.2308162003755569</v>
+        <v>0.1891030520200729</v>
       </c>
       <c r="X13" t="n">
-        <v>0.2027848213911057</v>
+        <v>0.004918903112411499</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.4851996004581451</v>
+        <v>0.4615930914878845</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.04705247282981873</v>
+        <v>-0.1113287433981895</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.04771599173545837</v>
+        <v>-0.01064574532210827</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0.103361688554287</v>
+        <v>-0.1579754054546356</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.06139229610562325</v>
+        <v>-0.2252887189388275</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.1448692381381989</v>
+        <v>0.02213728986680508</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.01643037796020508</v>
+        <v>0.179812103509903</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.1230861693620682</v>
+        <v>-0.08440753072500229</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.3050646185874939</v>
+        <v>-0.1639924198389053</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0.184575691819191</v>
+        <v>0.3622800409793854</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.1562591791152954</v>
+        <v>-0.06648817658424377</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.1294735968112946</v>
+        <v>-0.2516123056411743</v>
       </c>
       <c r="AK13" t="n">
-        <v>-0.01021974720060825</v>
+        <v>0.2334054112434387</v>
       </c>
       <c r="AL13" t="n">
-        <v>-0.6486862301826477</v>
+        <v>-0.6556451916694641</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0.207745686173439</v>
+        <v>-0.1034595295786858</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.1018159464001656</v>
+        <v>0.5100148320198059</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.08697208017110825</v>
+        <v>0.0295079629868269</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.01158058177679777</v>
+        <v>0.07313355803489685</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.04092271998524666</v>
+        <v>0.3032390177249908</v>
       </c>
       <c r="AR13" t="n">
-        <v>-0.08876791596412659</v>
+        <v>-0.290522962808609</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.224977120757103</v>
+        <v>0.1635661870241165</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.261923760175705</v>
+        <v>-0.04593648388981819</v>
       </c>
       <c r="AU13" t="n">
-        <v>-0.2514935731887817</v>
+        <v>0.1170993968844414</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.3620445132255554</v>
+        <v>0.2309735268354416</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.2843128442764282</v>
+        <v>0.4067554473876953</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.2134806364774704</v>
+        <v>-0.2161498069763184</v>
       </c>
       <c r="AY13" t="n">
         <v>1</v>
@@ -2547,154 +2547,154 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-0.2547828853130341</v>
+        <v>0.164233610033989</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.6066038012504578</v>
+        <v>-0.4657070934772491</v>
       </c>
       <c r="C14" t="n">
-        <v>0.07182101160287857</v>
+        <v>-0.09092172235250473</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2177480906248093</v>
+        <v>-0.2464614808559418</v>
       </c>
       <c r="E14" t="n">
-        <v>0.05669759586453438</v>
+        <v>-0.002395020797848701</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2057691663503647</v>
+        <v>0.1724375784397125</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1627142280340195</v>
+        <v>0.1331232935190201</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.06816729158163071</v>
+        <v>0.250923216342926</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5165308713912964</v>
+        <v>-0.05297998338937759</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0134208295494318</v>
+        <v>0.08008851110935211</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1042021885514259</v>
+        <v>-0.4117357730865479</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1455634832382202</v>
+        <v>0.2982370853424072</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1961170136928558</v>
+        <v>0.01551439892500639</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3651078343391418</v>
+        <v>0.04305016994476318</v>
       </c>
       <c r="O14" t="n">
-        <v>0.07209537923336029</v>
+        <v>0.2031764835119247</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1323836743831635</v>
+        <v>0.3181457221508026</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.04543334990739822</v>
+        <v>0.1074774265289307</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.4247362315654755</v>
+        <v>-0.6311184167861938</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1552666276693344</v>
+        <v>-0.09245475381612778</v>
       </c>
       <c r="T14" t="n">
-        <v>0.170393317937851</v>
+        <v>-0.1487922966480255</v>
       </c>
       <c r="U14" t="n">
-        <v>0.04831976071000099</v>
+        <v>-0.08322994410991669</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3902647495269775</v>
+        <v>0.06197793036699295</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.2542801797389984</v>
+        <v>0.1353800445795059</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1195204257965088</v>
+        <v>-0.01346053555607796</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.4191282093524933</v>
+        <v>0.4461658596992493</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.1939878761768341</v>
+        <v>-0.08878623694181442</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.09618275612592697</v>
+        <v>-0.005183362402021885</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0.09833892434835434</v>
+        <v>-0.06023889780044556</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.06215251982212067</v>
+        <v>-0.2471766769886017</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.1262590885162354</v>
+        <v>0.03600959479808807</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.03389152884483337</v>
+        <v>0.2150258123874664</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.04714059084653854</v>
+        <v>0.002239152323454618</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.2701911926269531</v>
+        <v>-0.4011681079864502</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0.2043799608945847</v>
+        <v>0.3091607689857483</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.1428331732749939</v>
+        <v>0.172042652964592</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.09637120366096497</v>
+        <v>-0.2894898056983948</v>
       </c>
       <c r="AK14" t="n">
-        <v>-0.06292053312063217</v>
+        <v>0.3144257068634033</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.7402031421661377</v>
+        <v>-0.7220552563667297</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0.3222865164279938</v>
+        <v>-0.2007157057523727</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.1799633204936981</v>
+        <v>0.5451114177703857</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.1333829760551453</v>
+        <v>-0.04328655824065208</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.0003438584681134671</v>
+        <v>0.1467027068138123</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0.01962794549763203</v>
+        <v>0.1101912185549736</v>
       </c>
       <c r="AR14" t="n">
-        <v>-0.1266440004110336</v>
+        <v>-0.1159553155303001</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.1808559596538544</v>
+        <v>0.179841086268425</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.2619926631450653</v>
+        <v>-0.09221994876861572</v>
       </c>
       <c r="AU14" t="n">
-        <v>-0.1513707339763641</v>
+        <v>0.05671792477369308</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.3715340793132782</v>
+        <v>0.2442654371261597</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.3724202513694763</v>
+        <v>0.3783586025238037</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.2288597375154495</v>
+        <v>-0.2240022420883179</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
@@ -2702,154 +2702,154 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0.5321901440620422</v>
+        <v>0.1426237821578979</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.7698443531990051</v>
+        <v>-0.3743588328361511</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3354141712188721</v>
+        <v>0.1814415156841278</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1908564567565918</v>
+        <v>0.03876461088657379</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1618697792291641</v>
+        <v>-0.06837023794651031</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4702095985412598</v>
+        <v>0.1046431586146355</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1638767868280411</v>
+        <v>0.3669987618923187</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1418881714344025</v>
+        <v>0.7681641578674316</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4460492432117462</v>
+        <v>0.08150316029787064</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01078507862985134</v>
+        <v>0.02391495183110237</v>
       </c>
       <c r="K15" t="n">
-        <v>0.245273545384407</v>
+        <v>-0.1492236405611038</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1271140575408936</v>
+        <v>0.2091661989688873</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2749888300895691</v>
+        <v>0.2014852613210678</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2682514488697052</v>
+        <v>-0.2529685795307159</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4310911595821381</v>
+        <v>0.2814728915691376</v>
       </c>
       <c r="P15" t="n">
-        <v>0.02270253375172615</v>
+        <v>0.230613186955452</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.02513799630105495</v>
+        <v>0.1424751132726669</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.6976146697998047</v>
+        <v>-0.5456969738006592</v>
       </c>
       <c r="S15" t="n">
-        <v>0.03168747946619987</v>
+        <v>-0.3245652318000793</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3089123070240021</v>
+        <v>-0.5573821067810059</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2409220039844513</v>
+        <v>-0.3700031936168671</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5515319108963013</v>
+        <v>-0.0854196697473526</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3766395151615143</v>
+        <v>0.3758849501609802</v>
       </c>
       <c r="X15" t="n">
-        <v>0.273463636636734</v>
+        <v>0.1127391085028648</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.429436057806015</v>
+        <v>0.6694658398628235</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.1847981363534927</v>
+        <v>-0.18152916431427</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.1483597755432129</v>
+        <v>0.2843708097934723</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.2548723816871643</v>
+        <v>-0.1760848611593246</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.2936737239360809</v>
+        <v>-0.0623399056494236</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.23673115670681</v>
+        <v>-0.08775618672370911</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.1540604829788208</v>
+        <v>0.2651008367538452</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.342015266418457</v>
+        <v>-0.03826932981610298</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.5286678075790405</v>
+        <v>-0.008715644478797913</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0.2902235686779022</v>
+        <v>0.6618689894676208</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.238229364156723</v>
+        <v>-0.2253248393535614</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.1521879285573959</v>
+        <v>-0.08485569059848785</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.2230032086372375</v>
+        <v>0.2399898320436478</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.6557019948959351</v>
+        <v>-0.5241069197654724</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0.1223338171839714</v>
+        <v>-0.1370528340339661</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0.1513804793357849</v>
+        <v>0.4305316805839539</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.0933128297328949</v>
+        <v>0.0945713147521019</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.05911421403288841</v>
+        <v>0.3990796208381653</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.159361869096756</v>
+        <v>0.6060326099395752</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.02691600471735001</v>
+        <v>-0.4559069275856018</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.1754450798034668</v>
+        <v>0.213153138756752</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.2875502407550812</v>
+        <v>-0.3822040259838104</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0.3418180644512177</v>
+        <v>0.274076372385025</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.4779697060585022</v>
+        <v>0.1696903258562088</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0.06491195410490036</v>
+        <v>0.9255847930908203</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.1439388394355774</v>
+        <v>-0.2285318076610565</v>
       </c>
       <c r="AY15" t="n">
         <v>1</v>
@@ -2857,154 +2857,154 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-0.4325193166732788</v>
+        <v>0.06912096589803696</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.7314843535423279</v>
+        <v>-0.2898992002010345</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3994533121585846</v>
+        <v>0.3038901388645172</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0606086254119873</v>
+        <v>0.08007676154375076</v>
       </c>
       <c r="E16" t="n">
-        <v>0.245400458574295</v>
+        <v>-0.1576236933469772</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4495263993740082</v>
+        <v>0.1824166625738144</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1302728801965714</v>
+        <v>0.347881019115448</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.02374671772122383</v>
+        <v>0.8014218807220459</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5171656608581543</v>
+        <v>-0.06761849671602249</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.01661830209195614</v>
+        <v>0.03420696407556534</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2569244205951691</v>
+        <v>-0.08161488175392151</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.06467969715595245</v>
+        <v>0.3042302131652832</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4332745373249054</v>
+        <v>0.1508762836456299</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3344403207302094</v>
+        <v>-0.1288128942251205</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4225142896175385</v>
+        <v>0.2994835078716278</v>
       </c>
       <c r="P16" t="n">
-        <v>0.007324031554162502</v>
+        <v>0.1937379091978073</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.06433704495429993</v>
+        <v>0.2334839552640915</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.6669290065765381</v>
+        <v>-0.5393190979957581</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0104838190600276</v>
+        <v>-0.2516009211540222</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2599375545978546</v>
+        <v>-0.5112540125846863</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2527923882007599</v>
+        <v>-0.3750847280025482</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6605742573738098</v>
+        <v>-0.2183811664581299</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3336359560489655</v>
+        <v>0.4076108038425446</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3664111196994781</v>
+        <v>0.08740664273500443</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.4886379241943359</v>
+        <v>0.6746468544006348</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.2935959696769714</v>
+        <v>-0.0855419933795929</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.2247807830572128</v>
+        <v>0.3364306390285492</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0.4028478562831879</v>
+        <v>-0.2027004510164261</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.2882621884346008</v>
+        <v>-0.1192047968506813</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.2050565034151077</v>
+        <v>-0.1483189612627029</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.2304985821247101</v>
+        <v>0.3266328871250153</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.3212055861949921</v>
+        <v>0.001253773458302021</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.6568717360496521</v>
+        <v>-0.09815116971731186</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0.2344813793897629</v>
+        <v>0.7643955945968628</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0.3291937112808228</v>
+        <v>-0.2721062004566193</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.1201283410191536</v>
+        <v>-0.0298349279910326</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.1707227230072021</v>
+        <v>0.2265354841947556</v>
       </c>
       <c r="AL16" t="n">
-        <v>-0.7110710740089417</v>
+        <v>-0.6852237582206726</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0.08155689388513565</v>
+        <v>-0.1736512780189514</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0.1778042167425156</v>
+        <v>0.3846175074577332</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.09874475747346878</v>
+        <v>0.1484205424785614</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.04058185592293739</v>
+        <v>0.4321666359901428</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.1401349902153015</v>
+        <v>0.6900471448898315</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.02423268556594849</v>
+        <v>-0.4254798889160156</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.2177857011556625</v>
+        <v>0.2486692816019058</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.2829199433326721</v>
+        <v>-0.3059494197368622</v>
       </c>
       <c r="AU16" t="n">
-        <v>-0.2581605017185211</v>
+        <v>0.2388234883546829</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.556733250617981</v>
+        <v>0.186065599322319</v>
       </c>
       <c r="AW16" t="n">
-        <v>-0.04102391004562378</v>
+        <v>0.8823845386505127</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.1394631713628769</v>
+        <v>-0.2102840095758438</v>
       </c>
       <c r="AY16" t="n">
         <v>1</v>
@@ -3012,154 +3012,154 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-0.2475138008594513</v>
+        <v>0.06951385736465454</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.5033755898475647</v>
+        <v>-0.3481281995773315</v>
       </c>
       <c r="C17" t="n">
-        <v>0.03592019900679588</v>
+        <v>-0.01925470493733883</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3572044372558594</v>
+        <v>-0.1322544664144516</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1747307926416397</v>
+        <v>-0.08292411267757416</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3871159553527832</v>
+        <v>0.1704597622156143</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2517033219337463</v>
+        <v>0.1306590586900711</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.01464415993541479</v>
+        <v>0.3616832494735718</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.534101128578186</v>
+        <v>0.03746540099382401</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1172799468040466</v>
+        <v>0.08173005282878876</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0512021966278553</v>
+        <v>-0.2173984497785568</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0604536309838295</v>
+        <v>0.2739624977111816</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2775986790657043</v>
+        <v>0.03650309517979622</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3193204700946808</v>
+        <v>0.08143918216228485</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1872263103723526</v>
+        <v>0.2011481672525406</v>
       </c>
       <c r="P17" t="n">
-        <v>0.02199131064116955</v>
+        <v>0.3222199380397797</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.01393399853259325</v>
+        <v>0.001658572815358639</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.6138084530830383</v>
+        <v>-0.6862335801124573</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0243950430303812</v>
+        <v>-0.1239704042673111</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1612604707479477</v>
+        <v>-0.2395332306623459</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2534134685993195</v>
+        <v>-0.2177287191152573</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2882253229618073</v>
+        <v>-0.04379918426275253</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.2969545125961304</v>
+        <v>0.2215800881385803</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1159782260656357</v>
+        <v>-0.07143808901309967</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.4903362691402435</v>
+        <v>0.3602445423603058</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.1097507178783417</v>
+        <v>-0.1185148730874062</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.02825292199850082</v>
+        <v>0.01434329152107239</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.06645920872688293</v>
+        <v>-0.04855808988213539</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.1150650009512901</v>
+        <v>-0.1806831806898117</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0.2908926904201508</v>
+        <v>-0.07397054135799408</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.04005397111177444</v>
+        <v>0.3004694581031799</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.09726455062627792</v>
+        <v>-0.1148023530840874</v>
       </c>
       <c r="AG17" t="n">
-        <v>-0.3435677587985992</v>
+        <v>-0.2593441009521484</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.1909526437520981</v>
+        <v>0.4215258061885834</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0.08186401426792145</v>
+        <v>-0.02974553406238556</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.01443094108253717</v>
+        <v>-0.01869074627757072</v>
       </c>
       <c r="AK17" t="n">
-        <v>-0.01627375744283199</v>
+        <v>0.230677917599678</v>
       </c>
       <c r="AL17" t="n">
-        <v>-0.7212452292442322</v>
+        <v>-0.7499410510063171</v>
       </c>
       <c r="AM17" t="n">
-        <v>-0.2610554993152618</v>
+        <v>-0.02854875475168228</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.1884196698665619</v>
+        <v>0.5150889158248901</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.1330987960100174</v>
+        <v>0.03003609739243984</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.04411675781011581</v>
+        <v>0.3831888437271118</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.227220356464386</v>
+        <v>0.07872846722602844</v>
       </c>
       <c r="AR17" t="n">
-        <v>-0.003119871951639652</v>
+        <v>-0.3188729584217072</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.1487824469804764</v>
+        <v>0.1878942400217056</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.09950406849384308</v>
+        <v>-0.1721044480800629</v>
       </c>
       <c r="AU17" t="n">
-        <v>-0.1259386986494064</v>
+        <v>0.05594746768474579</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.4077855348587036</v>
+        <v>0.2046835422515869</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.2564958333969116</v>
+        <v>0.5663962364196777</v>
       </c>
       <c r="AX17" t="n">
-        <v>-0.233748123049736</v>
+        <v>-0.3159470856189728</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3167,154 +3167,154 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-0.4989888072013855</v>
+        <v>0.09800483286380768</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.724574089050293</v>
+        <v>-0.3382270038127899</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3570743203163147</v>
+        <v>0.19097039103508</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.156210795044899</v>
+        <v>0.06712454557418823</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1960915774106979</v>
+        <v>-0.09156473726034164</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4394429624080658</v>
+        <v>0.08551272749900818</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1430689841508865</v>
+        <v>0.3539985716342926</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.07446428388357162</v>
+        <v>0.7400625348091125</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4554681777954102</v>
+        <v>0.04173965007066727</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.01614984124898911</v>
+        <v>0.06249477714300156</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2066527903079987</v>
+        <v>-0.1364602893590927</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1116250231862068</v>
+        <v>0.2175638824701309</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2904110252857208</v>
+        <v>0.176162987947464</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2731943130493164</v>
+        <v>-0.1863823086023331</v>
       </c>
       <c r="O18" t="n">
-        <v>0.425447553396225</v>
+        <v>0.2978730201721191</v>
       </c>
       <c r="P18" t="n">
-        <v>0.05703706666827202</v>
+        <v>0.2197211086750031</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.02528475970029831</v>
+        <v>0.168969988822937</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.6553663611412048</v>
+        <v>-0.5140895843505859</v>
       </c>
       <c r="S18" t="n">
-        <v>0.03938329219818115</v>
+        <v>-0.3070613741874695</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2769514322280884</v>
+        <v>-0.5139611959457397</v>
       </c>
       <c r="U18" t="n">
-        <v>0.186641052365303</v>
+        <v>-0.3803315460681915</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5935114026069641</v>
+        <v>-0.07401209324598312</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.353251039981842</v>
+        <v>0.3726734817028046</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3005176186561584</v>
+        <v>0.1001261621713638</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.4043606519699097</v>
+        <v>0.6835761070251465</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0.2080257385969162</v>
+        <v>-0.1599297225475311</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.2012081146240234</v>
+        <v>0.323763370513916</v>
       </c>
       <c r="AB18" t="n">
-        <v>-0.238764762878418</v>
+        <v>-0.1790246516466141</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.2636377513408661</v>
+        <v>-0.08153539896011353</v>
       </c>
       <c r="AD18" t="n">
-        <v>-0.2339839935302734</v>
+        <v>-0.04286917299032211</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0.1681157648563385</v>
+        <v>0.3159083724021912</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.2992361485958099</v>
+        <v>0.00109820393845439</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.56919264793396</v>
+        <v>-0.02201592735946178</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.2606218159198761</v>
+        <v>0.6318086385726929</v>
       </c>
       <c r="AI18" t="n">
-        <v>-0.2256083488464355</v>
+        <v>-0.2537434995174408</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.1086366176605225</v>
+        <v>-0.08691110461950302</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.2635564208030701</v>
+        <v>0.2216607332229614</v>
       </c>
       <c r="AL18" t="n">
-        <v>-0.658062756061554</v>
+        <v>-0.5398444533348083</v>
       </c>
       <c r="AM18" t="n">
-        <v>-0.1239065378904343</v>
+        <v>-0.1234596073627472</v>
       </c>
       <c r="AN18" t="n">
-        <v>-0.1649033725261688</v>
+        <v>0.3948139846324921</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.09946919232606888</v>
+        <v>0.1072199195623398</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.05482489988207817</v>
+        <v>0.4161809086799622</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.1280434429645538</v>
+        <v>0.6013873815536499</v>
       </c>
       <c r="AR18" t="n">
-        <v>-0.002772798296064138</v>
+        <v>-0.4093007743358612</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.1599367260932922</v>
+        <v>0.2256817519664764</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.2641191482543945</v>
+        <v>-0.374414324760437</v>
       </c>
       <c r="AU18" t="n">
-        <v>-0.3572805225849152</v>
+        <v>0.2606435716152191</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.4899206161499023</v>
+        <v>0.1680748015642166</v>
       </c>
       <c r="AW18" t="n">
-        <v>-0.05408130586147308</v>
+        <v>0.8915583491325378</v>
       </c>
       <c r="AX18" t="n">
-        <v>-0.1478240638971329</v>
+        <v>-0.2060659527778625</v>
       </c>
       <c r="AY18" t="n">
         <v>1</v>
@@ -3322,154 +3322,154 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-0.3867968320846558</v>
+        <v>0.1561459451913834</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.7831184864044189</v>
+        <v>-0.3638069927692413</v>
       </c>
       <c r="C19" t="n">
-        <v>0.106560193002224</v>
+        <v>-0.09232313930988312</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3654052913188934</v>
+        <v>-0.043372992426157</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2412389665842056</v>
+        <v>-0.009972802363336086</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4532082378864288</v>
+        <v>0.2396109700202942</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2128506451845169</v>
+        <v>0.289385050535202</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.008726823143661022</v>
+        <v>0.5637801885604858</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.436086505651474</v>
+        <v>-0.03352393209934235</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.07056265324354172</v>
+        <v>0.0675555020570755</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1532637774944305</v>
+        <v>-0.2741584479808807</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1872003674507141</v>
+        <v>0.2340377271175385</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2889281511306763</v>
+        <v>0.1625044494867325</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1144340932369232</v>
+        <v>-0.1301967650651932</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3305055797100067</v>
+        <v>0.2695830762386322</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.0555441714823246</v>
+        <v>0.5422142148017883</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.09993012994527817</v>
+        <v>-0.108915813267231</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.5907788872718811</v>
+        <v>-0.6731449365615845</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0455031655728817</v>
+        <v>-0.336486279964447</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1144665405154228</v>
+        <v>-0.306160181760788</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1316342949867249</v>
+        <v>-0.190582200884819</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3676263391971588</v>
+        <v>-0.09054455161094666</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.2986864745616913</v>
+        <v>0.4792211353778839</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1100236028432846</v>
+        <v>-0.04146852344274521</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.5132423639297485</v>
+        <v>0.5977524518966675</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.07047697901725769</v>
+        <v>-0.2444252073764801</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.1189303025603294</v>
+        <v>0.1174199879169464</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0.1681385636329651</v>
+        <v>-0.1023005843162537</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.1490330100059509</v>
+        <v>-0.3149177432060242</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0.2184505313634872</v>
+        <v>-0.2519355118274689</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.05127254500985146</v>
+        <v>0.4645742774009705</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.3463945984840393</v>
+        <v>0.02644327655434608</v>
       </c>
       <c r="AG19" t="n">
-        <v>-0.4594290256500244</v>
+        <v>-0.09244269132614136</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0.3492178320884705</v>
+        <v>0.5864270925521851</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.1303483545780182</v>
+        <v>-0.09438986331224442</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.1398632675409317</v>
+        <v>-0.1273927390575409</v>
       </c>
       <c r="AK19" t="n">
-        <v>0.02763272449374199</v>
+        <v>0.07423611730337143</v>
       </c>
       <c r="AL19" t="n">
-        <v>-0.8301291465759277</v>
+        <v>-0.5933375358581543</v>
       </c>
       <c r="AM19" t="n">
-        <v>-0.1847829073667526</v>
+        <v>-0.02744811773300171</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.06651061028242111</v>
+        <v>0.4746943414211273</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.2356545180082321</v>
+        <v>0.1878600418567657</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.007068292237818241</v>
+        <v>0.3946473002433777</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.0682908296585083</v>
+        <v>0.4140178859233856</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.1218282878398895</v>
+        <v>-0.2102862447500229</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.01061640866100788</v>
+        <v>0.2089284956455231</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.1809522360563278</v>
+        <v>-0.3255469799041748</v>
       </c>
       <c r="AU19" t="n">
-        <v>-0.2047027349472046</v>
+        <v>-0.02143585868179798</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.6114102005958557</v>
+        <v>0.3661064505577087</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.2050102800130844</v>
+        <v>0.6306723952293396</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.01385866571217775</v>
+        <v>-0.2076644897460938</v>
       </c>
       <c r="AY19" t="n">
         <v>1</v>
@@ -3477,154 +3477,154 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-0.4610674679279327</v>
+        <v>0.1416492015123367</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.8961787819862366</v>
+        <v>-0.3650881350040436</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06583016365766525</v>
+        <v>-0.1553187221288681</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4251188635826111</v>
+        <v>-0.004207471385598183</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2716987729072571</v>
+        <v>-0.0251808874309063</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4837760031223297</v>
+        <v>0.2788034379482269</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1074667349457741</v>
+        <v>0.2653642892837524</v>
       </c>
       <c r="H20" t="n">
-        <v>0.09808400273323059</v>
+        <v>0.5991361737251282</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3225676715373993</v>
+        <v>-0.05054511874914169</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.09867651015520096</v>
+        <v>0.1808958351612091</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1774968057870865</v>
+        <v>-0.4191833436489105</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2396932989358902</v>
+        <v>0.2392813116312027</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3964356184005737</v>
+        <v>0.2009246647357941</v>
       </c>
       <c r="N20" t="n">
-        <v>0.03677824512124062</v>
+        <v>-0.2178139537572861</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2637102901935577</v>
+        <v>0.2518986761569977</v>
       </c>
       <c r="P20" t="n">
-        <v>-7.319152064155787e-05</v>
+        <v>0.6366281509399414</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1994747668504715</v>
+        <v>-0.1094704866409302</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.6857191324234009</v>
+        <v>-0.5781968235969543</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.10183235257864</v>
+        <v>-0.4489494860172272</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1111996993422508</v>
+        <v>-0.3333379030227661</v>
       </c>
       <c r="U20" t="n">
-        <v>0.08214154094457626</v>
+        <v>-0.1626233160495758</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3572133779525757</v>
+        <v>-0.01630702428519726</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.2600347101688385</v>
+        <v>0.5599480867385864</v>
       </c>
       <c r="X20" t="n">
-        <v>0.09379356354475021</v>
+        <v>0.02832059375941753</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.5376084446907043</v>
+        <v>0.6346988677978516</v>
       </c>
       <c r="Z20" t="n">
-        <v>-0.2137269079685211</v>
+        <v>-0.2540779709815979</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.1599085330963135</v>
+        <v>0.150847852230072</v>
       </c>
       <c r="AB20" t="n">
-        <v>-0.1985936760902405</v>
+        <v>-0.1239535287022591</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.09490148723125458</v>
+        <v>-0.3846246898174286</v>
       </c>
       <c r="AD20" t="n">
-        <v>-0.262633353471756</v>
+        <v>-0.2780183851718903</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0.05605500191450119</v>
+        <v>0.5146517157554626</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0.4743688702583313</v>
+        <v>0.04719973355531693</v>
       </c>
       <c r="AG20" t="n">
-        <v>-0.4386777579784393</v>
+        <v>0.03949026763439178</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0.3531547486782074</v>
+        <v>0.6236573457717896</v>
       </c>
       <c r="AI20" t="n">
-        <v>-0.08831705898046494</v>
+        <v>-0.2017622888088226</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.2132066935300827</v>
+        <v>-0.1371724605560303</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.003600982716307044</v>
+        <v>0.03049670718610287</v>
       </c>
       <c r="AL20" t="n">
-        <v>-0.8477981686592102</v>
+        <v>-0.5758052468299866</v>
       </c>
       <c r="AM20" t="n">
-        <v>-0.1601255536079407</v>
+        <v>-0.02187524735927582</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.02257637865841389</v>
+        <v>0.4414777457714081</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.2553922235965729</v>
+        <v>0.1788915544748306</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.07587063312530518</v>
+        <v>0.4855947196483612</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.2059106677770615</v>
+        <v>0.5842245817184448</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.0941949188709259</v>
+        <v>-0.2249179780483246</v>
       </c>
       <c r="AS20" t="n">
-        <v>-0.04815738648176193</v>
+        <v>0.3009108603000641</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.1539153903722763</v>
+        <v>-0.3073389828205109</v>
       </c>
       <c r="AU20" t="n">
-        <v>-0.2476865947246552</v>
+        <v>-0.1479974985122681</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.6698542833328247</v>
+        <v>0.4103923738002777</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.1919935792684555</v>
+        <v>0.6795893907546997</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.04470450058579445</v>
+        <v>-0.1807935684919357</v>
       </c>
       <c r="AY20" t="n">
         <v>1</v>
@@ -3632,154 +3632,154 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-0.3612963855266571</v>
+        <v>0.1515427380800247</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.9372209906578064</v>
+        <v>-0.3270466923713684</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1216894313693047</v>
+        <v>-0.09526266902685165</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3922127783298492</v>
+        <v>-0.008837931789457798</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2607589960098267</v>
+        <v>-0.04178985580801964</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5063797831535339</v>
+        <v>0.3305394947528839</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.09696543961763382</v>
+        <v>0.2201511263847351</v>
       </c>
       <c r="H21" t="n">
-        <v>0.09300334751605988</v>
+        <v>0.6105054020881653</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3860394060611725</v>
+        <v>-0.1045129373669624</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.08172576129436493</v>
+        <v>0.1222821697592735</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2504144608974457</v>
+        <v>-0.3146019279956818</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.2058982253074646</v>
+        <v>0.298763632774353</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4544918537139893</v>
+        <v>0.1752458512783051</v>
       </c>
       <c r="N21" t="n">
-        <v>0.08224765211343765</v>
+        <v>-0.1661867052316666</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2738466560840607</v>
+        <v>0.2733098566532135</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.06963430345058441</v>
+        <v>0.6686139106750488</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.2132366001605988</v>
+        <v>-0.08336397260427475</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.6511077880859375</v>
+        <v>-0.6236470341682434</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1200313717126846</v>
+        <v>-0.4308633804321289</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1525163203477859</v>
+        <v>-0.3396122753620148</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1286522746086121</v>
+        <v>-0.1916330605745316</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.4123506546020508</v>
+        <v>-0.1010265126824379</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.2719243466854095</v>
+        <v>0.5243775844573975</v>
       </c>
       <c r="X21" t="n">
-        <v>0.08914964646100998</v>
+        <v>0.02087774313986301</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.5314080119132996</v>
+        <v>0.6615020632743835</v>
       </c>
       <c r="Z21" t="n">
-        <v>-0.2223209142684937</v>
+        <v>-0.1919698119163513</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.09750159084796906</v>
+        <v>0.09398119896650314</v>
       </c>
       <c r="AB21" t="n">
-        <v>-0.2958405315876007</v>
+        <v>-0.1314860433340073</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.165405735373497</v>
+        <v>-0.366809755563736</v>
       </c>
       <c r="AD21" t="n">
-        <v>-0.2234370559453964</v>
+        <v>-0.2519224882125854</v>
       </c>
       <c r="AE21" t="n">
-        <v>-0.08685882389545441</v>
+        <v>0.5063126683235168</v>
       </c>
       <c r="AF21" t="n">
-        <v>-0.4372792840003967</v>
+        <v>0.01432404108345509</v>
       </c>
       <c r="AG21" t="n">
-        <v>-0.5111992359161377</v>
+        <v>-0.05461694672703743</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.3703950643539429</v>
+        <v>0.7121100425720215</v>
       </c>
       <c r="AI21" t="n">
-        <v>-0.1188627183437347</v>
+        <v>-0.156531497836113</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.2123268693685532</v>
+        <v>-0.112059585750103</v>
       </c>
       <c r="AK21" t="n">
-        <v>-0.01815349049866199</v>
+        <v>0.02500626258552074</v>
       </c>
       <c r="AL21" t="n">
-        <v>-0.8706467747688293</v>
+        <v>-0.5938228368759155</v>
       </c>
       <c r="AM21" t="n">
-        <v>-0.1666726917028427</v>
+        <v>-0.05238660424947739</v>
       </c>
       <c r="AN21" t="n">
-        <v>-0.02999862469732761</v>
+        <v>0.45370152592659</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.3015572130680084</v>
+        <v>0.2187665551900864</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.0446903295814991</v>
+        <v>0.4826898872852325</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.1354841142892838</v>
+        <v>0.5874708294868469</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.1274487674236298</v>
+        <v>-0.2420549392700195</v>
       </c>
       <c r="AS21" t="n">
-        <v>-0.04994235932826996</v>
+        <v>0.3152433931827545</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.1181152537465096</v>
+        <v>-0.3251056373119354</v>
       </c>
       <c r="AU21" t="n">
-        <v>-0.2068630307912827</v>
+        <v>-0.1018354743719101</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.6715161800384521</v>
+        <v>0.3920151889324188</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.2191936671733856</v>
+        <v>0.6943623423576355</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.05425206944346428</v>
+        <v>-0.2361584007740021</v>
       </c>
       <c r="AY21" t="n">
         <v>1</v>
@@ -3787,154 +3787,154 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-0.3385410606861115</v>
+        <v>0.0301542654633522</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.4996834993362427</v>
+        <v>-0.6306236982345581</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.003127646166831255</v>
+        <v>-0.2815382182598114</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2599624693393707</v>
+        <v>-0.1543555855751038</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1267049759626389</v>
+        <v>0.0965934544801712</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2567289173603058</v>
+        <v>0.03026332333683968</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2636237740516663</v>
+        <v>0.2203769832849503</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.01631292700767517</v>
+        <v>0.2942643761634827</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4837058782577515</v>
+        <v>-0.01693634316325188</v>
       </c>
       <c r="J22" t="n">
-        <v>0.04444126784801483</v>
+        <v>0.1115698739886284</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1982197761535645</v>
+        <v>-0.4629228115081787</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1207029074430466</v>
+        <v>0.1472079157829285</v>
       </c>
       <c r="M22" t="n">
-        <v>0.03406167775392532</v>
+        <v>-0.2088750600814819</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4401199221611023</v>
+        <v>0.03599474206566811</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1480213552713394</v>
+        <v>0.09745153039693832</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1173119023442268</v>
+        <v>0.0199410654604435</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1271793991327286</v>
+        <v>0.1858738362789154</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.5985086560249329</v>
+        <v>-0.4242563843727112</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1367150247097015</v>
+        <v>-0.1820481270551682</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1423139572143555</v>
+        <v>-0.1146863102912903</v>
       </c>
       <c r="U22" t="n">
-        <v>0.06654992699623108</v>
+        <v>-0.09379004687070847</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1561279445886612</v>
+        <v>0.1057361513376236</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.2723898887634277</v>
+        <v>0.2595970034599304</v>
       </c>
       <c r="X22" t="n">
-        <v>0.1470099091529846</v>
+        <v>-0.02436833456158638</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.5949972867965698</v>
+        <v>0.3026739358901978</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.06292214244604111</v>
+        <v>-0.3168051242828369</v>
       </c>
       <c r="AA22" t="n">
-        <v>-0.05534977465867996</v>
+        <v>0.1003018990159035</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.1366613209247589</v>
+        <v>-0.06825222820043564</v>
       </c>
       <c r="AC22" t="n">
-        <v>-0.09140238910913467</v>
+        <v>-0.3310288190841675</v>
       </c>
       <c r="AD22" t="n">
-        <v>-0.266657680273056</v>
+        <v>0.04560607671737671</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.06129347532987595</v>
+        <v>-0.005103966221213341</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0.01413971744477749</v>
+        <v>-0.04673498868942261</v>
       </c>
       <c r="AG22" t="n">
-        <v>-0.1648420542478561</v>
+        <v>-0.03926335275173187</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.2208179533481598</v>
+        <v>0.2386142462491989</v>
       </c>
       <c r="AI22" t="n">
-        <v>-0.1318032294511795</v>
+        <v>-0.1372562348842621</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.09353777021169662</v>
+        <v>-0.2199592441320419</v>
       </c>
       <c r="AK22" t="n">
-        <v>-0.03535233810544014</v>
+        <v>0.3676461279392242</v>
       </c>
       <c r="AL22" t="n">
-        <v>-0.655457079410553</v>
+        <v>-0.8066607713699341</v>
       </c>
       <c r="AM22" t="n">
-        <v>-0.1809704154729843</v>
+        <v>0.03409668058156967</v>
       </c>
       <c r="AN22" t="n">
-        <v>0.22132308781147</v>
+        <v>0.5096004009246826</v>
       </c>
       <c r="AO22" t="n">
-        <v>-0.0799419954419136</v>
+        <v>-0.06487620621919632</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.09347193688154221</v>
+        <v>-0.001220242585986853</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.1565108895301819</v>
+        <v>0.1145602762699127</v>
       </c>
       <c r="AR22" t="n">
-        <v>-0.1659745126962662</v>
+        <v>-0.416433721780777</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.2944608628749847</v>
+        <v>0.05306597426533699</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.3194743394851685</v>
+        <v>0.06792600452899933</v>
       </c>
       <c r="AU22" t="n">
-        <v>-0.21778205037117</v>
+        <v>0.04056531563401222</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.4099045097827911</v>
+        <v>0.2098564505577087</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.232814684510231</v>
+        <v>0.3684841096401215</v>
       </c>
       <c r="AX22" t="n">
-        <v>-0.3315820395946503</v>
+        <v>-0.3316984176635742</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
@@ -3942,154 +3942,154 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-0.267082005739212</v>
+        <v>0.1088841110467911</v>
       </c>
       <c r="B23" t="n">
-        <v>-0.5296873450279236</v>
+        <v>-0.5660178661346436</v>
       </c>
       <c r="C23" t="n">
-        <v>0.02500716410577297</v>
+        <v>-0.1435519605875015</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2201178967952728</v>
+        <v>-0.1784579455852509</v>
       </c>
       <c r="E23" t="n">
-        <v>0.09362060576677322</v>
+        <v>0.09960313141345978</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1970401704311371</v>
+        <v>0.08107089251279831</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1869913339614868</v>
+        <v>0.2114962339401245</v>
       </c>
       <c r="H23" t="n">
-        <v>0.006805824115872383</v>
+        <v>0.2693837285041809</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4242529273033142</v>
+        <v>-0.06704487651586533</v>
       </c>
       <c r="J23" t="n">
-        <v>0.04936904087662697</v>
+        <v>0.06852583587169647</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1547785252332687</v>
+        <v>-0.4658079743385315</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.1152768805623055</v>
+        <v>0.2052309066057205</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.07666333019733429</v>
+        <v>-0.1353997737169266</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4353578984737396</v>
+        <v>0.09365733712911606</v>
       </c>
       <c r="O23" t="n">
-        <v>0.07871786504983902</v>
+        <v>0.09615997970104218</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1608445048332214</v>
+        <v>0.08420809358358383</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1249516531825066</v>
+        <v>0.2752587199211121</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.6200152635574341</v>
+        <v>-0.4173400104045868</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1969414949417114</v>
+        <v>-0.1956404745578766</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1298616677522659</v>
+        <v>-0.1436115801334381</v>
       </c>
       <c r="U23" t="n">
-        <v>0.07600489258766174</v>
+        <v>-0.1059611141681671</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.220648854970932</v>
+        <v>0.0898486003279686</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.2595778405666351</v>
+        <v>0.2559980452060699</v>
       </c>
       <c r="X23" t="n">
-        <v>0.1028428077697754</v>
+        <v>-0.05576427653431892</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.4956752359867096</v>
+        <v>0.3456262350082397</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.02569985389709473</v>
+        <v>-0.171746164560318</v>
       </c>
       <c r="AA23" t="n">
-        <v>-0.2128159999847412</v>
+        <v>0.04281492903828621</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.02528741210699081</v>
+        <v>-0.02659118361771107</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.02783604525029659</v>
+        <v>-0.2365003973245621</v>
       </c>
       <c r="AD23" t="n">
-        <v>-0.2507124841213226</v>
+        <v>0.06331034749746323</v>
       </c>
       <c r="AE23" t="n">
-        <v>-0.02944107353687286</v>
+        <v>0.09171907603740692</v>
       </c>
       <c r="AF23" t="n">
-        <v>-0.05305900424718857</v>
+        <v>-0.02038262225687504</v>
       </c>
       <c r="AG23" t="n">
-        <v>-0.1276378929615021</v>
+        <v>-0.1107413917779922</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.2104126214981079</v>
+        <v>0.2534277737140656</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.1540760099887848</v>
+        <v>-0.09830938279628754</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.09077014774084091</v>
+        <v>-0.2630266845226288</v>
       </c>
       <c r="AK23" t="n">
-        <v>-0.1160665899515152</v>
+        <v>0.3494398891925812</v>
       </c>
       <c r="AL23" t="n">
-        <v>-0.6674036979675293</v>
+        <v>-0.7569928169250488</v>
       </c>
       <c r="AM23" t="n">
-        <v>-0.2468334436416626</v>
+        <v>0.01088191755115986</v>
       </c>
       <c r="AN23" t="n">
-        <v>0.09492995589971542</v>
+        <v>0.5193073749542236</v>
       </c>
       <c r="AO23" t="n">
-        <v>-0.05097666755318642</v>
+        <v>-0.07825402170419693</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.1276648193597794</v>
+        <v>0.01382936257869005</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.1174137219786644</v>
+        <v>0.2233737856149673</v>
       </c>
       <c r="AR23" t="n">
-        <v>-0.1733789294958115</v>
+        <v>-0.3907540440559387</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.260701060295105</v>
+        <v>0.1513925939798355</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.3933223485946655</v>
+        <v>0.100413016974926</v>
       </c>
       <c r="AU23" t="n">
-        <v>-0.3089819848537445</v>
+        <v>0.06904497742652893</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.3301823437213898</v>
+        <v>0.1723330467939377</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.2695384621620178</v>
+        <v>0.3709753751754761</v>
       </c>
       <c r="AX23" t="n">
-        <v>-0.2118541151285172</v>
+        <v>-0.3015470802783966</v>
       </c>
       <c r="AY23" t="n">
         <v>0</v>
@@ -4097,154 +4097,154 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-0.04936674237251282</v>
+        <v>0.202472910284996</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.6710317730903625</v>
+        <v>-0.4400600492954254</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2000088393688202</v>
+        <v>0.05703780800104141</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.02128658257424831</v>
+        <v>-0.2629065811634064</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1206893399357796</v>
+        <v>0.2661917805671692</v>
       </c>
       <c r="F24" t="n">
-        <v>0.00840369425714016</v>
+        <v>0.1068764105439186</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1262428760528564</v>
+        <v>0.09590291976928711</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.01418863888829947</v>
+        <v>0.4850881397724152</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.6112223863601685</v>
+        <v>-0.1504220217466354</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1740689128637314</v>
+        <v>0.07988011837005615</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1071518212556839</v>
+        <v>-0.1627407670021057</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.04964950680732727</v>
+        <v>0.1837758272886276</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3154691755771637</v>
+        <v>-0.1355224400758743</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5022172331809998</v>
+        <v>0.1507459133863449</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1731659471988678</v>
+        <v>0.055643480271101</v>
       </c>
       <c r="P24" t="n">
-        <v>0.01977868191897869</v>
+        <v>-0.06352619081735611</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.2810356616973877</v>
+        <v>0.1606835424900055</v>
       </c>
       <c r="R24" t="n">
-        <v>-0.3318230211734772</v>
+        <v>-0.6475046873092651</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4654057919979095</v>
+        <v>-0.1229447796940804</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1213575378060341</v>
+        <v>-0.02406233362853527</v>
       </c>
       <c r="U24" t="n">
-        <v>0.06824611127376556</v>
+        <v>-0.08741487562656403</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1890594065189362</v>
+        <v>-0.1238006129860878</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.3869051337242126</v>
+        <v>0.07351728528738022</v>
       </c>
       <c r="X24" t="n">
-        <v>0.2532072365283966</v>
+        <v>0.2184986770153046</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.4898762404918671</v>
+        <v>0.4512577056884766</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.2191199511289597</v>
+        <v>0.09665164351463318</v>
       </c>
       <c r="AA24" t="n">
-        <v>-0.2954033017158508</v>
+        <v>-0.2434487044811249</v>
       </c>
       <c r="AB24" t="n">
-        <v>-0.1633576303720474</v>
+        <v>-0.1000939607620239</v>
       </c>
       <c r="AC24" t="n">
-        <v>-0.04406379535794258</v>
+        <v>-0.3250343799591064</v>
       </c>
       <c r="AD24" t="n">
-        <v>-0.06655139476060867</v>
+        <v>-0.06277310848236084</v>
       </c>
       <c r="AE24" t="n">
-        <v>-0.1337798535823822</v>
+        <v>-0.04636562615633011</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0.002530470490455627</v>
+        <v>-0.1688302010297775</v>
       </c>
       <c r="AG24" t="n">
-        <v>-0.1110002249479294</v>
+        <v>-0.3491070866584778</v>
       </c>
       <c r="AH24" t="n">
-        <v>-0.4980013072490692</v>
+        <v>0.2678108811378479</v>
       </c>
       <c r="AI24" t="n">
-        <v>-0.2734351456165314</v>
+        <v>0.1283520758152008</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.05743840709328651</v>
+        <v>-0.7324551939964294</v>
       </c>
       <c r="AK24" t="n">
-        <v>-0.1055457442998886</v>
+        <v>0.1892176270484924</v>
       </c>
       <c r="AL24" t="n">
-        <v>-0.5002048015594482</v>
+        <v>-0.9796754717826843</v>
       </c>
       <c r="AM24" t="n">
-        <v>-0.3965529799461365</v>
+        <v>-0.09265363961458206</v>
       </c>
       <c r="AN24" t="n">
-        <v>0.09993902593851089</v>
+        <v>0.3239514827728271</v>
       </c>
       <c r="AO24" t="n">
-        <v>0.08842927217483521</v>
+        <v>0.03341369330883026</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.1439121812582016</v>
+        <v>-0.1853196024894714</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.3338808417320251</v>
+        <v>0.08047036081552505</v>
       </c>
       <c r="AR24" t="n">
-        <v>-0.138912171125412</v>
+        <v>-0.4139991998672485</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.3779410421848297</v>
+        <v>0.4670867025852203</v>
       </c>
       <c r="AT24" t="n">
-        <v>-0.004921112675219774</v>
+        <v>0.3016690313816071</v>
       </c>
       <c r="AU24" t="n">
-        <v>-0.4150891602039337</v>
+        <v>0.1686096489429474</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.03814980015158653</v>
+        <v>0.1967358887195587</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.3590262234210968</v>
+        <v>0.1919158846139908</v>
       </c>
       <c r="AX24" t="n">
-        <v>-0.2878860831260681</v>
+        <v>-0.1363435983657837</v>
       </c>
       <c r="AY24" t="n">
         <v>0</v>
@@ -4252,154 +4252,154 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-0.391970694065094</v>
+        <v>-0.1281676590442657</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.5977723598480225</v>
+        <v>-0.8045452237129211</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.07078070193529129</v>
+        <v>-0.3394977748394012</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.1344606429338455</v>
+        <v>-0.06780007481575012</v>
       </c>
       <c r="E25" t="n">
-        <v>0.07704944163560867</v>
+        <v>0.1635934710502625</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.03487662598490715</v>
+        <v>0.0528508760035038</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3410482406616211</v>
+        <v>0.03812181204557419</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1246640533208847</v>
+        <v>0.3706759214401245</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.7617467641830444</v>
+        <v>-0.380498081445694</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.07341723144054413</v>
+        <v>0.2494623363018036</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.2275760024785995</v>
+        <v>-0.4993500113487244</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.07866667956113815</v>
+        <v>0.2668621242046356</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.03823450952768326</v>
+        <v>-0.2770936191082001</v>
       </c>
       <c r="N25" t="n">
-        <v>0.47630575299263</v>
+        <v>0.04451149702072144</v>
       </c>
       <c r="O25" t="n">
-        <v>0.119773767888546</v>
+        <v>0.05332961305975914</v>
       </c>
       <c r="P25" t="n">
-        <v>0.05941398441791534</v>
+        <v>-0.0624840147793293</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.2415701150894165</v>
+        <v>0.2868857383728027</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.5681542158126831</v>
+        <v>-0.6219393014907837</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5085697770118713</v>
+        <v>-0.317171037197113</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1508659422397614</v>
+        <v>-0.1582123637199402</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1462471485137939</v>
+        <v>-0.3222109973430634</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.2764788866043091</v>
+        <v>-0.1572173088788986</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.03808166086673737</v>
+        <v>0.3484675288200378</v>
       </c>
       <c r="X25" t="n">
-        <v>0.1017851084470749</v>
+        <v>0.148275762796402</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.7726514339447021</v>
+        <v>0.4100446999073029</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.2721984386444092</v>
+        <v>-0.3342235386371613</v>
       </c>
       <c r="AA25" t="n">
-        <v>-0.1226033493876457</v>
+        <v>0.1926997303962708</v>
       </c>
       <c r="AB25" t="n">
-        <v>-0.07990779727697372</v>
+        <v>-0.1582725942134857</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.09131275862455368</v>
+        <v>-0.6357698440551758</v>
       </c>
       <c r="AD25" t="n">
-        <v>-0.3413402736186981</v>
+        <v>-0.04355449229478836</v>
       </c>
       <c r="AE25" t="n">
-        <v>-0.0251733586192131</v>
+        <v>-0.1327043771743774</v>
       </c>
       <c r="AF25" t="n">
-        <v>-0.06164930388331413</v>
+        <v>0.06880944222211838</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.3080572485923767</v>
+        <v>0.1151090934872627</v>
       </c>
       <c r="AH25" t="n">
-        <v>-0.3364243805408478</v>
+        <v>0.421471118927002</v>
       </c>
       <c r="AI25" t="n">
-        <v>-0.0534418523311615</v>
+        <v>-0.3583988845348358</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.2735827267169952</v>
+        <v>-0.1823161840438843</v>
       </c>
       <c r="AK25" t="n">
-        <v>0.02581308223307133</v>
+        <v>0.1595782786607742</v>
       </c>
       <c r="AL25" t="n">
-        <v>-0.8007020354270935</v>
+        <v>-0.908970057964325</v>
       </c>
       <c r="AM25" t="n">
-        <v>-0.04009274765849113</v>
+        <v>-0.1428871899843216</v>
       </c>
       <c r="AN25" t="n">
-        <v>0.1424403190612793</v>
+        <v>0.5225591063499451</v>
       </c>
       <c r="AO25" t="n">
-        <v>-0.08548267930746078</v>
+        <v>-0.01543309073895216</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.1619270145893097</v>
+        <v>-0.04742840304970741</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.2351751029491425</v>
+        <v>0.2553696632385254</v>
       </c>
       <c r="AR25" t="n">
-        <v>-0.4136132895946503</v>
+        <v>-0.401982456445694</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.3962598741054535</v>
+        <v>0.2090471088886261</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.213274359703064</v>
+        <v>0.3338211476802826</v>
       </c>
       <c r="AU25" t="n">
-        <v>-0.01377827860414982</v>
+        <v>-0.1965421587228775</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.4876838326454163</v>
+        <v>0.3641518950462341</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.2323997765779495</v>
+        <v>0.3628213107585907</v>
       </c>
       <c r="AX25" t="n">
-        <v>-0.4200984835624695</v>
+        <v>-0.3693104982376099</v>
       </c>
       <c r="AY25" t="n">
         <v>0</v>
@@ -4407,154 +4407,154 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-0.3510980606079102</v>
+        <v>-0.005523674190044403</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.4954645931720734</v>
+        <v>-0.6979606747627258</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02862528525292873</v>
+        <v>-0.1875785440206528</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2379080355167389</v>
+        <v>-0.2498593479394913</v>
       </c>
       <c r="E26" t="n">
-        <v>0.07773176580667496</v>
+        <v>0.1028747260570526</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.2769072353839874</v>
+        <v>0.02008607983589172</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.2624692022800446</v>
+        <v>0.2099054306745529</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.003120865672826767</v>
+        <v>0.3902598917484283</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5567834377288818</v>
+        <v>-0.1455408185720444</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.04091806337237358</v>
+        <v>0.1755400449037552</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.2631950974464417</v>
+        <v>-0.4342375993728638</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.07852966338396072</v>
+        <v>0.06211293116211891</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.02104537934064865</v>
+        <v>-0.1518552452325821</v>
       </c>
       <c r="N26" t="n">
-        <v>0.4249224066734314</v>
+        <v>0.01255912985652685</v>
       </c>
       <c r="O26" t="n">
-        <v>0.2039458751678467</v>
+        <v>0.1297684013843536</v>
       </c>
       <c r="P26" t="n">
-        <v>0.03055770508944988</v>
+        <v>0.01944884844124317</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.2035839259624481</v>
+        <v>0.2082238793373108</v>
       </c>
       <c r="R26" t="n">
-        <v>-0.5761054754257202</v>
+        <v>-0.5006226301193237</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2100639790296555</v>
+        <v>-0.2492648065090179</v>
       </c>
       <c r="T26" t="n">
-        <v>0.12094596773386</v>
+        <v>-0.123123362660408</v>
       </c>
       <c r="U26" t="n">
-        <v>0.08566523343324661</v>
+        <v>-0.1231550797820091</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.2530635595321655</v>
+        <v>0.003635923843830824</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.2087256759405136</v>
+        <v>0.3125360310077667</v>
       </c>
       <c r="X26" t="n">
-        <v>0.09553318470716476</v>
+        <v>0.05736603960394859</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.6649089455604553</v>
+        <v>0.3664616346359253</v>
       </c>
       <c r="Z26" t="n">
-        <v>-0.01076787989586592</v>
+        <v>-0.2577413022518158</v>
       </c>
       <c r="AA26" t="n">
-        <v>-0.02542180754244328</v>
+        <v>0.1304663866758347</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.1365130096673965</v>
+        <v>-0.131804421544075</v>
       </c>
       <c r="AC26" t="n">
-        <v>-0.1106951981782913</v>
+        <v>-0.4496620297431946</v>
       </c>
       <c r="AD26" t="n">
-        <v>-0.2132450044155121</v>
+        <v>0.0758475735783577</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.05234352499246597</v>
+        <v>-0.05016759037971497</v>
       </c>
       <c r="AF26" t="n">
-        <v>-0.08212464302778244</v>
+        <v>-0.1012432351708412</v>
       </c>
       <c r="AG26" t="n">
-        <v>-0.2069856077432632</v>
+        <v>0.02353569306433201</v>
       </c>
       <c r="AH26" t="n">
-        <v>-0.3062448501586914</v>
+        <v>0.294261634349823</v>
       </c>
       <c r="AI26" t="n">
-        <v>-0.09314931929111481</v>
+        <v>-0.1862710863351822</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.1191659495234489</v>
+        <v>-0.227044016122818</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.08070112764835358</v>
+        <v>0.1961462944746017</v>
       </c>
       <c r="AL26" t="n">
-        <v>-0.6993788480758667</v>
+        <v>-0.8341597318649292</v>
       </c>
       <c r="AM26" t="n">
-        <v>-0.1671895980834961</v>
+        <v>-0.1116235181689262</v>
       </c>
       <c r="AN26" t="n">
-        <v>0.1312292218208313</v>
+        <v>0.5221077799797058</v>
       </c>
       <c r="AO26" t="n">
-        <v>-0.1218713223934174</v>
+        <v>-0.1167359128594398</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.1315594166517258</v>
+        <v>0.03294263035058975</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.131293311715126</v>
+        <v>0.1563213169574738</v>
       </c>
       <c r="AR26" t="n">
-        <v>-0.2464388459920883</v>
+        <v>-0.3472310602664948</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.3429737985134125</v>
+        <v>0.03704077750444412</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.2803975641727448</v>
+        <v>0.1311783939599991</v>
       </c>
       <c r="AU26" t="n">
-        <v>-0.212358295917511</v>
+        <v>0.04133733361959457</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.4416374862194061</v>
+        <v>0.2308489233255386</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.2001136541366577</v>
+        <v>0.4383084774017334</v>
       </c>
       <c r="AX26" t="n">
-        <v>-0.3736947476863861</v>
+        <v>-0.3270032405853271</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
@@ -4562,154 +4562,154 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-0.2437709867954254</v>
+        <v>0.02408353239297867</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.5407042503356934</v>
+        <v>-0.5612848997116089</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2035035640001297</v>
+        <v>-0.05245101824402809</v>
       </c>
       <c r="D27" t="n">
-        <v>0.02210632339119911</v>
+        <v>-0.2373200803995132</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02876966260373592</v>
+        <v>-0.05951595306396484</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.2082221359014511</v>
+        <v>0.2279617488384247</v>
       </c>
       <c r="G27" t="n">
-        <v>0.135947197675705</v>
+        <v>-0.005235645454376936</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3833543658256531</v>
+        <v>0.03189302980899811</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.7518293857574463</v>
+        <v>-0.4463925957679749</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.1176456362009048</v>
+        <v>0.2117248475551605</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.2885052859783173</v>
+        <v>-0.3060915470123291</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.01191818248480558</v>
+        <v>0.5990532040596008</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.3974389433860779</v>
+        <v>0.02722791396081448</v>
       </c>
       <c r="N27" t="n">
-        <v>0.5442848801612854</v>
+        <v>0.2729236781597137</v>
       </c>
       <c r="O27" t="n">
-        <v>0.1907912641763687</v>
+        <v>0.1141695752739906</v>
       </c>
       <c r="P27" t="n">
-        <v>0.2110827565193176</v>
+        <v>0.09544525295495987</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.3397346138954163</v>
+        <v>0.4018256068229675</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.6143810153007507</v>
+        <v>-0.4743895530700684</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.3087485432624817</v>
+        <v>-0.3124043047428131</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.1361393183469772</v>
+        <v>-0.009388210251927376</v>
       </c>
       <c r="U27" t="n">
-        <v>0.04975127428770065</v>
+        <v>-0.3130097389221191</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.6686561703681946</v>
+        <v>-0.06557245552539825</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.3670613765716553</v>
+        <v>0.1096310913562775</v>
       </c>
       <c r="X27" t="n">
-        <v>0.3428469598293304</v>
+        <v>0.08077079802751541</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.7208377122879028</v>
+        <v>0.8906164765357971</v>
       </c>
       <c r="Z27" t="n">
-        <v>-0.09718070924282074</v>
+        <v>0.1478596478700638</v>
       </c>
       <c r="AA27" t="n">
-        <v>-0.1843413561582565</v>
+        <v>0.2341778874397278</v>
       </c>
       <c r="AB27" t="n">
-        <v>-0.5171297788619995</v>
+        <v>-0.08724705874919891</v>
       </c>
       <c r="AC27" t="n">
-        <v>-0.1708753556013107</v>
+        <v>-0.3332515060901642</v>
       </c>
       <c r="AD27" t="n">
-        <v>-0.2236355543136597</v>
+        <v>-0.01017936784774065</v>
       </c>
       <c r="AE27" t="n">
-        <v>-0.07683888822793961</v>
+        <v>0.2601006627082825</v>
       </c>
       <c r="AF27" t="n">
-        <v>-0.2319940328598022</v>
+        <v>-0.2305840700864792</v>
       </c>
       <c r="AG27" t="n">
-        <v>-0.2569887936115265</v>
+        <v>-0.1739298105239868</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.09137926250696182</v>
+        <v>0.4687133133411407</v>
       </c>
       <c r="AI27" t="n">
-        <v>-0.2165560275316238</v>
+        <v>-0.05185772106051445</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.1510012894868851</v>
+        <v>-0.293626606464386</v>
       </c>
       <c r="AK27" t="n">
-        <v>-0.3015572130680084</v>
+        <v>-0.0265080202370882</v>
       </c>
       <c r="AL27" t="n">
-        <v>-0.9221499562263489</v>
+        <v>-1.08035933971405</v>
       </c>
       <c r="AM27" t="n">
-        <v>-0.2203744649887085</v>
+        <v>-0.3329824805259705</v>
       </c>
       <c r="AN27" t="n">
-        <v>-0.3665894865989685</v>
+        <v>0.4102547168731689</v>
       </c>
       <c r="AO27" t="n">
-        <v>0.2097559869289398</v>
+        <v>0.06485431641340256</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.2096383422613144</v>
+        <v>0.09509360790252686</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.02468932047486305</v>
+        <v>0.4905886650085449</v>
       </c>
       <c r="AR27" t="n">
-        <v>-0.3875883519649506</v>
+        <v>-0.5112311244010925</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.3374662399291992</v>
+        <v>0.2643099725246429</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.04417189583182335</v>
+        <v>0.04278337210416794</v>
       </c>
       <c r="AU27" t="n">
-        <v>0.0947597473859787</v>
+        <v>0.08502000570297241</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.2542013823986053</v>
+        <v>0.1677712947130203</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.5587210655212402</v>
+        <v>0.3467913568019867</v>
       </c>
       <c r="AX27" t="n">
-        <v>-0.1421733051538467</v>
+        <v>-0.2687188386917114</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -4717,154 +4717,154 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-0.295509546995163</v>
+        <v>0.1191775724291801</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.5445173978805542</v>
+        <v>-0.5189749598503113</v>
       </c>
       <c r="C28" t="n">
-        <v>0.082383893430233</v>
+        <v>-0.1241194680333138</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.1789524257183075</v>
+        <v>-0.15544293820858</v>
       </c>
       <c r="E28" t="n">
-        <v>0.09836610406637192</v>
+        <v>0.1776792109012604</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1967998892068863</v>
+        <v>0.03120698034763336</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.1993197649717331</v>
+        <v>0.1147757023572922</v>
       </c>
       <c r="H28" t="n">
-        <v>0.03360320627689362</v>
+        <v>0.3661312460899353</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4771147668361664</v>
+        <v>-0.1425804197788239</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0639406144618988</v>
+        <v>0.1375697702169418</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.1325581520795822</v>
+        <v>-0.3313907086849213</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.07042437046766281</v>
+        <v>0.2134007960557938</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.09994402527809143</v>
+        <v>-0.1181782782077789</v>
       </c>
       <c r="N28" t="n">
-        <v>0.4297729730606079</v>
+        <v>0.1042132452130318</v>
       </c>
       <c r="O28" t="n">
-        <v>0.0766649916768074</v>
+        <v>0.1091443970799446</v>
       </c>
       <c r="P28" t="n">
-        <v>0.1364618241786957</v>
+        <v>0.005035001318901777</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.1583127379417419</v>
+        <v>0.246208131313324</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.5412799715995789</v>
+        <v>-0.450861394405365</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.2711332440376282</v>
+        <v>-0.1744570732116699</v>
       </c>
       <c r="T28" t="n">
-        <v>0.09354328364133835</v>
+        <v>-0.1613740175962448</v>
       </c>
       <c r="U28" t="n">
-        <v>0.0651305690407753</v>
+        <v>-0.1536965817213058</v>
       </c>
       <c r="V28" t="n">
-        <v>-0.2621066272258759</v>
+        <v>0.0174532812088728</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.29387566447258</v>
+        <v>0.135362982749939</v>
       </c>
       <c r="X28" t="n">
-        <v>0.09760574251413345</v>
+        <v>0.09411659091711044</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.5258830785751343</v>
+        <v>0.4023696184158325</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.04067469388246536</v>
+        <v>-0.07800666242837906</v>
       </c>
       <c r="AA28" t="n">
-        <v>-0.0662781298160553</v>
+        <v>-0.003894712775945663</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.02481075935065746</v>
+        <v>-0.1006260961294174</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.003759089391678572</v>
+        <v>-0.2634360492229462</v>
       </c>
       <c r="AD28" t="n">
-        <v>-0.175236701965332</v>
+        <v>0.005225093569606543</v>
       </c>
       <c r="AE28" t="n">
-        <v>-0.006930746138095856</v>
+        <v>-0.01760905049741268</v>
       </c>
       <c r="AF28" t="n">
-        <v>-0.03690135851502419</v>
+        <v>-0.07263978570699692</v>
       </c>
       <c r="AG28" t="n">
-        <v>-0.150145947933197</v>
+        <v>-0.1437491029500961</v>
       </c>
       <c r="AH28" t="n">
-        <v>-0.2869992256164551</v>
+        <v>0.2186557948589325</v>
       </c>
       <c r="AI28" t="n">
-        <v>-0.1557068377733231</v>
+        <v>-0.122767262160778</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.09787217527627945</v>
+        <v>-0.3653545081615448</v>
       </c>
       <c r="AK28" t="n">
-        <v>-0.05147799849510193</v>
+        <v>0.2456593364477158</v>
       </c>
       <c r="AL28" t="n">
-        <v>-0.5963535308837891</v>
+        <v>-0.8093687891960144</v>
       </c>
       <c r="AM28" t="n">
-        <v>-0.2234586179256439</v>
+        <v>-0.07942201197147369</v>
       </c>
       <c r="AN28" t="n">
-        <v>0.1260510385036469</v>
+        <v>0.4192047417163849</v>
       </c>
       <c r="AO28" t="n">
-        <v>-0.05557646602392197</v>
+        <v>-0.02277173660695553</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.1785652637481689</v>
+        <v>0.03836636990308762</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.2088589668273926</v>
+        <v>0.2212255448102951</v>
       </c>
       <c r="AR28" t="n">
-        <v>-0.1891853958368301</v>
+        <v>-0.3319473266601562</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.2876235842704773</v>
+        <v>0.249336451292038</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.1938318014144897</v>
+        <v>0.0844307541847229</v>
       </c>
       <c r="AU28" t="n">
-        <v>-0.2801653742790222</v>
+        <v>0.05377713218331337</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.287970632314682</v>
+        <v>0.2353431135416031</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.2825904190540314</v>
+        <v>0.3712624609470367</v>
       </c>
       <c r="AX28" t="n">
-        <v>-0.2677344083786011</v>
+        <v>-0.24055315554142</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
@@ -4872,154 +4872,154 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>-0.3368038833141327</v>
+        <v>-0.03352048620581627</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.4591620266437531</v>
+        <v>-0.7127429842948914</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.01517118606716394</v>
+        <v>-0.2758408486843109</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.2694836258888245</v>
+        <v>-0.2718462944030762</v>
       </c>
       <c r="E29" t="n">
-        <v>0.001143125118687749</v>
+        <v>0.03619689866900444</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3498294055461884</v>
+        <v>-0.001278056995943189</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.2438530921936035</v>
+        <v>0.2711741626262665</v>
       </c>
       <c r="H29" t="n">
-        <v>0.03997509554028511</v>
+        <v>0.3758115768432617</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5222368836402893</v>
+        <v>-0.04485554993152618</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0208334531635046</v>
+        <v>0.2049143761396408</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.2779229581356049</v>
+        <v>-0.4185566306114197</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.1183900311589241</v>
+        <v>0.09135672450065613</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0312843956053257</v>
+        <v>-0.1930113285779953</v>
       </c>
       <c r="N29" t="n">
-        <v>0.4846958518028259</v>
+        <v>0.04300776869058609</v>
       </c>
       <c r="O29" t="n">
-        <v>0.1754824668169022</v>
+        <v>0.1395698189735413</v>
       </c>
       <c r="P29" t="n">
-        <v>0.05378749221563339</v>
+        <v>0.009335235692560673</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.1523181051015854</v>
+        <v>0.2027955055236816</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.6417025327682495</v>
+        <v>-0.5370705723762512</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.1548382639884949</v>
+        <v>-0.2433531731367111</v>
       </c>
       <c r="T29" t="n">
-        <v>0.155961811542511</v>
+        <v>-0.09301868826150894</v>
       </c>
       <c r="U29" t="n">
-        <v>0.1218288093805313</v>
+        <v>-0.1317859888076782</v>
       </c>
       <c r="V29" t="n">
-        <v>-0.1839580088853836</v>
+        <v>0.04871966317296028</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.1823417097330093</v>
+        <v>0.2953532040119171</v>
       </c>
       <c r="X29" t="n">
-        <v>0.1084411516785622</v>
+        <v>0.00724107725545764</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.6364014744758606</v>
+        <v>0.3010294735431671</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.07542454451322556</v>
+        <v>-0.2927177846431732</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.03238599002361298</v>
+        <v>0.1227906495332718</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.1975035667419434</v>
+        <v>-0.1095524802803993</v>
       </c>
       <c r="AC29" t="n">
-        <v>-0.1423897296190262</v>
+        <v>-0.3276208639144897</v>
       </c>
       <c r="AD29" t="n">
-        <v>-0.2824976146221161</v>
+        <v>0.1302740126848221</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.05977290123701096</v>
+        <v>-0.01812385767698288</v>
       </c>
       <c r="AF29" t="n">
-        <v>-0.0675317719578743</v>
+        <v>-0.1766022145748138</v>
       </c>
       <c r="AG29" t="n">
-        <v>-0.1649223417043686</v>
+        <v>0.1318397372961044</v>
       </c>
       <c r="AH29" t="n">
-        <v>-0.3099880814552307</v>
+        <v>0.183152824640274</v>
       </c>
       <c r="AI29" t="n">
-        <v>-0.1034825295209885</v>
+        <v>-0.2232217192649841</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.0803525522351265</v>
+        <v>-0.209941104054451</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.07782029360532761</v>
+        <v>0.270176500082016</v>
       </c>
       <c r="AL29" t="n">
-        <v>-0.6854294538497925</v>
+        <v>-0.7556084990501404</v>
       </c>
       <c r="AM29" t="n">
-        <v>-0.1589806526899338</v>
+        <v>-0.06418302655220032</v>
       </c>
       <c r="AN29" t="n">
-        <v>0.137886255979538</v>
+        <v>0.5805206298828125</v>
       </c>
       <c r="AO29" t="n">
-        <v>-0.163948580622673</v>
+        <v>-0.2003181874752045</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.1293198317289352</v>
+        <v>0.09584696590900421</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.1172235980629921</v>
+        <v>0.09877505153417587</v>
       </c>
       <c r="AR29" t="n">
-        <v>-0.2267193198204041</v>
+        <v>-0.3608549237251282</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.3373293280601501</v>
+        <v>0.06356260925531387</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.2883453369140625</v>
+        <v>0.1413790285587311</v>
       </c>
       <c r="AU29" t="n">
-        <v>-0.2156551480293274</v>
+        <v>0.04119857773184776</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.3899125456809998</v>
+        <v>0.1651537120342255</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.152479812502861</v>
+        <v>0.3655352592468262</v>
       </c>
       <c r="AX29" t="n">
-        <v>-0.390791267156601</v>
+        <v>-0.3304347097873688</v>
       </c>
       <c r="AY29" t="n">
         <v>0</v>
@@ -5027,154 +5027,154 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>-0.2544001042842865</v>
+        <v>0.1102151647210121</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.5364010334014893</v>
+        <v>-0.5944420099258423</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.009678810834884644</v>
+        <v>-0.2128561288118362</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.2552158832550049</v>
+        <v>-0.2078393548727036</v>
       </c>
       <c r="E30" t="n">
-        <v>0.03591815754771233</v>
+        <v>0.07580301910638809</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.139263242483139</v>
+        <v>0.05752861127257347</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.2183225601911545</v>
+        <v>0.2570784389972687</v>
       </c>
       <c r="H30" t="n">
-        <v>0.02755152992904186</v>
+        <v>0.2726455628871918</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4370448887348175</v>
+        <v>-0.1024853512644768</v>
       </c>
       <c r="J30" t="n">
-        <v>0.04782230034470558</v>
+        <v>0.05942114070057869</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.1857647150754929</v>
+        <v>-0.457775354385376</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.137920930981636</v>
+        <v>0.26258584856987</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.02994443848729134</v>
+        <v>-0.1755761504173279</v>
       </c>
       <c r="N30" t="n">
-        <v>0.3984327018260956</v>
+        <v>0.08547545224428177</v>
       </c>
       <c r="O30" t="n">
-        <v>0.02143481932580471</v>
+        <v>0.08605013787746429</v>
       </c>
       <c r="P30" t="n">
-        <v>0.1667680293321609</v>
+        <v>0.1407328099012375</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.1503743380308151</v>
+        <v>0.1857363134622574</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.6435976028442383</v>
+        <v>-0.5523729920387268</v>
       </c>
       <c r="S30" t="n">
-        <v>-0.1888643503189087</v>
+        <v>-0.1751471608877182</v>
       </c>
       <c r="T30" t="n">
-        <v>0.1908001005649567</v>
+        <v>-0.1083922609686852</v>
       </c>
       <c r="U30" t="n">
-        <v>0.08243545144796371</v>
+        <v>-0.07540633529424667</v>
       </c>
       <c r="V30" t="n">
-        <v>-0.2222974300384521</v>
+        <v>0.1235264539718628</v>
       </c>
       <c r="W30" t="n">
-        <v>-0.1999359130859375</v>
+        <v>0.2736785411834717</v>
       </c>
       <c r="X30" t="n">
-        <v>0.130389392375946</v>
+        <v>-0.09274321794509888</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.5093063116073608</v>
+        <v>0.3436147272586823</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.06165532395243645</v>
+        <v>-0.1721283495426178</v>
       </c>
       <c r="AA30" t="n">
-        <v>-0.1433292776346207</v>
+        <v>0.02820112928748131</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.000111280387500301</v>
+        <v>-0.02094119973480701</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.06016863882541656</v>
+        <v>-0.2620542645454407</v>
       </c>
       <c r="AD30" t="n">
-        <v>-0.352295994758606</v>
+        <v>0.04369144514203072</v>
       </c>
       <c r="AE30" t="n">
-        <v>-0.02965192310512066</v>
+        <v>0.05272326990962029</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.00349548296071589</v>
+        <v>-0.02020195499062538</v>
       </c>
       <c r="AG30" t="n">
-        <v>-0.1342828422784805</v>
+        <v>-0.1131015345454216</v>
       </c>
       <c r="AH30" t="n">
-        <v>-0.2125719487667084</v>
+        <v>0.2353470921516418</v>
       </c>
       <c r="AI30" t="n">
-        <v>-0.1292978823184967</v>
+        <v>-0.02828232571482658</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.1109673380851746</v>
+        <v>-0.2579228281974792</v>
       </c>
       <c r="AK30" t="n">
-        <v>-0.1327672898769379</v>
+        <v>0.3294366002082825</v>
       </c>
       <c r="AL30" t="n">
-        <v>-0.6860457062721252</v>
+        <v>-0.6587677597999573</v>
       </c>
       <c r="AM30" t="n">
-        <v>-0.2042293697595596</v>
+        <v>-0.0003351044724695385</v>
       </c>
       <c r="AN30" t="n">
-        <v>0.1877136379480362</v>
+        <v>0.5716031193733215</v>
       </c>
       <c r="AO30" t="n">
-        <v>-0.0004706860345322639</v>
+        <v>-0.170895978808403</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.1078546643257141</v>
+        <v>0.05525071918964386</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.08432508260011673</v>
+        <v>0.1585128307342529</v>
       </c>
       <c r="AR30" t="n">
-        <v>-0.1625520288944244</v>
+        <v>-0.4460108280181885</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.2840904891490936</v>
+        <v>0.1988406181335449</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.3995945751667023</v>
+        <v>0.1704430729150772</v>
       </c>
       <c r="AU30" t="n">
-        <v>-0.3004270792007446</v>
+        <v>-0.02571647241711617</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.3340096473693848</v>
+        <v>0.1595733016729355</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.2763828933238983</v>
+        <v>0.2730949819087982</v>
       </c>
       <c r="AX30" t="n">
-        <v>-0.208742767572403</v>
+        <v>-0.3171145021915436</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
@@ -5182,154 +5182,154 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-0.2820712924003601</v>
+        <v>0.07561572641134262</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.5403656959533691</v>
+        <v>-0.5416920185089111</v>
       </c>
       <c r="C31" t="n">
-        <v>0.02817724272608757</v>
+        <v>-0.1011592298746109</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.1271692216396332</v>
+        <v>-0.2429917454719543</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1372807770967484</v>
+        <v>0.09174363315105438</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1929183304309845</v>
+        <v>0.1120619475841522</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.263689249753952</v>
+        <v>0.08827824890613556</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.006190774030983448</v>
+        <v>0.270697146654129</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5569882988929749</v>
+        <v>-0.08748983591794968</v>
       </c>
       <c r="J31" t="n">
-        <v>0.07905469089746475</v>
+        <v>0.03026525117456913</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.1619345992803574</v>
+        <v>-0.3686150014400482</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.02453642152249813</v>
+        <v>0.1926205605268478</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.139511913061142</v>
+        <v>-0.1971096843481064</v>
       </c>
       <c r="N31" t="n">
-        <v>0.5067102909088135</v>
+        <v>0.06342577934265137</v>
       </c>
       <c r="O31" t="n">
-        <v>0.1487134397029877</v>
+        <v>0.1406759023666382</v>
       </c>
       <c r="P31" t="n">
-        <v>0.1563949435949326</v>
+        <v>-0.01061390992254019</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.1083179414272308</v>
+        <v>0.2697220146656036</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.4811441898345947</v>
+        <v>-0.4358629584312439</v>
       </c>
       <c r="S31" t="n">
-        <v>-0.2164649665355682</v>
+        <v>-0.2122936546802521</v>
       </c>
       <c r="T31" t="n">
-        <v>0.01382806245237589</v>
+        <v>-0.2495946735143661</v>
       </c>
       <c r="U31" t="n">
-        <v>0.08330308645963669</v>
+        <v>-0.1006636843085289</v>
       </c>
       <c r="V31" t="n">
-        <v>-0.2489459067583084</v>
+        <v>-0.08270873129367828</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.259998619556427</v>
+        <v>0.1837861090898514</v>
       </c>
       <c r="X31" t="n">
-        <v>0.1672226935625076</v>
+        <v>0.05911262705922127</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.5294957160949707</v>
+        <v>0.3236274421215057</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.05477802455425262</v>
+        <v>-0.1491388529539108</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.1392858922481537</v>
+        <v>-0.02425585687160492</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.06514950096607208</v>
+        <v>-0.09030281007289886</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.03153597190976143</v>
+        <v>-0.2838416993618011</v>
       </c>
       <c r="AD31" t="n">
-        <v>-0.2194433063268661</v>
+        <v>0.01273901294916868</v>
       </c>
       <c r="AE31" t="n">
-        <v>-0.02476072870194912</v>
+        <v>-0.03642343729734421</v>
       </c>
       <c r="AF31" t="n">
-        <v>-0.0985102504491806</v>
+        <v>-0.04756220802664757</v>
       </c>
       <c r="AG31" t="n">
-        <v>-0.1993050873279572</v>
+        <v>-0.1077364981174469</v>
       </c>
       <c r="AH31" t="n">
-        <v>-0.2160748243331909</v>
+        <v>0.2133029252290726</v>
       </c>
       <c r="AI31" t="n">
-        <v>-0.1996743083000183</v>
+        <v>-0.1117062419652939</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.09200087934732437</v>
+        <v>-0.273895800113678</v>
       </c>
       <c r="AK31" t="n">
-        <v>-0.0818214938044548</v>
+        <v>0.3535126149654388</v>
       </c>
       <c r="AL31" t="n">
-        <v>-0.6133798956871033</v>
+        <v>-0.928156316280365</v>
       </c>
       <c r="AM31" t="n">
-        <v>-0.2533270120620728</v>
+        <v>-0.0439557284116745</v>
       </c>
       <c r="AN31" t="n">
-        <v>0.07744685560464859</v>
+        <v>0.480886697769165</v>
       </c>
       <c r="AO31" t="n">
-        <v>-0.09012067317962646</v>
+        <v>-0.07126270979642868</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.1859003603458405</v>
+        <v>0.01363079529255629</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.267850935459137</v>
+        <v>0.1708496361970901</v>
       </c>
       <c r="AR31" t="n">
-        <v>-0.2063415795564651</v>
+        <v>-0.3945772051811218</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.2774916887283325</v>
+        <v>0.2048893123865128</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.2980066537857056</v>
+        <v>0.1009458974003792</v>
       </c>
       <c r="AU31" t="n">
-        <v>-0.2489627301692963</v>
+        <v>0.1842600256204605</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.3177759349346161</v>
+        <v>0.2199324071407318</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.2310097515583038</v>
+        <v>0.4360560476779938</v>
       </c>
       <c r="AX31" t="n">
-        <v>-0.2906952500343323</v>
+        <v>-0.2521582841873169</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
@@ -5337,154 +5337,154 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-0.2756674289703369</v>
+        <v>0.1944008469581604</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.5296071171760559</v>
+        <v>-0.6095786690711975</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0197102315723896</v>
+        <v>-0.2015876173973083</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.296490490436554</v>
+        <v>-0.1596071422100067</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1126031950116158</v>
+        <v>0.1450434327125549</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1470761895179749</v>
+        <v>-0.003259225282818079</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.2391299456357956</v>
+        <v>0.2320606112480164</v>
       </c>
       <c r="H32" t="n">
-        <v>0.00522942841053009</v>
+        <v>0.2778263688087463</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3770991563796997</v>
+        <v>-0.05308376997709274</v>
       </c>
       <c r="J32" t="n">
-        <v>0.07590923458337784</v>
+        <v>0.0805184617638588</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.1641078442335129</v>
+        <v>-0.5187525749206543</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.1254385709762573</v>
+        <v>0.2380476444959641</v>
       </c>
       <c r="M32" t="n">
-        <v>0.01815841719508171</v>
+        <v>-0.1191897913813591</v>
       </c>
       <c r="N32" t="n">
-        <v>0.4076916575431824</v>
+        <v>0.09432642906904221</v>
       </c>
       <c r="O32" t="n">
-        <v>0.0217705462127924</v>
+        <v>0.05966656282544136</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2370924055576324</v>
+        <v>0.04166267067193985</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.1230079904198647</v>
+        <v>0.2860516309738159</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.6452858448028564</v>
+        <v>-0.391373485326767</v>
       </c>
       <c r="S32" t="n">
-        <v>-0.195075586438179</v>
+        <v>-0.1435982882976532</v>
       </c>
       <c r="T32" t="n">
-        <v>0.1740953028202057</v>
+        <v>-0.1581682562828064</v>
       </c>
       <c r="U32" t="n">
-        <v>0.04773780331015587</v>
+        <v>-0.07154446840286255</v>
       </c>
       <c r="V32" t="n">
-        <v>-0.211074635386467</v>
+        <v>0.2623523473739624</v>
       </c>
       <c r="W32" t="n">
-        <v>-0.2896923720836639</v>
+        <v>0.2188798785209656</v>
       </c>
       <c r="X32" t="n">
-        <v>0.02688405476510525</v>
+        <v>-0.07286234945058823</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.4794144332408905</v>
+        <v>0.3443313837051392</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.1003019511699677</v>
+        <v>-0.135705754160881</v>
       </c>
       <c r="AA32" t="n">
-        <v>-0.1859513521194458</v>
+        <v>0.008251779712736607</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.1164112165570259</v>
+        <v>0.002490735379979014</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.008350221440196037</v>
+        <v>-0.2028234452009201</v>
       </c>
       <c r="AD32" t="n">
-        <v>-0.272758424282074</v>
+        <v>0.1028122752904892</v>
       </c>
       <c r="AE32" t="n">
-        <v>-0.04786698892712593</v>
+        <v>0.05641765892505646</v>
       </c>
       <c r="AF32" t="n">
-        <v>-0.008182738907635212</v>
+        <v>-0.04581315815448761</v>
       </c>
       <c r="AG32" t="n">
-        <v>-0.08557769656181335</v>
+        <v>-0.1443662196397781</v>
       </c>
       <c r="AH32" t="n">
-        <v>-0.203723356127739</v>
+        <v>0.119238555431366</v>
       </c>
       <c r="AI32" t="n">
-        <v>-0.1608547121286392</v>
+        <v>-0.1194809973239899</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.04683481156826019</v>
+        <v>-0.2707687318325043</v>
       </c>
       <c r="AK32" t="n">
-        <v>-0.09284819662570953</v>
+        <v>0.3266556262969971</v>
       </c>
       <c r="AL32" t="n">
-        <v>-0.6325212717056274</v>
+        <v>-0.7228134870529175</v>
       </c>
       <c r="AM32" t="n">
-        <v>-0.2678967714309692</v>
+        <v>0.04846124351024628</v>
       </c>
       <c r="AN32" t="n">
-        <v>0.1808481067419052</v>
+        <v>0.5474149584770203</v>
       </c>
       <c r="AO32" t="n">
-        <v>-0.07806981354951859</v>
+        <v>-0.1651909947395325</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.1652644574642181</v>
+        <v>0.02153456024825573</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.1064582988619804</v>
+        <v>0.187746673822403</v>
       </c>
       <c r="AR32" t="n">
-        <v>-0.1629941016435623</v>
+        <v>-0.411386638879776</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.2270033359527588</v>
+        <v>0.2128430604934692</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.4128548204898834</v>
+        <v>0.1116900965571404</v>
       </c>
       <c r="AU32" t="n">
-        <v>-0.3311153948307037</v>
+        <v>0.01091969478875399</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.2734715044498444</v>
+        <v>0.1771335452795029</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.2933557033538818</v>
+        <v>0.274999588727951</v>
       </c>
       <c r="AX32" t="n">
-        <v>-0.1651518940925598</v>
+        <v>-0.3318552374839783</v>
       </c>
       <c r="AY32" t="n">
         <v>0</v>
@@ -5492,154 +5492,154 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-0.397477000951767</v>
+        <v>0.1476950198411942</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.4739836156368256</v>
+        <v>-0.6943926811218262</v>
       </c>
       <c r="C33" t="n">
-        <v>0.07789052277803421</v>
+        <v>-0.2688000202178955</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1283562183380127</v>
+        <v>-0.07719656080007553</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1573589891195297</v>
+        <v>0.2327730804681778</v>
       </c>
       <c r="F33" t="n">
-        <v>0.02907702513039112</v>
+        <v>0.1335026472806931</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.06139378249645233</v>
+        <v>-0.0008993845549412072</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1596910655498505</v>
+        <v>0.4629156589508057</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5777111053466797</v>
+        <v>-0.1883660703897476</v>
       </c>
       <c r="J33" t="n">
-        <v>-4.394197458168492e-05</v>
+        <v>0.2902064919471741</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.006820742040872574</v>
+        <v>-0.3528996407985687</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.2014432847499847</v>
+        <v>0.4726667404174805</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.03592783957719803</v>
+        <v>-0.04289963468909264</v>
       </c>
       <c r="N33" t="n">
-        <v>0.5233867168426514</v>
+        <v>0.1252545714378357</v>
       </c>
       <c r="O33" t="n">
-        <v>0.1975567936897278</v>
+        <v>0.1384382843971252</v>
       </c>
       <c r="P33" t="n">
-        <v>0.3315143585205078</v>
+        <v>-0.09933757781982422</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.3349686563014984</v>
+        <v>0.3379436135292053</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.5595851540565491</v>
+        <v>-0.3141609132289886</v>
       </c>
       <c r="S33" t="n">
-        <v>-0.451510101556778</v>
+        <v>-0.3041837513446808</v>
       </c>
       <c r="T33" t="n">
-        <v>0.1324636191129684</v>
+        <v>-0.3045696616172791</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.131353497505188</v>
+        <v>-0.2115223258733749</v>
       </c>
       <c r="V33" t="n">
-        <v>-0.417164534330368</v>
+        <v>-0.06452792137861252</v>
       </c>
       <c r="W33" t="n">
-        <v>-0.2168330401182175</v>
+        <v>0.09804951399564743</v>
       </c>
       <c r="X33" t="n">
-        <v>0.1562396436929703</v>
+        <v>0.1922269463539124</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.6342669129371643</v>
+        <v>0.6155471205711365</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.09698174148797989</v>
+        <v>0.08625243604183197</v>
       </c>
       <c r="AA33" t="n">
-        <v>-0.05806320533156395</v>
+        <v>0.03149299696087837</v>
       </c>
       <c r="AB33" t="n">
-        <v>-0.1905626505613327</v>
+        <v>-0.2574444711208344</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.07266253232955933</v>
+        <v>-0.2975701093673706</v>
       </c>
       <c r="AD33" t="n">
-        <v>-0.2194509357213974</v>
+        <v>-0.04381057247519493</v>
       </c>
       <c r="AE33" t="n">
-        <v>-0.01683482527732849</v>
+        <v>-0.008000032044947147</v>
       </c>
       <c r="AF33" t="n">
-        <v>-0.3250482678413391</v>
+        <v>0.07713743299245834</v>
       </c>
       <c r="AG33" t="n">
-        <v>-0.2045860588550568</v>
+        <v>0.2200519591569901</v>
       </c>
       <c r="AH33" t="n">
-        <v>-0.2405297160148621</v>
+        <v>0.2586585581302643</v>
       </c>
       <c r="AI33" t="n">
-        <v>-0.2901831865310669</v>
+        <v>-0.3324173986911774</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.3231562077999115</v>
+        <v>-0.4766149520874023</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.1111352071166039</v>
+        <v>-0.009932766668498516</v>
       </c>
       <c r="AL33" t="n">
-        <v>-0.6362254023551941</v>
+        <v>-0.802490770816803</v>
       </c>
       <c r="AM33" t="n">
-        <v>-0.05356269702315331</v>
+        <v>-0.292947381734848</v>
       </c>
       <c r="AN33" t="n">
-        <v>-0.1442511230707169</v>
+        <v>0.4162917137145996</v>
       </c>
       <c r="AO33" t="n">
-        <v>-0.1278512179851532</v>
+        <v>0.003979475703090429</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.2153482139110565</v>
+        <v>0.05927767232060432</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.2108907550573349</v>
+        <v>0.5868012309074402</v>
       </c>
       <c r="AR33" t="n">
-        <v>-0.4162647128105164</v>
+        <v>-0.1688279807567596</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.1712823659181595</v>
+        <v>0.331850528717041</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.1235609278082848</v>
+        <v>-0.01730599440634251</v>
       </c>
       <c r="AU33" t="n">
-        <v>-0.1431176215410233</v>
+        <v>-0.1901340186595917</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.205217644572258</v>
+        <v>0.3785942792892456</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.340173602104187</v>
+        <v>0.2624552547931671</v>
       </c>
       <c r="AX33" t="n">
-        <v>-0.1160770133137703</v>
+        <v>-0.2887995541095734</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
@@ -5647,154 +5647,154 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>-0.2829754650592804</v>
+        <v>0.1131423860788345</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.5812587738037109</v>
+        <v>-0.5382398962974548</v>
       </c>
       <c r="C34" t="n">
-        <v>0.05888726562261581</v>
+        <v>-0.08734936267137527</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.1664683222770691</v>
+        <v>-0.1745570152997971</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1170173361897469</v>
+        <v>0.1430589407682419</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.08232089132070541</v>
+        <v>0.1387391984462738</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.241151750087738</v>
+        <v>0.008447141386568546</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.02117647975683212</v>
+        <v>0.3861387968063354</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5191332697868347</v>
+        <v>-0.1577979028224945</v>
       </c>
       <c r="J34" t="n">
-        <v>0.1086382940411568</v>
+        <v>0.1283494681119919</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.09194770455360413</v>
+        <v>-0.2599768936634064</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.04531850665807724</v>
+        <v>0.2994987964630127</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.1746398061513901</v>
+        <v>-0.1327847838401794</v>
       </c>
       <c r="N34" t="n">
-        <v>0.4311169385910034</v>
+        <v>0.1196869611740112</v>
       </c>
       <c r="O34" t="n">
-        <v>0.08435730636119843</v>
+        <v>0.1033219695091248</v>
       </c>
       <c r="P34" t="n">
-        <v>0.141352191567421</v>
+        <v>0.02541241236031055</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.1656771004199982</v>
+        <v>0.2298768907785416</v>
       </c>
       <c r="R34" t="n">
-        <v>-0.5143737196922302</v>
+        <v>-0.5010303258895874</v>
       </c>
       <c r="S34" t="n">
-        <v>-0.3646314144134521</v>
+        <v>-0.1796073615550995</v>
       </c>
       <c r="T34" t="n">
-        <v>0.05245555937290192</v>
+        <v>-0.1899223923683167</v>
       </c>
       <c r="U34" t="n">
-        <v>0.05850829184055328</v>
+        <v>-0.1884600669145584</v>
       </c>
       <c r="V34" t="n">
-        <v>-0.2749247848987579</v>
+        <v>-0.07886634021997452</v>
       </c>
       <c r="W34" t="n">
-        <v>-0.2436417043209076</v>
+        <v>0.1624385863542557</v>
       </c>
       <c r="X34" t="n">
-        <v>0.1920808702707291</v>
+        <v>0.1496365517377853</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.6016882658004761</v>
+        <v>0.4336199760437012</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.01416959706693888</v>
+        <v>-0.01771485805511475</v>
       </c>
       <c r="AA34" t="n">
-        <v>-0.08407275378704071</v>
+        <v>-0.1058528125286102</v>
       </c>
       <c r="AB34" t="n">
-        <v>-0.08510253578424454</v>
+        <v>-0.1743685156106949</v>
       </c>
       <c r="AC34" t="n">
-        <v>-0.02666456066071987</v>
+        <v>-0.2568698227405548</v>
       </c>
       <c r="AD34" t="n">
-        <v>-0.1735179275274277</v>
+        <v>0.01153968460857868</v>
       </c>
       <c r="AE34" t="n">
-        <v>-0.01586988009512424</v>
+        <v>-0.01867251470685005</v>
       </c>
       <c r="AF34" t="n">
-        <v>-0.1061442419886589</v>
+        <v>-0.05080606788396835</v>
       </c>
       <c r="AG34" t="n">
-        <v>-0.138386070728302</v>
+        <v>-0.1172033846378326</v>
       </c>
       <c r="AH34" t="n">
-        <v>-0.2927269339561462</v>
+        <v>0.2009976953268051</v>
       </c>
       <c r="AI34" t="n">
-        <v>-0.2006676644086838</v>
+        <v>-0.1211255937814713</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.08520763367414474</v>
+        <v>-0.402037650346756</v>
       </c>
       <c r="AK34" t="n">
-        <v>-0.06725821644067764</v>
+        <v>0.2924222946166992</v>
       </c>
       <c r="AL34" t="n">
-        <v>-0.5894542336463928</v>
+        <v>-0.8564521670341492</v>
       </c>
       <c r="AM34" t="n">
-        <v>-0.2194957584142685</v>
+        <v>-0.1119799315929413</v>
       </c>
       <c r="AN34" t="n">
-        <v>0.07793308049440384</v>
+        <v>0.4205013811588287</v>
       </c>
       <c r="AO34" t="n">
-        <v>-0.001963287126272917</v>
+        <v>-0.02003021724522114</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.2091369479894638</v>
+        <v>-0.009527037851512432</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.2945930659770966</v>
+        <v>0.2263200283050537</v>
       </c>
       <c r="AR34" t="n">
-        <v>-0.2344335168600082</v>
+        <v>-0.313767671585083</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.2991396486759186</v>
+        <v>0.2887647747993469</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.1562467366456985</v>
+        <v>0.1084512025117874</v>
       </c>
       <c r="AU34" t="n">
-        <v>-0.2334625720977783</v>
+        <v>0.05113288387656212</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.2400321960449219</v>
+        <v>0.2819808721542358</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.3284823298454285</v>
+        <v>0.3749347627162933</v>
       </c>
       <c r="AX34" t="n">
-        <v>-0.3209861516952515</v>
+        <v>-0.2516006231307983</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
@@ -5802,154 +5802,154 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-0.3029104769229889</v>
+        <v>0.1336623877286911</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.4526813924312592</v>
+        <v>-0.5928842425346375</v>
       </c>
       <c r="C35" t="n">
-        <v>0.01917929761111736</v>
+        <v>-0.1794181913137436</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.3343533873558044</v>
+        <v>-0.2508441805839539</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01240204181522131</v>
+        <v>0.02625641599297523</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2820332646369934</v>
+        <v>0.02373869158327579</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.1377004832029343</v>
+        <v>0.199496328830719</v>
       </c>
       <c r="H35" t="n">
-        <v>0.064924456179142</v>
+        <v>0.2218419909477234</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4382400512695312</v>
+        <v>-0.02989954128861427</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0412713848054409</v>
+        <v>0.1834351122379303</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.2409214675426483</v>
+        <v>-0.4716387093067169</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.2072818279266357</v>
+        <v>0.247137188911438</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.01047368347644806</v>
+        <v>-0.09926001727581024</v>
       </c>
       <c r="N35" t="n">
-        <v>0.48173588514328</v>
+        <v>0.02630515769124031</v>
       </c>
       <c r="O35" t="n">
-        <v>0.03790381923317909</v>
+        <v>0.1102845072746277</v>
       </c>
       <c r="P35" t="n">
-        <v>0.1459830403327942</v>
+        <v>0.1250601708889008</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.2005191594362259</v>
+        <v>0.2468532919883728</v>
       </c>
       <c r="R35" t="n">
-        <v>-0.6809177994728088</v>
+        <v>-0.4023231863975525</v>
       </c>
       <c r="S35" t="n">
-        <v>-0.1103726848959923</v>
+        <v>-0.1749145090579987</v>
       </c>
       <c r="T35" t="n">
-        <v>0.154888316988945</v>
+        <v>-0.07794179022312164</v>
       </c>
       <c r="U35" t="n">
-        <v>0.08608164638280869</v>
+        <v>-0.1054399162530899</v>
       </c>
       <c r="V35" t="n">
-        <v>-0.2364650368690491</v>
+        <v>0.2446670830249786</v>
       </c>
       <c r="W35" t="n">
-        <v>-0.2901802361011505</v>
+        <v>0.1518677622079849</v>
       </c>
       <c r="X35" t="n">
-        <v>0.1615365743637085</v>
+        <v>-0.04265860095620155</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.4831665456295013</v>
+        <v>0.3974205851554871</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.1278802305459976</v>
+        <v>-0.1631958186626434</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.0994880273938179</v>
+        <v>0.08780615031719208</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.06010224297642708</v>
+        <v>-0.006569284945726395</v>
       </c>
       <c r="AC35" t="n">
-        <v>-0.07090172171592712</v>
+        <v>-0.1833267360925674</v>
       </c>
       <c r="AD35" t="n">
-        <v>-0.230266273021698</v>
+        <v>0.07284298539161682</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.03752557560801506</v>
+        <v>0.08830410242080688</v>
       </c>
       <c r="AF35" t="n">
-        <v>-0.08335259556770325</v>
+        <v>-0.09730936586856842</v>
       </c>
       <c r="AG35" t="n">
-        <v>-0.1639830470085144</v>
+        <v>-0.1250380575656891</v>
       </c>
       <c r="AH35" t="n">
-        <v>-0.1988003849983215</v>
+        <v>0.2081783562898636</v>
       </c>
       <c r="AI35" t="n">
-        <v>-0.1823399662971497</v>
+        <v>-0.1199298202991486</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.04917630925774574</v>
+        <v>-0.2418210208415985</v>
       </c>
       <c r="AK35" t="n">
-        <v>-0.0915771946310997</v>
+        <v>0.2951653897762299</v>
       </c>
       <c r="AL35" t="n">
-        <v>-0.5731701254844666</v>
+        <v>-0.791303277015686</v>
       </c>
       <c r="AM35" t="n">
-        <v>-0.157856673002243</v>
+        <v>-0.03106564655900002</v>
       </c>
       <c r="AN35" t="n">
-        <v>0.0598854161798954</v>
+        <v>0.529309093952179</v>
       </c>
       <c r="AO35" t="n">
-        <v>-0.06727298349142075</v>
+        <v>-0.1149245873093605</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.07003334909677505</v>
+        <v>0.09097468852996826</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.09125779569149017</v>
+        <v>0.1683145612478256</v>
       </c>
       <c r="AR35" t="n">
-        <v>-0.191010445356369</v>
+        <v>-0.3905806839466095</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.2815387845039368</v>
+        <v>0.1351038813591003</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.3380894660949707</v>
+        <v>0.01269206684082747</v>
       </c>
       <c r="AU35" t="n">
-        <v>-0.3002738952636719</v>
+        <v>0.06868679821491241</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.2734273672103882</v>
+        <v>0.112354502081871</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.2327199578285217</v>
+        <v>0.3292370140552521</v>
       </c>
       <c r="AX35" t="n">
-        <v>-0.2731145322322845</v>
+        <v>-0.3444041609764099</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
@@ -5957,154 +5957,154 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>-0.2989478707313538</v>
+        <v>0.08287421613931656</v>
       </c>
       <c r="B36" t="n">
-        <v>-0.5854966044425964</v>
+        <v>-0.6095635294914246</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1491034626960754</v>
+        <v>-0.0718701183795929</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1360334157943726</v>
+        <v>-0.270259290933609</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.01060913503170013</v>
+        <v>-0.1096969023346901</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.1423993408679962</v>
+        <v>0.2096774280071259</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1475146561861038</v>
+        <v>-0.03022208623588085</v>
       </c>
       <c r="H36" t="n">
-        <v>0.3661417663097382</v>
+        <v>0.07133816182613373</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5970767736434937</v>
+        <v>-0.3759582340717316</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.02883291058242321</v>
+        <v>0.2200490236282349</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.3288764953613281</v>
+        <v>-0.4125688970088959</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.06419859826564789</v>
+        <v>0.6240824460983276</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.3612057268619537</v>
+        <v>-0.03567910939455032</v>
       </c>
       <c r="N36" t="n">
-        <v>0.5697523355484009</v>
+        <v>0.2073895931243896</v>
       </c>
       <c r="O36" t="n">
-        <v>0.07961104810237885</v>
+        <v>0.1063181310892105</v>
       </c>
       <c r="P36" t="n">
-        <v>0.1826402693986893</v>
+        <v>0.2153432369232178</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.3025706708431244</v>
+        <v>0.3920446932315826</v>
       </c>
       <c r="R36" t="n">
-        <v>-0.6298701763153076</v>
+        <v>-0.3950333297252655</v>
       </c>
       <c r="S36" t="n">
-        <v>-0.3248213529586792</v>
+        <v>-0.3214712738990784</v>
       </c>
       <c r="T36" t="n">
-        <v>-0.02190804667770863</v>
+        <v>-0.03546909242868423</v>
       </c>
       <c r="U36" t="n">
-        <v>0.08597391843795776</v>
+        <v>-0.2977922260761261</v>
       </c>
       <c r="V36" t="n">
-        <v>-0.5352312922477722</v>
+        <v>0.03958863392472267</v>
       </c>
       <c r="W36" t="n">
-        <v>-0.2986168265342712</v>
+        <v>0.05820364877581596</v>
       </c>
       <c r="X36" t="n">
-        <v>0.2669108510017395</v>
+        <v>0.0565011091530323</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.637919545173645</v>
+        <v>0.7758286595344543</v>
       </c>
       <c r="Z36" t="n">
-        <v>-0.03778208419680595</v>
+        <v>0.1272702515125275</v>
       </c>
       <c r="AA36" t="n">
-        <v>-0.1396734416484833</v>
+        <v>0.1242404133081436</v>
       </c>
       <c r="AB36" t="n">
-        <v>-0.3808220028877258</v>
+        <v>-0.06014299392700195</v>
       </c>
       <c r="AC36" t="n">
-        <v>-0.1647203415632248</v>
+        <v>-0.2936696708202362</v>
       </c>
       <c r="AD36" t="n">
-        <v>-0.2547014951705933</v>
+        <v>0.08785823732614517</v>
       </c>
       <c r="AE36" t="n">
-        <v>-0.02678355947136879</v>
+        <v>0.1775977909564972</v>
       </c>
       <c r="AF36" t="n">
-        <v>-0.2255227416753769</v>
+        <v>-0.1760150343179703</v>
       </c>
       <c r="AG36" t="n">
-        <v>-0.2168167680501938</v>
+        <v>-0.1592478305101395</v>
       </c>
       <c r="AH36" t="n">
-        <v>-0.07802793383598328</v>
+        <v>0.366587907075882</v>
       </c>
       <c r="AI36" t="n">
-        <v>-0.1754234731197357</v>
+        <v>-0.1551519483327866</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.1394244283437729</v>
+        <v>-0.2690070569515228</v>
       </c>
       <c r="AK36" t="n">
-        <v>-0.2731585800647736</v>
+        <v>0.1403967887163162</v>
       </c>
       <c r="AL36" t="n">
-        <v>-0.8672270774841309</v>
+        <v>-0.9382916688919067</v>
       </c>
       <c r="AM36" t="n">
-        <v>-0.2314276099205017</v>
+        <v>-0.2548116147518158</v>
       </c>
       <c r="AN36" t="n">
-        <v>-0.2983707785606384</v>
+        <v>0.4110668003559113</v>
       </c>
       <c r="AO36" t="n">
-        <v>0.1986206471920013</v>
+        <v>-0.03352988138794899</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.2421844005584717</v>
+        <v>0.1124444827437401</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.1160577386617661</v>
+        <v>0.5111417174339294</v>
       </c>
       <c r="AR36" t="n">
-        <v>-0.4203670024871826</v>
+        <v>-0.5095241665840149</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.2785040438175201</v>
+        <v>0.3045267164707184</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.1940527856349945</v>
+        <v>0.04793725535273552</v>
       </c>
       <c r="AU36" t="n">
-        <v>0.08428968489170074</v>
+        <v>0.06081770732998848</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.2410449087619781</v>
+        <v>0.1827887445688248</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.5330981612205505</v>
+        <v>0.2490335553884506</v>
       </c>
       <c r="AX36" t="n">
-        <v>-0.1451058238744736</v>
+        <v>-0.291237086057663</v>
       </c>
       <c r="AY36" t="n">
         <v>0</v>
@@ -6112,154 +6112,154 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-0.2416988015174866</v>
+        <v>0.08266577124595642</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.5169363021850586</v>
+        <v>-0.5391760468482971</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.01036817207932472</v>
+        <v>-0.1000088006258011</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.2520093619823456</v>
+        <v>-0.3183163106441498</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0339818149805069</v>
+        <v>0.05110922828316689</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.1754996031522751</v>
+        <v>0.08638203889131546</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.2806483805179596</v>
+        <v>0.1157008036971092</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.07500408589839935</v>
+        <v>0.2375798374414444</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.4438445270061493</v>
+        <v>0.004391091875731945</v>
       </c>
       <c r="J37" t="n">
-        <v>0.1454779207706451</v>
+        <v>-0.01923390105366707</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.2192174196243286</v>
+        <v>-0.4255372285842896</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.06051874533295631</v>
+        <v>0.1433587074279785</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.07966187596321106</v>
+        <v>-0.2308557033538818</v>
       </c>
       <c r="N37" t="n">
-        <v>0.4504259526729584</v>
+        <v>0.1111506372690201</v>
       </c>
       <c r="O37" t="n">
-        <v>0.0201425738632679</v>
+        <v>0.1495041102170944</v>
       </c>
       <c r="P37" t="n">
-        <v>0.144773930311203</v>
+        <v>0.01901119947433472</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.08837036043405533</v>
+        <v>0.2554327845573425</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.5686401128768921</v>
+        <v>-0.4461337029933929</v>
       </c>
       <c r="S37" t="n">
-        <v>-0.09758596122264862</v>
+        <v>-0.2043037712574005</v>
       </c>
       <c r="T37" t="n">
-        <v>0.09483075886964798</v>
+        <v>-0.1688941568136215</v>
       </c>
       <c r="U37" t="n">
-        <v>0.1311299204826355</v>
+        <v>-0.005650209728628397</v>
       </c>
       <c r="V37" t="n">
-        <v>-0.1964448690414429</v>
+        <v>0.06209845095872879</v>
       </c>
       <c r="W37" t="n">
-        <v>-0.2713383138179779</v>
+        <v>0.202235996723175</v>
       </c>
       <c r="X37" t="n">
-        <v>0.1791675835847855</v>
+        <v>-0.03175201639533043</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.4910305738449097</v>
+        <v>0.2738024294376373</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.1284313499927521</v>
+        <v>-0.1751561760902405</v>
       </c>
       <c r="AA37" t="n">
-        <v>-0.2115564346313477</v>
+        <v>-0.06758113950490952</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.08055852353572845</v>
+        <v>0.0138391749933362</v>
       </c>
       <c r="AC37" t="n">
-        <v>-0.06025370210409164</v>
+        <v>-0.1762292832136154</v>
       </c>
       <c r="AD37" t="n">
-        <v>-0.2486923038959503</v>
+        <v>0.05202536284923553</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.02317661419510841</v>
+        <v>-0.02165546268224716</v>
       </c>
       <c r="AF37" t="n">
-        <v>-0.02469823136925697</v>
+        <v>-0.02690159156918526</v>
       </c>
       <c r="AG37" t="n">
-        <v>-0.160502627491951</v>
+        <v>-0.1649722456932068</v>
       </c>
       <c r="AH37" t="n">
-        <v>-0.1691611409187317</v>
+        <v>0.1533542424440384</v>
       </c>
       <c r="AI37" t="n">
-        <v>-0.2067453116178513</v>
+        <v>-0.09298880398273468</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.01074407063424587</v>
+        <v>-0.2699109315872192</v>
       </c>
       <c r="AK37" t="n">
-        <v>-0.1517321169376373</v>
+        <v>0.4232019782066345</v>
       </c>
       <c r="AL37" t="n">
-        <v>-0.6470288634300232</v>
+        <v>-0.9066829085350037</v>
       </c>
       <c r="AM37" t="n">
-        <v>-0.3044677376747131</v>
+        <v>0.07964691519737244</v>
       </c>
       <c r="AN37" t="n">
-        <v>0.1521272361278534</v>
+        <v>0.5453454256057739</v>
       </c>
       <c r="AO37" t="n">
-        <v>-0.09729535132646561</v>
+        <v>-0.1581710875034332</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.1651150733232498</v>
+        <v>0.034794632345438</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.22138312458992</v>
+        <v>0.07087592780590057</v>
       </c>
       <c r="AR37" t="n">
-        <v>-0.1492964178323746</v>
+        <v>-0.4810772240161896</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.3030950129032135</v>
+        <v>0.1830857396125793</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.391033947467804</v>
+        <v>0.113552562892437</v>
       </c>
       <c r="AU37" t="n">
-        <v>-0.3037585020065308</v>
+        <v>0.2430360317230225</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.3102140128612518</v>
+        <v>0.112146757543087</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.2335153669118881</v>
+        <v>0.4059016704559326</v>
       </c>
       <c r="AX37" t="n">
-        <v>-0.3270235061645508</v>
+        <v>-0.2899420857429504</v>
       </c>
       <c r="AY37" t="n">
         <v>0</v>
@@ -6267,154 +6267,154 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-0.3326835334300995</v>
+        <v>0.0608326829969883</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.5189765691757202</v>
+        <v>-0.5883608460426331</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1381169259548187</v>
+        <v>-0.0628359466791153</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.05520812794566154</v>
+        <v>-0.2643519043922424</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.01363293547183275</v>
+        <v>-0.05676114186644554</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.119846798479557</v>
+        <v>0.1979993581771851</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1182581409811974</v>
+        <v>-0.01158672291785479</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3570904135704041</v>
+        <v>0.08509214222431183</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.7473089098930359</v>
+        <v>-0.3781441748142242</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.09340233355760574</v>
+        <v>0.2055021226406097</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.3056637048721313</v>
+        <v>-0.3692796528339386</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.07349171489477158</v>
+        <v>0.604706883430481</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.3327156901359558</v>
+        <v>-0.03619333356618881</v>
       </c>
       <c r="N38" t="n">
-        <v>0.5624492764472961</v>
+        <v>0.2086707651615143</v>
       </c>
       <c r="O38" t="n">
-        <v>0.1756776571273804</v>
+        <v>0.130439966917038</v>
       </c>
       <c r="P38" t="n">
-        <v>0.2646318376064301</v>
+        <v>0.1078534126281738</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.3194511234760284</v>
+        <v>0.3552816808223724</v>
       </c>
       <c r="R38" t="n">
-        <v>-0.5293011665344238</v>
+        <v>-0.4421582221984863</v>
       </c>
       <c r="S38" t="n">
-        <v>-0.3468296825885773</v>
+        <v>-0.2550651729106903</v>
       </c>
       <c r="T38" t="n">
-        <v>-0.09827952831983566</v>
+        <v>-0.048476193100214</v>
       </c>
       <c r="U38" t="n">
-        <v>0.04670319333672523</v>
+        <v>-0.2985267043113708</v>
       </c>
       <c r="V38" t="n">
-        <v>-0.5814578533172607</v>
+        <v>-0.04219942539930344</v>
       </c>
       <c r="W38" t="n">
-        <v>-0.2899639010429382</v>
+        <v>0.02875969372689724</v>
       </c>
       <c r="X38" t="n">
-        <v>0.3275118172168732</v>
+        <v>0.0752420574426651</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.657416820526123</v>
+        <v>0.7935978770256042</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.006208368111401796</v>
+        <v>0.1424092501401901</v>
       </c>
       <c r="AA38" t="n">
-        <v>-0.1550299972295761</v>
+        <v>0.2063835561275482</v>
       </c>
       <c r="AB38" t="n">
-        <v>-0.3945829272270203</v>
+        <v>-0.1164380237460136</v>
       </c>
       <c r="AC38" t="n">
-        <v>-0.1506565660238266</v>
+        <v>-0.3320416808128357</v>
       </c>
       <c r="AD38" t="n">
-        <v>-0.2067701667547226</v>
+        <v>0.01427324768155813</v>
       </c>
       <c r="AE38" t="n">
-        <v>-0.01155429426580667</v>
+        <v>0.161668062210083</v>
       </c>
       <c r="AF38" t="n">
-        <v>-0.2246699184179306</v>
+        <v>-0.1627853065729141</v>
       </c>
       <c r="AG38" t="n">
-        <v>-0.2762386798858643</v>
+        <v>-0.1906499415636063</v>
       </c>
       <c r="AH38" t="n">
-        <v>-0.1189357191324234</v>
+        <v>0.394062876701355</v>
       </c>
       <c r="AI38" t="n">
-        <v>-0.2716286480426788</v>
+        <v>-0.07134432345628738</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.1433925628662109</v>
+        <v>-0.3986804783344269</v>
       </c>
       <c r="AK38" t="n">
-        <v>-0.166794627904892</v>
+        <v>0.0968240424990654</v>
       </c>
       <c r="AL38" t="n">
-        <v>-0.8266531825065613</v>
+        <v>-0.9962114095687866</v>
       </c>
       <c r="AM38" t="n">
-        <v>-0.197208359837532</v>
+        <v>-0.3623447418212891</v>
       </c>
       <c r="AN38" t="n">
-        <v>-0.3134572505950928</v>
+        <v>0.3994855284690857</v>
       </c>
       <c r="AO38" t="n">
-        <v>0.1535703390836716</v>
+        <v>0.05356363207101822</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.2196471393108368</v>
+        <v>0.08672516047954559</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.1111677661538124</v>
+        <v>0.4387752413749695</v>
       </c>
       <c r="AR38" t="n">
-        <v>-0.3967344462871552</v>
+        <v>-0.4336414933204651</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.3125288486480713</v>
+        <v>0.2479473501443863</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.06596889346837997</v>
+        <v>0.06259483844041824</v>
       </c>
       <c r="AU38" t="n">
-        <v>0.07896637916564941</v>
+        <v>0.0139072434976697</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.2706463932991028</v>
+        <v>0.2451532036066055</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.5676937103271484</v>
+        <v>0.2699656188488007</v>
       </c>
       <c r="AX38" t="n">
-        <v>-0.1512783467769623</v>
+        <v>-0.239337757229805</v>
       </c>
       <c r="AY38" t="n">
         <v>0</v>
@@ -6422,154 +6422,154 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>-0.367830216884613</v>
+        <v>0.1294514536857605</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.5080340504646301</v>
+        <v>-0.5659785270690918</v>
       </c>
       <c r="C39" t="n">
-        <v>0.05888637155294418</v>
+        <v>-0.1469634771347046</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.3079343736171722</v>
+        <v>-0.2075500935316086</v>
       </c>
       <c r="E39" t="n">
-        <v>0.07190721482038498</v>
+        <v>0.0525752380490303</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.2705967426300049</v>
+        <v>0.01488138269633055</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.2357620596885681</v>
+        <v>0.277097076177597</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.07349099963903427</v>
+        <v>0.3414486050605774</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.4389378130435944</v>
+        <v>0.004863904789090157</v>
       </c>
       <c r="J39" t="n">
-        <v>0.04639851674437523</v>
+        <v>0.03873065859079361</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.1425145715475082</v>
+        <v>-0.422127902507782</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.162366196513176</v>
+        <v>0.1461610049009323</v>
       </c>
       <c r="M39" t="n">
-        <v>0.03378014639019966</v>
+        <v>-0.07057557255029678</v>
       </c>
       <c r="N39" t="n">
-        <v>0.4063620269298553</v>
+        <v>-0.006099960766732693</v>
       </c>
       <c r="O39" t="n">
-        <v>0.206300362944603</v>
+        <v>0.1322477012872696</v>
       </c>
       <c r="P39" t="n">
-        <v>0.1523233950138092</v>
+        <v>0.1213454157114029</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.1117041856050491</v>
+        <v>0.2043882310390472</v>
       </c>
       <c r="R39" t="n">
-        <v>-0.6564281582832336</v>
+        <v>-0.4546136260032654</v>
       </c>
       <c r="S39" t="n">
-        <v>-0.08642835915088654</v>
+        <v>-0.156538113951683</v>
       </c>
       <c r="T39" t="n">
-        <v>0.1499322354793549</v>
+        <v>-0.1402403861284256</v>
       </c>
       <c r="U39" t="n">
-        <v>0.07668736577033997</v>
+        <v>-0.07895917445421219</v>
       </c>
       <c r="V39" t="n">
-        <v>-0.2701844274997711</v>
+        <v>0.1664387285709381</v>
       </c>
       <c r="W39" t="n">
-        <v>-0.2909236550331116</v>
+        <v>0.2354578226804733</v>
       </c>
       <c r="X39" t="n">
-        <v>0.1356330811977386</v>
+        <v>-0.05336927622556686</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.4960846304893494</v>
+        <v>0.3667877316474915</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.06718584895133972</v>
+        <v>-0.2316599637269974</v>
       </c>
       <c r="AA39" t="n">
-        <v>-0.03872755914926529</v>
+        <v>0.1079157590866089</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.0920596569776535</v>
+        <v>-0.08729853481054306</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.004325494170188904</v>
+        <v>-0.2415056675672531</v>
       </c>
       <c r="AD39" t="n">
-        <v>-0.2674068212509155</v>
+        <v>0.04274235293269157</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.05080434307456017</v>
+        <v>0.03277889639139175</v>
       </c>
       <c r="AF39" t="n">
-        <v>-0.03399692475795746</v>
+        <v>-0.04989593848586082</v>
       </c>
       <c r="AG39" t="n">
-        <v>-0.1769796162843704</v>
+        <v>-0.07684621959924698</v>
       </c>
       <c r="AH39" t="n">
-        <v>-0.2373056709766388</v>
+        <v>0.258436530828476</v>
       </c>
       <c r="AI39" t="n">
-        <v>-0.1743306517601013</v>
+        <v>-0.08848083764314651</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.07409673184156418</v>
+        <v>-0.2526409924030304</v>
       </c>
       <c r="AK39" t="n">
-        <v>-0.05566932260990143</v>
+        <v>0.300131767988205</v>
       </c>
       <c r="AL39" t="n">
-        <v>-0.6256383061408997</v>
+        <v>-0.6931921243667603</v>
       </c>
       <c r="AM39" t="n">
-        <v>-0.2238987684249878</v>
+        <v>-0.01271423045545816</v>
       </c>
       <c r="AN39" t="n">
-        <v>0.1871636062860489</v>
+        <v>0.5466679334640503</v>
       </c>
       <c r="AO39" t="n">
-        <v>-0.0716918557882309</v>
+        <v>-0.08304182440042496</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.07202835381031036</v>
+        <v>0.05057644844055176</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.1157756820321083</v>
+        <v>0.2029293775558472</v>
       </c>
       <c r="AR39" t="n">
-        <v>-0.10550457239151</v>
+        <v>-0.3794165253639221</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.2555217146873474</v>
+        <v>0.07533016800880432</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.3359315395355225</v>
+        <v>-0.03871883079409599</v>
       </c>
       <c r="AU39" t="n">
-        <v>-0.29997518658638</v>
+        <v>0.08542061597108841</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.3513432741165161</v>
+        <v>0.1987373530864716</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.2164023816585541</v>
+        <v>0.4083351194858551</v>
       </c>
       <c r="AX39" t="n">
-        <v>-0.2538371086120605</v>
+        <v>-0.3292064964771271</v>
       </c>
       <c r="AY39" t="n">
         <v>0</v>
@@ -6577,154 +6577,154 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>-0.2688199877738953</v>
+        <v>0.128383457660675</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.5050778388977051</v>
+        <v>-0.5711171627044678</v>
       </c>
       <c r="C40" t="n">
-        <v>0.007099202834069729</v>
+        <v>-0.1867740154266357</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2564099431037903</v>
+        <v>-0.2055288255214691</v>
       </c>
       <c r="E40" t="n">
-        <v>0.01785651035606861</v>
+        <v>0.05563408881425858</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.1697223484516144</v>
+        <v>0.02437800168991089</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.2337913513183594</v>
+        <v>0.2714995443820953</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.007775655947625637</v>
+        <v>0.2641579210758209</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3534662127494812</v>
+        <v>-0.0244817603379488</v>
       </c>
       <c r="J40" t="n">
-        <v>0.08599857985973358</v>
+        <v>0.07078144699335098</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.1951316148042679</v>
+        <v>-0.4475716948509216</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.1528410911560059</v>
+        <v>0.2132959067821503</v>
       </c>
       <c r="M40" t="n">
-        <v>0.002748671220615506</v>
+        <v>-0.1876956224441528</v>
       </c>
       <c r="N40" t="n">
-        <v>0.4179529249668121</v>
+        <v>0.07075557857751846</v>
       </c>
       <c r="O40" t="n">
-        <v>0.01189204026013613</v>
+        <v>0.1125984638929367</v>
       </c>
       <c r="P40" t="n">
-        <v>0.1600283533334732</v>
+        <v>0.09677139669656754</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.09257811307907104</v>
+        <v>0.2575350403785706</v>
       </c>
       <c r="R40" t="n">
-        <v>-0.6334825754165649</v>
+        <v>-0.4695416986942291</v>
       </c>
       <c r="S40" t="n">
-        <v>-0.1283081024885178</v>
+        <v>-0.1453704088926315</v>
       </c>
       <c r="T40" t="n">
-        <v>0.250715434551239</v>
+        <v>-0.1314961165189743</v>
       </c>
       <c r="U40" t="n">
-        <v>0.06991345435380936</v>
+        <v>-0.04299867525696754</v>
       </c>
       <c r="V40" t="n">
-        <v>-0.2024025917053223</v>
+        <v>0.1687591522932053</v>
       </c>
       <c r="W40" t="n">
-        <v>-0.2030285745859146</v>
+        <v>0.2463800460100174</v>
       </c>
       <c r="X40" t="n">
-        <v>0.1023425906896591</v>
+        <v>-0.1018698439002037</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.4593113958835602</v>
+        <v>0.2959833741188049</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.1181889399886131</v>
+        <v>-0.1946101486682892</v>
       </c>
       <c r="AA40" t="n">
-        <v>-0.1721195131540298</v>
+        <v>0.021574717015028</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.0536762997508049</v>
+        <v>-0.006522055715322495</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.007877068594098091</v>
+        <v>-0.1481437683105469</v>
       </c>
       <c r="AD40" t="n">
-        <v>-0.2918579280376434</v>
+        <v>0.1098241060972214</v>
       </c>
       <c r="AE40" t="n">
-        <v>-0.01042984053492546</v>
+        <v>0.04425172135233879</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.004113237839192152</v>
+        <v>-0.0354294516146183</v>
       </c>
       <c r="AG40" t="n">
-        <v>-0.1444292664527893</v>
+        <v>-0.1521345227956772</v>
       </c>
       <c r="AH40" t="n">
-        <v>-0.1732827574014664</v>
+        <v>0.172532320022583</v>
       </c>
       <c r="AI40" t="n">
-        <v>-0.1580953299999237</v>
+        <v>-0.08489515632390976</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.04724816977977753</v>
+        <v>-0.2197897732257843</v>
       </c>
       <c r="AK40" t="n">
-        <v>-0.1024251282215118</v>
+        <v>0.3806174397468567</v>
       </c>
       <c r="AL40" t="n">
-        <v>-0.6525943875312805</v>
+        <v>-0.6459600925445557</v>
       </c>
       <c r="AM40" t="n">
-        <v>-0.278465747833252</v>
+        <v>0.03169337660074234</v>
       </c>
       <c r="AN40" t="n">
-        <v>0.1421447545289993</v>
+        <v>0.5921531319618225</v>
       </c>
       <c r="AO40" t="n">
-        <v>-0.06021718680858612</v>
+        <v>-0.1747649013996124</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.1345369964838028</v>
+        <v>0.06946154683828354</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.07956631481647491</v>
+        <v>0.1431533992290497</v>
       </c>
       <c r="AR40" t="n">
-        <v>-0.1432603746652603</v>
+        <v>-0.4408186376094818</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.249531015753746</v>
+        <v>0.1407743096351624</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.4205867946147919</v>
+        <v>0.09633257240056992</v>
       </c>
       <c r="AU40" t="n">
-        <v>-0.3187365233898163</v>
+        <v>0.05443870648741722</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.3080988526344299</v>
+        <v>0.1133927181363106</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.2483475506305695</v>
+        <v>0.3136693239212036</v>
       </c>
       <c r="AX40" t="n">
-        <v>-0.2574918866157532</v>
+        <v>-0.3128090500831604</v>
       </c>
       <c r="AY40" t="n">
         <v>0</v>
@@ -6732,154 +6732,154 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-0.3325807750225067</v>
+        <v>0.04340283572673798</v>
       </c>
       <c r="B41" t="n">
-        <v>-0.4953594505786896</v>
+        <v>-0.6371082663536072</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.01461939699947834</v>
+        <v>-0.2782315909862518</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1767271608114243</v>
+        <v>-0.2142840474843979</v>
       </c>
       <c r="E41" t="n">
-        <v>0.07985294610261917</v>
+        <v>0.06489825993776321</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.2952067852020264</v>
+        <v>0.04324331507086754</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.2377571016550064</v>
+        <v>0.1031903177499771</v>
       </c>
       <c r="H41" t="n">
-        <v>0.03271184116601944</v>
+        <v>0.2613897323608398</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4885692894458771</v>
+        <v>-0.05166858062148094</v>
       </c>
       <c r="J41" t="n">
-        <v>0.02514543943107128</v>
+        <v>0.1477218866348267</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.1929862946271896</v>
+        <v>-0.3899933099746704</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.1064069122076035</v>
+        <v>0.1621568948030472</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.04770160093903542</v>
+        <v>-0.2119177728891373</v>
       </c>
       <c r="N41" t="n">
-        <v>0.4510079622268677</v>
+        <v>0.09603977203369141</v>
       </c>
       <c r="O41" t="n">
-        <v>0.1930055469274521</v>
+        <v>0.1082861721515656</v>
       </c>
       <c r="P41" t="n">
-        <v>0.09287264943122864</v>
+        <v>-0.0127573786303401</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.09139886498451233</v>
+        <v>0.2048194706439972</v>
       </c>
       <c r="R41" t="n">
-        <v>-0.559172511100769</v>
+        <v>-0.4536812305450439</v>
       </c>
       <c r="S41" t="n">
-        <v>-0.2374992221593857</v>
+        <v>-0.2193746268749237</v>
       </c>
       <c r="T41" t="n">
-        <v>0.1388222426176071</v>
+        <v>-0.1664850413799286</v>
       </c>
       <c r="U41" t="n">
-        <v>0.1410912424325943</v>
+        <v>-0.1510107219219208</v>
       </c>
       <c r="V41" t="n">
-        <v>-0.1677238941192627</v>
+        <v>-0.01051451731473207</v>
       </c>
       <c r="W41" t="n">
-        <v>-0.2413108795881271</v>
+        <v>0.1971412748098373</v>
       </c>
       <c r="X41" t="n">
-        <v>0.1288006603717804</v>
+        <v>0.01079768221825361</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.6091123819351196</v>
+        <v>0.3595696985721588</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.05703698471188545</v>
+        <v>-0.2424633651971817</v>
       </c>
       <c r="AA41" t="n">
-        <v>-0.05087766796350479</v>
+        <v>0.06925731152296066</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.1281103044748306</v>
+        <v>-0.1027746647596359</v>
       </c>
       <c r="AC41" t="n">
-        <v>-0.09790325164794922</v>
+        <v>-0.3003859519958496</v>
       </c>
       <c r="AD41" t="n">
-        <v>-0.2617736458778381</v>
+        <v>0.06953795254230499</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.04217225313186646</v>
+        <v>-0.02814186923205853</v>
       </c>
       <c r="AF41" t="n">
-        <v>-0.01817041262984276</v>
+        <v>-0.04267273470759392</v>
       </c>
       <c r="AG41" t="n">
-        <v>-0.1964940875768661</v>
+        <v>-0.06024017930030823</v>
       </c>
       <c r="AH41" t="n">
-        <v>-0.2623375952243805</v>
+        <v>0.2096170634031296</v>
       </c>
       <c r="AI41" t="n">
-        <v>-0.1963546425104141</v>
+        <v>-0.1375724077224731</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.09201794117689133</v>
+        <v>-0.250324159860611</v>
       </c>
       <c r="AK41" t="n">
-        <v>-0.03740594163537025</v>
+        <v>0.3415797352790833</v>
       </c>
       <c r="AL41" t="n">
-        <v>-0.6402485370635986</v>
+        <v>-0.8534193634986877</v>
       </c>
       <c r="AM41" t="n">
-        <v>-0.1907812803983688</v>
+        <v>-0.05325507372617722</v>
       </c>
       <c r="AN41" t="n">
-        <v>0.1441912800073624</v>
+        <v>0.4906408786773682</v>
       </c>
       <c r="AO41" t="n">
-        <v>-0.09242548793554306</v>
+        <v>-0.05538858845829964</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.1621924191713333</v>
+        <v>0.06623437255620956</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.1622143238782883</v>
+        <v>0.1013267114758492</v>
       </c>
       <c r="AR41" t="n">
-        <v>-0.2410827130079269</v>
+        <v>-0.4161092042922974</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.2858326733112335</v>
+        <v>0.1313876807689667</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.2554358541965485</v>
+        <v>0.08722231537103653</v>
       </c>
       <c r="AU41" t="n">
-        <v>-0.2367464900016785</v>
+        <v>0.02051110751926899</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.4111754894256592</v>
+        <v>0.2623990774154663</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.2394630610942841</v>
+        <v>0.411771833896637</v>
       </c>
       <c r="AX41" t="n">
-        <v>-0.3272852897644043</v>
+        <v>-0.2946912944316864</v>
       </c>
       <c r="AY41" t="n">
         <v>0</v>
